--- a/src/attributions/attributions_saliency_traj_165.xlsx
+++ b/src/attributions/attributions_saliency_traj_165.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03064239025115967</v>
+        <v>7.488707342417911e-05</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01333566568791866</v>
+        <v>1.949600664374884e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002600640058517456</v>
+        <v>9.251743904314935e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006317188963294029</v>
+        <v>0.0004164128913544118</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003490629605948925</v>
+        <v>4.336858546594158e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007353659253567457</v>
+        <v>3.742444823728874e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001403734087944031</v>
+        <v>9.069110092241317e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001869297353550792</v>
+        <v>5.906449950998649e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004235398955643177</v>
+        <v>2.895278885262087e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02624965086579323</v>
+        <v>3.969705721829087e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00783095508813858</v>
+        <v>5.105930176796392e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002398312790319324</v>
+        <v>6.513830157928169e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003002840094268322</v>
+        <v>0.0005934000946581364</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002175292000174522</v>
+        <v>0.0001991588360397145</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003165229223668575</v>
+        <v>0.0001227508037118241</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003133560530841351</v>
+        <v>8.196983253583312e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00315348943695426</v>
+        <v>9.906472405418754e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001411493169143796</v>
+        <v>1.279640855500475e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.006103773601353168</v>
+        <v>1.922527189890388e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>0.008626993745565414</v>
+        <v>3.82654725399334e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001547375693917274</v>
+        <v>1.717856503091753e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00666850944980979</v>
+        <v>2.761337600531988e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>0.008114107884466648</v>
+        <v>1.037980382534442e-06</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004197543021291494</v>
+        <v>0.0001662536669755355</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001240164623595774</v>
+        <v>3.072606341447681e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.003073366358876228</v>
+        <v>4.5497712562792e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001882159500382841</v>
+        <v>7.167378498706967e-06</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.002205181634053588</v>
+        <v>8.515615263604559e-06</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.00738761480897665</v>
+        <v>8.439092198386788e-07</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0001972935860976577</v>
+        <v>8.14492377685383e-05</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.001018999377265573</v>
+        <v>3.444157846388407e-05</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.008416567929089069</v>
+        <v>9.64681021287106e-05</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.003467726754024625</v>
+        <v>9.368347673444077e-05</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0008606607443653047</v>
+        <v>7.004124927334487e-05</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.001721864799037576</v>
+        <v>2.287957795488182e-05</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.00309390458278358</v>
+        <v>7.49617101973854e-05</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0010872712591663</v>
+        <v>3.388525146874599e-05</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.004089728929102421</v>
+        <v>5.369071368477307e-05</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.003589707892388105</v>
+        <v>1.329217502643587e-05</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0003272304311394691</v>
+        <v>9.678830247139558e-05</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.003303691511973739</v>
+        <v>1.65499350259779e-05</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0005692169070243835</v>
+        <v>4.576098217512481e-05</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.00054455193458125</v>
+        <v>0.0001115412233048119</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.003158056642860174</v>
+        <v>2.198078072979115e-05</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0005336151807568967</v>
+        <v>6.259921974560712e-06</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.01472195517271757</v>
+        <v>7.13297922629863e-05</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.002161608077585697</v>
+        <v>7.773489778628573e-05</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.214032277464867e-06</v>
+        <v>4.140616147196852e-05</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.006345923524349928</v>
+        <v>0.0002041288971668109</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.003272929461672902</v>
+        <v>0.0001838335301727057</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.00149505166336894</v>
+        <v>3.027015372936148e-05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.006035975180566311</v>
+        <v>4.391016773297451e-06</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.005167306400835514</v>
+        <v>4.247172182658687e-05</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.003034750465303659</v>
+        <v>3.582337012630887e-05</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0129933450371027</v>
+        <v>0.0001316829439019784</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.01296116877347231</v>
+        <v>2.747185590123991e-07</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0005430795717984438</v>
+        <v>9.725478776090313e-06</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.002550291828811169</v>
+        <v>4.459583215066232e-05</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.006728728767484426</v>
+        <v>6.632968143094331e-05</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.001024671830236912</v>
+        <v>8.450854511465877e-05</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.003623769152909517</v>
+        <v>6.379042315529659e-05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.00277811917476356</v>
+        <v>0.0001280961296288297</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.007054434157907963</v>
+        <v>0.0001166011279565282</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0006766734295524657</v>
+        <v>6.492964075732743e-06</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.007137606386095285</v>
+        <v>7.034774625935825e-06</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.002823417540639639</v>
+        <v>2.562899317126721e-05</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.002218231093138456</v>
+        <v>0.0001097879867302254</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.002321095205843449</v>
+        <v>5.008875086787157e-05</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.004265612922608852</v>
+        <v>1.555477501824498e-05</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.002256285864859819</v>
+        <v>4.330504816607572e-05</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.001587879145517945</v>
+        <v>2.493389183655381e-05</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.001176188350655138</v>
+        <v>2.4488608687534e-05</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.008775882422924042</v>
+        <v>5.359379429137334e-05</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.006671234499663115</v>
+        <v>4.824352799914777e-05</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.002984323538839817</v>
+        <v>1.828211679821834e-05</v>
       </c>
       <c r="BX2" t="n">
-        <v>6.409399793483317e-05</v>
+        <v>0.0002120018471032381</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.004027975257486105</v>
+        <v>3.481261228444055e-05</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.001999587984755635</v>
+        <v>7.09917294443585e-05</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.00258215144276619</v>
+        <v>4.381906546768732e-05</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.002532597631216049</v>
+        <v>1.29604413814377e-05</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.004356714896857738</v>
+        <v>3.848007327178493e-05</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.006447813473641872</v>
+        <v>2.242997106804978e-05</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.003561204532161355</v>
+        <v>3.717269646585919e-05</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.001421401393599808</v>
+        <v>1.25509177451022e-05</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.00122785521671176</v>
+        <v>0.0001544295810163021</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.001215530559420586</v>
+        <v>2.353747186134569e-05</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.003644153475761414</v>
+        <v>3.845632454613224e-05</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.0007465564995072782</v>
+        <v>2.225785465270746e-05</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.002305088099092245</v>
+        <v>3.334488428663462e-05</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.0004645426815841347</v>
+        <v>1.911865365400445e-05</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.007833480834960938</v>
+        <v>1.208254525408847e-05</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.004550473764538765</v>
+        <v>8.958970283856615e-06</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0002138214185833931</v>
+        <v>9.107188816415146e-05</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.004645644687116146</v>
+        <v>0.0002226286451332271</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.006421519909054041</v>
+        <v>1.514999712526333e-05</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.003691236721351743</v>
+        <v>2.923933789134026e-05</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.002483531134203076</v>
+        <v>3.742436820175499e-05</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.004202927928417921</v>
+        <v>0.0001135169513872825</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.0006401555729098618</v>
+        <v>8.40777502162382e-05</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.005441987887024879</v>
+        <v>2.407645479252096e-05</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.004173136316239834</v>
+        <v>3.713360638357699e-05</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.002237340901046991</v>
+        <v>2.200820745201781e-05</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0007282629958353937</v>
+        <v>0.0001650033518671989</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.001438578590750694</v>
+        <v>3.825959356618114e-05</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.003747655777260661</v>
+        <v>1.530675035610329e-05</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0006377066019922495</v>
+        <v>8.979217454907484e-06</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.001613285043276846</v>
+        <v>2.180102092097513e-05</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.0003990783588960767</v>
+        <v>1.307861475652317e-05</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.004569104872643948</v>
+        <v>7.482220098609105e-06</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.01075793616473675</v>
+        <v>1.700471693766303e-05</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.004130610264837742</v>
+        <v>0.000173649939824827</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.004874110221862793</v>
+        <v>7.769287913106382e-05</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.009791355580091476</v>
+        <v>0.0001075830441550352</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.007820699363946915</v>
+        <v>8.507912571076304e-05</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.006473154295235872</v>
+        <v>8.820318180369213e-05</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.008830609731376171</v>
+        <v>0.0001920991635415703</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.0007094132015481591</v>
+        <v>1.855119080573786e-05</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.005037752911448479</v>
+        <v>4.873617945122533e-05</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.00206596334464848</v>
+        <v>6.666943954769522e-05</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.0005920552648603916</v>
+        <v>0.0001087434939108789</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.007198266219347715</v>
+        <v>6.14043019595556e-05</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.004598012194037437</v>
+        <v>9.422139555681497e-05</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.007659775204956532</v>
+        <v>4.11440669267904e-05</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.0006655105389654636</v>
+        <v>4.474904199014418e-05</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.00180925871245563</v>
+        <v>8.266721124527976e-05</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.001248476561158895</v>
+        <v>9.47525113588199e-05</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.005701006390154362</v>
+        <v>2.615242192405276e-05</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.002841718960553408</v>
+        <v>8.941144187701866e-06</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.00140546471811831</v>
+        <v>0.0001936921325977892</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.0008812720770947635</v>
+        <v>3.578182077035308e-05</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.003551461733877659</v>
+        <v>2.185317862313241e-05</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.004018895793706179</v>
+        <v>6.371674680849537e-05</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.004094940144568682</v>
+        <v>3.320442556287162e-05</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.001612509367987514</v>
+        <v>0.0002119156415574253</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.001785367843694985</v>
+        <v>8.912065095501021e-05</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.006633831653743982</v>
+        <v>7.98129040049389e-05</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.008545830845832825</v>
+        <v>1.053959931596182e-05</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.007860961370170116</v>
+        <v>1.693722651907592e-06</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.003773381933569908</v>
+        <v>0.0001490861177444458</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0005799494683742523</v>
+        <v>6.814722291892394e-05</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.00370349339209497</v>
+        <v>3.148946780129336e-05</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.001101151923649013</v>
+        <v>3.892580934916623e-06</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.002544372575357556</v>
+        <v>7.770214324409608e-06</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.0004360306193120778</v>
+        <v>6.215463145053945e-06</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.0008468460873700678</v>
+        <v>2.23304105020361e-05</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.008387971669435501</v>
+        <v>2.459752977301832e-05</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.0005175094120204449</v>
+        <v>4.264113522367552e-05</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.000972876267042011</v>
+        <v>0.0001467389520257711</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.002362402155995369</v>
+        <v>2.181458694394678e-05</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.009727058932185173</v>
+        <v>4.682995859184302e-05</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.001001665950752795</v>
+        <v>2.897536978707649e-05</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.002943988656625152</v>
+        <v>6.038834180799313e-05</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.003499068785458803</v>
+        <v>6.972575647523627e-05</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.006174700800329447</v>
+        <v>1.551018613099586e-05</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.004101828206330538</v>
+        <v>2.599086474219803e-05</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.002985199447721243</v>
+        <v>9.84388589131413e-06</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.0002072372881229967</v>
+        <v>0.0001991962926695123</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.001808884437195957</v>
+        <v>2.236492582596838e-05</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.002716967836022377</v>
+        <v>7.794553312123753e-06</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.0002250756369903684</v>
+        <v>7.236467354232445e-07</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.001873771310783923</v>
+        <v>4.248485493008047e-05</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.0005484962021000683</v>
+        <v>9.523447261017282e-06</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.002347997156903148</v>
+        <v>1.968650394701399e-05</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.002898499602451921</v>
+        <v>2.808399221976288e-05</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.002921442035585642</v>
+        <v>2.510156082280446e-05</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.002360600978136063</v>
+        <v>0.0001100439185393043</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.0001582327822688967</v>
+        <v>0.0001030941348290071</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.0006740383105352521</v>
+        <v>5.284628059598617e-06</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.001733324956148863</v>
+        <v>1.764822081895545e-05</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.0001153654302470386</v>
+        <v>7.683451258344576e-05</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.001415731501765549</v>
+        <v>3.611964348237962e-05</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.004625509493052959</v>
+        <v>6.430179928429425e-05</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.00222176406532526</v>
+        <v>8.194628026103601e-05</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.008561877533793449</v>
+        <v>6.376600504154339e-05</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.004366207867860794</v>
+        <v>0.0001459136692574248</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.009504438377916813</v>
+        <v>3.006166662089527e-05</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.00526475952938199</v>
+        <v>0.0001297332055401057</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.008057220838963985</v>
+        <v>8.422075552516617e-06</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.000667886168230325</v>
+        <v>0.0001610813778825104</v>
       </c>
       <c r="FX2" t="n">
-        <v>7.075793109834194e-05</v>
+        <v>5.072755084256642e-05</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.000358989869710058</v>
+        <v>4.120605353818974e-06</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.005458422005176544</v>
+        <v>2.580795080575626e-05</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.0009953937260434031</v>
+        <v>4.477757829590701e-05</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.002555532148107886</v>
+        <v>0.0001839474134612828</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.009510272182524204</v>
+        <v>2.305376438016538e-05</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.001945127965882421</v>
+        <v>8.80783554748632e-05</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.003516673808917403</v>
+        <v>8.503091521561146e-05</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.002334181685000658</v>
+        <v>1.446929127268959e-05</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.000701767101418227</v>
+        <v>3.120396286249161e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2706,6830 +2706,6830 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4.901096872345079e-06</v>
+        <v>1.749316469457085e-09</v>
       </c>
       <c r="B5" t="n">
-        <v>3.647983248811215e-05</v>
+        <v>1.012781414289066e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.936526354664238e-06</v>
+        <v>6.865971124980774e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.062375097011682e-05</v>
+        <v>5.691343396563298e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>8.42841745907208e-06</v>
+        <v>1.564156443256692e-11</v>
       </c>
       <c r="F5" t="n">
-        <v>1.051770959747955e-05</v>
+        <v>4.843580203583997e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>9.130026228376664e-07</v>
+        <v>2.024490020069436e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>6.050216256880958e-07</v>
+        <v>1.485774836496034e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>2.904142547777155e-06</v>
+        <v>1.447262532039417e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>9.974150088964961e-06</v>
+        <v>1.1927303589232e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>2.86007416434586e-05</v>
+        <v>1.023734341742966e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.523738885429339e-06</v>
+        <v>2.111526731241042e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>1.468185655539855e-05</v>
+        <v>8.865054468287781e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>8.826493285596371e-06</v>
+        <v>3.416644300813232e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>1.734166289679706e-05</v>
+        <v>5.996342089531481e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>4.3719073801185e-06</v>
+        <v>8.366857900954372e-11</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.865867817396065e-06</v>
+        <v>7.338585295002531e-11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.147412262980652e-06</v>
+        <v>1.627352363975376e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.244526742993912e-06</v>
+        <v>4.781303131196069e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>5.272239377518417e-06</v>
+        <v>3.090472044942061e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>1.013938685900939e-06</v>
+        <v>9.40768019042082e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>2.250892521260539e-06</v>
+        <v>7.077359254203941e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>1.603467012500914e-06</v>
+        <v>2.143085930939037e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>4.143661499256268e-06</v>
+        <v>9.652568744300538e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.03790170114371e-06</v>
+        <v>2.332287918349607e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.531665581453126e-06</v>
+        <v>1.755685929971662e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.778662398370216e-06</v>
+        <v>8.522166305979795e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44070440910582e-06</v>
+        <v>6.516489015062632e-10</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.934900973945332e-07</v>
+        <v>1.758825529663e-09</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.01661020280153e-07</v>
+        <v>2.907963037035444e-10</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.160288888968353e-06</v>
+        <v>1.975571040091495e-09</v>
       </c>
       <c r="AF5" t="n">
-        <v>5.505850708686921e-07</v>
+        <v>9.431457836939217e-10</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.64739196861774e-06</v>
+        <v>2.530280429624554e-09</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.667071387601027e-06</v>
+        <v>7.197118595536622e-11</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.770839048731432e-06</v>
+        <v>3.164792650167669e-09</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.24236441681569e-06</v>
+        <v>7.559590731176513e-10</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.807242824725108e-06</v>
+        <v>4.816929077833265e-10</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.341645646694815e-06</v>
+        <v>1.53483603604343e-09</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.031336862273747e-06</v>
+        <v>2.548748545549984e-09</v>
       </c>
       <c r="AN5" t="n">
-        <v>6.551933324772108e-07</v>
+        <v>2.267876553219139e-09</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.226914688208126e-07</v>
+        <v>9.167445136348817e-10</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.460641101402871e-07</v>
+        <v>7.137149204972104e-10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.181385980293271e-06</v>
+        <v>5.2145254780811e-10</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.624433351338666e-07</v>
+        <v>7.246604705191118e-11</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.388326604181202e-06</v>
+        <v>5.439985684141391e-10</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.283227104271646e-06</v>
+        <v>6.354580195377935e-10</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.250865327368956e-05</v>
+        <v>6.439919708611797e-09</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.517448802398576e-07</v>
+        <v>2.81736700635804e-09</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.063500899879728e-06</v>
+        <v>1.447305719715075e-09</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.394811074031168e-06</v>
+        <v>7.038977400952717e-09</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.392047235844075e-06</v>
+        <v>4.555718913223927e-09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.60735452886729e-06</v>
+        <v>1.722551962179963e-10</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.728581651150307e-06</v>
+        <v>8.604985612947758e-10</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.180950549605768e-06</v>
+        <v>6.254630147140006e-11</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.525920647007297e-06</v>
+        <v>9.393788524825197e-11</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.554640887974529e-06</v>
+        <v>2.951647370963428e-09</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.054373205988668e-05</v>
+        <v>2.602246196303781e-10</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.852764282579301e-06</v>
+        <v>2.095219775455348e-09</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.859182576590683e-06</v>
+        <v>4.493978522646103e-09</v>
       </c>
       <c r="BH5" t="n">
-        <v>6.700119229208212e-06</v>
+        <v>5.029088812058546e-10</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.479645334256929e-06</v>
+        <v>1.019503481636264e-09</v>
       </c>
       <c r="BJ5" t="n">
-        <v>7.692511644563638e-06</v>
+        <v>3.148710625566764e-09</v>
       </c>
       <c r="BK5" t="n">
-        <v>2.18080072045268e-06</v>
+        <v>9.867295869270265e-10</v>
       </c>
       <c r="BL5" t="n">
-        <v>2.685640538402367e-06</v>
+        <v>3.771230550064786e-10</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.797536692218273e-06</v>
+        <v>6.979616884450479e-10</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.557942131417803e-06</v>
+        <v>1.50638113094459e-11</v>
       </c>
       <c r="BO5" t="n">
-        <v>7.616585548930743e-07</v>
+        <v>7.353336828330725e-10</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.671098061706289e-06</v>
+        <v>2.350571293163739e-09</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.609686357071041e-07</v>
+        <v>2.307573715443212e-10</v>
       </c>
       <c r="BR5" t="n">
-        <v>1.441826384507294e-06</v>
+        <v>5.389000357070017e-10</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.651970305578288e-07</v>
+        <v>1.311291852879037e-09</v>
       </c>
       <c r="BT5" t="n">
-        <v>1.548985721910867e-07</v>
+        <v>3.661447811609264e-10</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.485131057663239e-07</v>
+        <v>1.27602858834841e-10</v>
       </c>
       <c r="BV5" t="n">
-        <v>1.209150104841683e-05</v>
+        <v>2.827842848773798e-09</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.347543836047407e-06</v>
+        <v>1.238250169066646e-09</v>
       </c>
       <c r="BX5" t="n">
-        <v>5.473461897054221e-06</v>
+        <v>1.619371747807463e-09</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.65691879678343e-07</v>
+        <v>1.073759636760485e-09</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.177644321614935e-06</v>
+        <v>2.095864815032655e-09</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.276486379239941e-06</v>
+        <v>2.147095390370168e-09</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.269668246095534e-06</v>
+        <v>5.426914473360966e-10</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.726775841845665e-06</v>
+        <v>6.50777695621052e-11</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.355317457793717e-07</v>
+        <v>2.729852455196635e-10</v>
       </c>
       <c r="CE5" t="n">
-        <v>5.922904620092595e-06</v>
+        <v>3.376213308925458e-09</v>
       </c>
       <c r="CF5" t="n">
-        <v>4.27880468123476e-06</v>
+        <v>7.965893916717093e-11</v>
       </c>
       <c r="CG5" t="n">
-        <v>1.691119450697443e-06</v>
+        <v>1.734167365263772e-09</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.10344569748122e-06</v>
+        <v>5.505403355421379e-10</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.486269977453048e-06</v>
+        <v>1.186572395894814e-09</v>
       </c>
       <c r="CJ5" t="n">
-        <v>5.550455171032809e-07</v>
+        <v>3.842385021268768e-10</v>
       </c>
       <c r="CK5" t="n">
-        <v>4.477036270600365e-07</v>
+        <v>5.288586235607795e-11</v>
       </c>
       <c r="CL5" t="n">
-        <v>3.439157580942265e-06</v>
+        <v>4.880176818211623e-10</v>
       </c>
       <c r="CM5" t="n">
-        <v>3.405805728107225e-06</v>
+        <v>1.950180683607527e-09</v>
       </c>
       <c r="CN5" t="n">
-        <v>9.691457307781093e-07</v>
+        <v>3.970801909503052e-09</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.604509179742308e-06</v>
+        <v>3.668116255184373e-09</v>
       </c>
       <c r="CP5" t="n">
-        <v>4.579835604090476e-06</v>
+        <v>3.462835795886576e-09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.745338972294121e-06</v>
+        <v>8.787764405049359e-10</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.793811861716677e-06</v>
+        <v>9.814643542327417e-11</v>
       </c>
       <c r="CS5" t="n">
-        <v>6.73357499181293e-06</v>
+        <v>2.162882095646523e-10</v>
       </c>
       <c r="CT5" t="n">
-        <v>4.830464604310691e-06</v>
+        <v>2.7365234522847e-09</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.583131847837649e-07</v>
+        <v>1.108584557485415e-09</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.803228653647238e-07</v>
+        <v>5.136370218039588e-10</v>
       </c>
       <c r="CW5" t="n">
-        <v>5.254234110907419e-06</v>
+        <v>3.160834927129486e-09</v>
       </c>
       <c r="CX5" t="n">
-        <v>3.898129307344789e-06</v>
+        <v>3.936372339197192e-10</v>
       </c>
       <c r="CY5" t="n">
-        <v>3.960600224672817e-06</v>
+        <v>1.956264927827078e-09</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.316703446718748e-06</v>
+        <v>9.24303189542286e-10</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.969350362036494e-06</v>
+        <v>1.396111670715072e-09</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.181229436042486e-06</v>
+        <v>5.048678697328057e-10</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.208598860102938e-06</v>
+        <v>1.578414482450441e-10</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.259306484120316e-06</v>
+        <v>3.216818478257721e-10</v>
       </c>
       <c r="DE5" t="n">
-        <v>2.645498852871242e-06</v>
+        <v>1.232850710408684e-09</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.253026084668818e-06</v>
+        <v>5.148553250400312e-10</v>
       </c>
       <c r="DG5" t="n">
-        <v>7.766156159050297e-06</v>
+        <v>1.416782247076753e-09</v>
       </c>
       <c r="DH5" t="n">
-        <v>1.918458838190418e-05</v>
+        <v>2.110317476322621e-09</v>
       </c>
       <c r="DI5" t="n">
-        <v>4.61956324215862e-06</v>
+        <v>1.80633108470829e-09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.556456138336216e-06</v>
+        <v>2.960942380170195e-09</v>
       </c>
       <c r="DK5" t="n">
-        <v>2.215920858361642e-06</v>
+        <v>6.37087049781826e-10</v>
       </c>
       <c r="DL5" t="n">
-        <v>5.359929673431907e-06</v>
+        <v>2.913865149167805e-09</v>
       </c>
       <c r="DM5" t="n">
-        <v>1.234297997143585e-07</v>
+        <v>1.445872754857191e-09</v>
       </c>
       <c r="DN5" t="n">
-        <v>2.164362911116768e-08</v>
+        <v>1.471774924155511e-10</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.328864866285585e-06</v>
+        <v>1.241844627131172e-09</v>
       </c>
       <c r="DP5" t="n">
-        <v>4.526552856987109e-06</v>
+        <v>5.27259347293807e-10</v>
       </c>
       <c r="DQ5" t="n">
-        <v>1.180293907054875e-06</v>
+        <v>8.932626305302449e-10</v>
       </c>
       <c r="DR5" t="n">
-        <v>1.158984105131822e-06</v>
+        <v>2.717691349740647e-10</v>
       </c>
       <c r="DS5" t="n">
-        <v>2.730651203819434e-06</v>
+        <v>1.375224101263228e-10</v>
       </c>
       <c r="DT5" t="n">
-        <v>5.30042711943679e-07</v>
+        <v>1.824551176810019e-09</v>
       </c>
       <c r="DU5" t="n">
-        <v>1.436012553313049e-07</v>
+        <v>1.532100446510753e-09</v>
       </c>
       <c r="DV5" t="n">
-        <v>7.133649887691718e-06</v>
+        <v>3.402536585817018e-10</v>
       </c>
       <c r="DW5" t="n">
-        <v>2.445349764457205e-06</v>
+        <v>2.013726130289939e-10</v>
       </c>
       <c r="DX5" t="n">
-        <v>5.218164915277157e-06</v>
+        <v>1.466250121318069e-09</v>
       </c>
       <c r="DY5" t="n">
-        <v>5.332452474249294e-06</v>
+        <v>1.769365876036488e-09</v>
       </c>
       <c r="DZ5" t="n">
-        <v>1.56621933911083e-06</v>
+        <v>2.029421963811728e-09</v>
       </c>
       <c r="EA5" t="n">
-        <v>1.564952526678098e-06</v>
+        <v>1.680299677175867e-09</v>
       </c>
       <c r="EB5" t="n">
-        <v>5.899961706745671e-06</v>
+        <v>9.844404180725519e-10</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.848708620855177e-06</v>
+        <v>5.647349810011804e-10</v>
       </c>
       <c r="ED5" t="n">
-        <v>1.285419216401351e-06</v>
+        <v>3.238416868001082e-09</v>
       </c>
       <c r="EE5" t="n">
-        <v>7.611324690515175e-07</v>
+        <v>1.784993597375717e-09</v>
       </c>
       <c r="EF5" t="n">
-        <v>1.020631316350773e-06</v>
+        <v>1.505064961548896e-09</v>
       </c>
       <c r="EG5" t="n">
-        <v>3.403961954973056e-06</v>
+        <v>1.385348835647449e-09</v>
       </c>
       <c r="EH5" t="n">
-        <v>1.236190428244299e-06</v>
+        <v>1.059025978022987e-09</v>
       </c>
       <c r="EI5" t="n">
-        <v>8.689995638633263e-07</v>
+        <v>9.74809788445441e-10</v>
       </c>
       <c r="EJ5" t="n">
-        <v>1.094502522391849e-06</v>
+        <v>7.174255078901126e-10</v>
       </c>
       <c r="EK5" t="n">
-        <v>2.287365305164712e-06</v>
+        <v>9.960635649619576e-10</v>
       </c>
       <c r="EL5" t="n">
-        <v>6.828591949670226e-07</v>
+        <v>9.761842445499269e-10</v>
       </c>
       <c r="EM5" t="n">
-        <v>1.332527176600706e-06</v>
+        <v>6.133621388570987e-10</v>
       </c>
       <c r="EN5" t="n">
-        <v>1.368424705106008e-06</v>
+        <v>7.639112259427705e-11</v>
       </c>
       <c r="EO5" t="n">
-        <v>1.964758666872513e-07</v>
+        <v>7.365391629932105e-10</v>
       </c>
       <c r="EP5" t="n">
-        <v>8.220162612815329e-07</v>
+        <v>2.45941622623036e-09</v>
       </c>
       <c r="EQ5" t="n">
-        <v>5.540367510548094e-06</v>
+        <v>2.993528758210573e-10</v>
       </c>
       <c r="ER5" t="n">
-        <v>1.236317217490068e-07</v>
+        <v>7.190405909573983e-11</v>
       </c>
       <c r="ES5" t="n">
-        <v>2.046237796093919e-06</v>
+        <v>1.022263051986272e-09</v>
       </c>
       <c r="ET5" t="n">
-        <v>3.328363391119638e-06</v>
+        <v>5.979256534338617e-10</v>
       </c>
       <c r="EU5" t="n">
-        <v>2.521341457395465e-06</v>
+        <v>4.503853401338631e-10</v>
       </c>
       <c r="EV5" t="n">
-        <v>8.411161616095342e-06</v>
+        <v>1.108090286194852e-09</v>
       </c>
       <c r="EW5" t="n">
-        <v>1.384742972732056e-06</v>
+        <v>1.359219403695988e-09</v>
       </c>
       <c r="EX5" t="n">
-        <v>1.2927478110214e-07</v>
+        <v>2.686420252917543e-10</v>
       </c>
       <c r="EY5" t="n">
-        <v>5.088763828098308e-06</v>
+        <v>3.364268419403516e-09</v>
       </c>
       <c r="EZ5" t="n">
-        <v>3.308644409116823e-06</v>
+        <v>2.809633359301955e-10</v>
       </c>
       <c r="FA5" t="n">
-        <v>2.712128434723127e-06</v>
+        <v>2.309760160912333e-09</v>
       </c>
       <c r="FB5" t="n">
-        <v>7.470001150977623e-07</v>
+        <v>1.450356779120199e-10</v>
       </c>
       <c r="FC5" t="n">
-        <v>2.595528485471732e-06</v>
+        <v>6.952007858274101e-10</v>
       </c>
       <c r="FD5" t="n">
-        <v>1.975165332623874e-06</v>
+        <v>9.17574627390394e-11</v>
       </c>
       <c r="FE5" t="n">
-        <v>3.519601534662797e-07</v>
+        <v>5.556680116036716e-10</v>
       </c>
       <c r="FF5" t="n">
-        <v>3.381683200132102e-06</v>
+        <v>1.321182330205062e-10</v>
       </c>
       <c r="FG5" t="n">
-        <v>3.413984359212918e-06</v>
+        <v>1.625329315579904e-10</v>
       </c>
       <c r="FH5" t="n">
-        <v>6.857109013935769e-08</v>
+        <v>1.383334002902359e-09</v>
       </c>
       <c r="FI5" t="n">
-        <v>5.88973216508748e-06</v>
+        <v>1.098732993476403e-09</v>
       </c>
       <c r="FJ5" t="n">
-        <v>3.020902340722387e-06</v>
+        <v>1.943325944608887e-09</v>
       </c>
       <c r="FK5" t="n">
-        <v>3.725823773947923e-07</v>
+        <v>1.94222624094742e-10</v>
       </c>
       <c r="FL5" t="n">
-        <v>1.763547970767831e-06</v>
+        <v>5.946733105943736e-10</v>
       </c>
       <c r="FM5" t="n">
-        <v>6.434598276428005e-08</v>
+        <v>1.144933259311642e-09</v>
       </c>
       <c r="FN5" t="n">
-        <v>6.020412001817022e-06</v>
+        <v>9.448006821344279e-10</v>
       </c>
       <c r="FO5" t="n">
-        <v>1.830619339671102e-06</v>
+        <v>3.278311400123357e-09</v>
       </c>
       <c r="FP5" t="n">
-        <v>1.687292296992382e-07</v>
+        <v>1.766461421581766e-09</v>
       </c>
       <c r="FQ5" t="n">
-        <v>3.312178023406886e-06</v>
+        <v>5.300651917394816e-09</v>
       </c>
       <c r="FR5" t="n">
-        <v>2.139030925718544e-07</v>
+        <v>2.492958284250335e-09</v>
       </c>
       <c r="FS5" t="n">
-        <v>2.031214734188325e-07</v>
+        <v>1.178073638641308e-09</v>
       </c>
       <c r="FT5" t="n">
-        <v>9.076736205315683e-06</v>
+        <v>2.431044698880669e-09</v>
       </c>
       <c r="FU5" t="n">
-        <v>1.006898060040839e-06</v>
+        <v>1.272122407414145e-09</v>
       </c>
       <c r="FV5" t="n">
-        <v>3.425896238695714e-06</v>
+        <v>1.328311016735029e-09</v>
       </c>
       <c r="FW5" t="n">
-        <v>2.543378741393099e-06</v>
+        <v>7.985039296443119e-10</v>
       </c>
       <c r="FX5" t="n">
-        <v>1.338393531113979e-06</v>
+        <v>1.118624526341705e-09</v>
       </c>
       <c r="FY5" t="n">
-        <v>6.456828486989252e-06</v>
+        <v>1.111020164756837e-09</v>
       </c>
       <c r="FZ5" t="n">
-        <v>2.906960389736923e-06</v>
+        <v>1.079978328988318e-10</v>
       </c>
       <c r="GA5" t="n">
-        <v>7.59328884214483e-08</v>
+        <v>2.168680124370326e-09</v>
       </c>
       <c r="GB5" t="n">
-        <v>5.23617245562491e-07</v>
+        <v>1.077290590068003e-09</v>
       </c>
       <c r="GC5" t="n">
-        <v>1.813706262510095e-06</v>
+        <v>1.077694378182059e-09</v>
       </c>
       <c r="GD5" t="n">
-        <v>4.804464424523758e-06</v>
+        <v>2.157612311037838e-09</v>
       </c>
       <c r="GE5" t="n">
-        <v>9.96144262899179e-06</v>
+        <v>2.380190711193109e-09</v>
       </c>
       <c r="GF5" t="n">
-        <v>1.939776666404214e-06</v>
+        <v>2.758429040738974e-10</v>
       </c>
       <c r="GG5" t="n">
-        <v>3.839195869659306e-06</v>
+        <v>9.766080166784263e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9.013726958073676e-05</v>
+        <v>1.318807852501843e-15</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01256097387522459</v>
+        <v>1.973868405557482e-15</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001039525028318167</v>
+        <v>9.160100165227702e-16</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004663453903049231</v>
+        <v>2.053989252038266e-15</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00351404445245862</v>
+        <v>2.117773374065357e-15</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005614263471215963</v>
+        <v>1.343916979552895e-15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000982457771897316</v>
+        <v>3.353720863776759e-15</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002154237125068903</v>
+        <v>4.858340110456291e-16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005354995373636484</v>
+        <v>6.441322927888411e-17</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001728065079078078</v>
+        <v>9.984345808618494e-16</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01102332584559917</v>
+        <v>1.172038006808118e-15</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001268235209863633</v>
+        <v>4.870865610163814e-16</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003548896405845881</v>
+        <v>3.441362304037977e-15</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002107054460793734</v>
+        <v>1.647549174385999e-15</v>
       </c>
       <c r="O6" t="n">
-        <v>0.006334485020488501</v>
+        <v>2.106561543049686e-16</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0009945172350853682</v>
+        <v>5.691965055551148e-16</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0008365886751562357</v>
+        <v>3.200002595058469e-15</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0006165446247905493</v>
+        <v>6.265585296552417e-16</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0006035799742676318</v>
+        <v>2.041994630230435e-15</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001325643388554454</v>
+        <v>1.546434510428399e-15</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0002504688745830208</v>
+        <v>6.892178448679378e-16</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0009538698941469193</v>
+        <v>1.010660230906044e-15</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001412652200087905</v>
+        <v>2.795408308077388e-16</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0003002127632498741</v>
+        <v>8.003352797183419e-16</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0004931119037792087</v>
+        <v>3.293912343827165e-16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001587779494002461</v>
+        <v>7.088131050697187e-16</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0007569309673272073</v>
+        <v>2.936596524286063e-15</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0005640265881083906</v>
+        <v>1.674972501328068e-15</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0007471864810213447</v>
+        <v>6.904631421190792e-16</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0007781313615851104</v>
+        <v>1.563305818550929e-15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.000213621009606868</v>
+        <v>4.246932670886824e-16</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0006346488371491432</v>
+        <v>1.078148639769715e-15</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0005647915531881154</v>
+        <v>1.526247491833842e-15</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0002594200777821243</v>
+        <v>2.292293236720995e-16</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0003179762279614806</v>
+        <v>1.276316021186358e-15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0008298620814457536</v>
+        <v>7.752533636007212e-16</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.001377889420837164</v>
+        <v>1.685445004929683e-15</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.001393182552419603</v>
+        <v>3.08976866851161e-16</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0006667133420705795</v>
+        <v>1.315099965775238e-15</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0001759572332957759</v>
+        <v>7.110222199357172e-16</v>
       </c>
       <c r="AO6" t="n">
-        <v>2.566753573773894e-05</v>
+        <v>2.149898369139397e-15</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0008777244365774095</v>
+        <v>1.038061958507958e-15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0002603985776659101</v>
+        <v>1.246822439842081e-15</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0004838047898374498</v>
+        <v>2.970159146029831e-15</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0009091776446439326</v>
+        <v>8.609934266535905e-16</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0007070614956319332</v>
+        <v>4.219478215483944e-16</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.009004761464893818</v>
+        <v>4.826799885753212e-15</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.0008554582018405199</v>
+        <v>2.145231005841789e-15</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.001133560319431126</v>
+        <v>2.10640179792979e-16</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.790879266802222e-05</v>
+        <v>3.430259396165368e-15</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.00223515322431922</v>
+        <v>6.864872753437859e-16</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.001135904807597399</v>
+        <v>9.453581199583556e-16</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0008395748445764184</v>
+        <v>2.836915569470809e-16</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.001270067412406206</v>
+        <v>5.364993926647635e-16</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0005439851665869355</v>
+        <v>5.31323142560357e-15</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.001981978537514806</v>
+        <v>3.866854058498124e-15</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.002316054189577699</v>
+        <v>1.205726307065434e-15</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.077987978234887e-05</v>
+        <v>2.919852588742977e-15</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.003957285545766354</v>
+        <v>5.18244657393219e-15</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.003207386005669832</v>
+        <v>8.815602336458722e-16</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0008225332130677998</v>
+        <v>1.587712225893114e-15</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.001433155499398708</v>
+        <v>1.29384176813976e-15</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0002088983310386539</v>
+        <v>2.73243214960286e-15</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.001320457085967064</v>
+        <v>6.939880167895188e-16</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.001633308362215757</v>
+        <v>3.962347070663916e-16</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.001094800652936101</v>
+        <v>1.621065524619791e-15</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0004140171804465353</v>
+        <v>7.886672420512363e-16</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0008396682096645236</v>
+        <v>2.356944879304752e-16</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.001222976366989315</v>
+        <v>3.4067596317141e-16</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0005905438447371125</v>
+        <v>3.191641109319648e-15</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0007665751618333161</v>
+        <v>3.842612875520213e-16</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0005265054642222822</v>
+        <v>1.046457749081142e-15</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0005133567610755563</v>
+        <v>3.382432104315127e-15</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.004671348258852959</v>
+        <v>3.436047807568667e-15</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.001339876558631659</v>
+        <v>3.572489039382692e-16</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0005780662759207189</v>
+        <v>2.50116928511286e-15</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.001178841572255e-05</v>
+        <v>3.974036390033822e-16</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0004250835627317429</v>
+        <v>6.678667515409476e-17</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.000311749055981636</v>
+        <v>1.458914619395112e-15</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.000213432518648915</v>
+        <v>2.240095625439837e-16</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0009703585528768599</v>
+        <v>8.44634891101505e-16</v>
       </c>
       <c r="CD6" t="n">
-        <v>7.966451084939763e-05</v>
+        <v>6.073685747187219e-16</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.002089135348796844</v>
+        <v>3.58275534340121e-16</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.000805527379270643</v>
+        <v>4.289008503146089e-16</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0009429635829292238</v>
+        <v>6.053453306450866e-18</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0001768506917869672</v>
+        <v>1.521610912889911e-16</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.0008743289508856833</v>
+        <v>3.453693462623664e-16</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.00107309187296778</v>
+        <v>6.941270890115461e-16</v>
       </c>
       <c r="CK6" t="n">
-        <v>2.267025774926879e-05</v>
+        <v>1.747048731801643e-16</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0005729999393224716</v>
+        <v>1.001558544250442e-15</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.002707142382860184</v>
+        <v>7.067436447608989e-16</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0009314591879956424</v>
+        <v>3.51098714175286e-15</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0001247361360583454</v>
+        <v>7.055366757506207e-16</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.002253187820315361</v>
+        <v>2.25063938568814e-15</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.001184446620754898</v>
+        <v>8.478482694055918e-16</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0001632526109460741</v>
+        <v>7.744818754044501e-16</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.002790016587823629</v>
+        <v>5.522281698084773e-15</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.002499419962987304</v>
+        <v>5.315497026979238e-17</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0006868792115710676</v>
+        <v>2.304000555541029e-15</v>
       </c>
       <c r="CV6" t="n">
-        <v>7.646750600542873e-05</v>
+        <v>2.929213043963966e-16</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.001852212240919471</v>
+        <v>4.821715464608199e-16</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.0009202277869917452</v>
+        <v>8.694675677743961e-16</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.001384862815029919</v>
+        <v>3.332623602401259e-16</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0003236481861677021</v>
+        <v>2.632034181397755e-16</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.001074574654921889</v>
+        <v>5.461159694731784e-16</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0009370375191792846</v>
+        <v>1.623185614999544e-17</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.0004004203656222671</v>
+        <v>8.558529425153818e-17</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.0002639912418089807</v>
+        <v>9.322575907587654e-16</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.00127571658231318</v>
+        <v>1.413185798732134e-16</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.00144882476888597</v>
+        <v>4.61984686684941e-15</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.0001943015959113836</v>
+        <v>2.722478030164964e-15</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.003096319502219558</v>
+        <v>8.768042495261577e-16</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.002543893875554204</v>
+        <v>4.560179219066857e-16</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.001107907854020596</v>
+        <v>1.442602670655125e-15</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.000868643750436604</v>
+        <v>1.460553310510693e-15</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0005522655555978417</v>
+        <v>2.676005249876501e-16</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.001583814504556358</v>
+        <v>6.700755884742602e-16</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.000488448713440448</v>
+        <v>1.761611213398415e-16</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.00020134802616667</v>
+        <v>7.063907496592491e-16</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.00169972877483815</v>
+        <v>2.687671275840357e-17</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.703199814073741e-05</v>
+        <v>7.620494963815659e-16</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.001215803320519626</v>
+        <v>9.837821814237709e-16</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.001175732119008899</v>
+        <v>2.059338688616651e-15</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.0006637029000557959</v>
+        <v>1.591397560367499e-16</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0002770522842183709</v>
+        <v>1.044706296704457e-15</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.001194910611957312</v>
+        <v>2.099060298678141e-15</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.0002573571400716901</v>
+        <v>2.714894120671722e-16</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0009359890827909112</v>
+        <v>2.652909308382837e-16</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0008823351236060262</v>
+        <v>1.997137035893268e-15</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0006202084477990866</v>
+        <v>1.668710704386372e-15</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0002639666781760752</v>
+        <v>1.958365796798597e-15</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.001297924667596817</v>
+        <v>8.545947280117947e-16</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.000313272699713707</v>
+        <v>3.506640168667551e-15</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.001217277022078633</v>
+        <v>1.115525239116732e-15</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0003126142255496234</v>
+        <v>2.00023908230435e-15</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0003774217329919338</v>
+        <v>5.512945700940136e-17</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.002133678644895554</v>
+        <v>5.318928569206802e-16</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.0004717270494438708</v>
+        <v>4.203702491539129e-16</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0002938679826911539</v>
+        <v>5.481891884907017e-16</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0001214069488923997</v>
+        <v>3.123259292454861e-17</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.0004279481363482773</v>
+        <v>4.657105728616759e-16</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.001043744035996497</v>
+        <v>1.616055960011493e-15</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.0004190289182588458</v>
+        <v>5.981394625441166e-16</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.000119660617201589</v>
+        <v>2.284298569187894e-15</v>
       </c>
       <c r="EO6" t="n">
-        <v>5.26494113728404e-05</v>
+        <v>6.990475034021463e-16</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.001280829077586532</v>
+        <v>1.741193219507054e-16</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.001027579652145505</v>
+        <v>2.260680643640484e-17</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.000538854394108057</v>
+        <v>5.559217522661862e-16</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0002597762504592538</v>
+        <v>9.17001362708413e-16</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.001395156956277788</v>
+        <v>8.457524981358479e-16</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0006688730791211128</v>
+        <v>1.478105844881052e-15</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.001742302672937512</v>
+        <v>1.557535088960403e-15</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.001426349976100028</v>
+        <v>1.148773346939272e-16</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.0003830599598586559</v>
+        <v>6.484230970018354e-16</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.001651872647926211</v>
+        <v>5.186075686594701e-16</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0004835054569412023</v>
+        <v>7.226983044158217e-16</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0008736643940210342</v>
+        <v>8.515089869849473e-16</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0002300143096363172</v>
+        <v>2.354915706000485e-16</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.0009969657985493541</v>
+        <v>5.740840974190089e-16</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.001170151401311159</v>
+        <v>2.185782549372911e-16</v>
       </c>
       <c r="FE6" t="n">
-        <v>1.2004993550363e-05</v>
+        <v>5.026840109955793e-17</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.0005925537552684546</v>
+        <v>1.007512550594929e-15</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0002189650840591639</v>
+        <v>3.081711796996446e-16</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0002762858930509537</v>
+        <v>1.262567829419473e-15</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.001878457143902779</v>
+        <v>4.437713607366054e-16</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.003197936341166496</v>
+        <v>1.447357701862774e-15</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0005341659998521209</v>
+        <v>8.930930107392131e-17</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.001392462407238781</v>
+        <v>2.677542879373564e-16</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0003571462875697762</v>
+        <v>1.319770823083753e-15</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0003182666259817779</v>
+        <v>2.705977775412891e-16</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.001265189726836979</v>
+        <v>3.689592509010901e-15</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.001244613784365356</v>
+        <v>4.027835211222646e-15</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.002748003927990794</v>
+        <v>1.640289625571997e-16</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0007900593336671591</v>
+        <v>1.949629710738853e-15</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.001138201914727688</v>
+        <v>4.127262903186671e-15</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001563087454997003</v>
+        <v>7.010156056309154e-15</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0006692001479677856</v>
+        <v>4.437296973035124e-16</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0009899104479700327</v>
+        <v>1.258810285386335e-15</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.00121460179798305</v>
+        <v>6.412609040372082e-15</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.0002019747334998101</v>
+        <v>6.696986588127321e-16</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.002112170215696096</v>
+        <v>2.232877951817164e-15</v>
       </c>
       <c r="FZ6" t="n">
-        <v>8.275494474219158e-05</v>
+        <v>9.780017109543523e-17</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0005286425584927201</v>
+        <v>3.277332044461577e-15</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0001677376276347786</v>
+        <v>1.106540760645205e-15</v>
       </c>
       <c r="GC6" t="n">
-        <v>8.175476978067309e-06</v>
+        <v>5.575890307437379e-16</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0002207256620749831</v>
+        <v>8.834610549888496e-17</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.003126385621726513</v>
+        <v>1.330260690860787e-15</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0004109784495085478</v>
+        <v>2.792519184573422e-15</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0007072346052154899</v>
+        <v>7.402013138285457e-17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.602014435775345e-06</v>
+        <v>7.845627481017914e-10</v>
       </c>
       <c r="B7" t="n">
-        <v>1.194737524201628e-05</v>
+        <v>3.647858903832457e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.131290218836511e-06</v>
+        <v>4.85764095614627e-10</v>
       </c>
       <c r="D7" t="n">
-        <v>7.160921086324379e-06</v>
+        <v>1.920075876071792e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>3.494605152809527e-06</v>
+        <v>1.666897869734285e-10</v>
       </c>
       <c r="F7" t="n">
-        <v>3.078115014432115e-06</v>
+        <v>2.393976572534484e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>7.077207442307554e-08</v>
+        <v>5.204602304687e-10</v>
       </c>
       <c r="H7" t="n">
-        <v>1.277175556424481e-07</v>
+        <v>8.044902521930908e-10</v>
       </c>
       <c r="I7" t="n">
-        <v>8.40504071675241e-07</v>
+        <v>3.936974635188051e-10</v>
       </c>
       <c r="J7" t="n">
-        <v>3.124618160654791e-06</v>
+        <v>4.06697647781229e-10</v>
       </c>
       <c r="K7" t="n">
-        <v>9.652039807406254e-06</v>
+        <v>3.797429926066798e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>6.297871664173726e-07</v>
+        <v>1.233611879314367e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>5.152880930836545e-06</v>
+        <v>3.323751496253635e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.548380391293904e-06</v>
+        <v>1.357744028318564e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>5.565678748098435e-06</v>
+        <v>2.623982142679893e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6090253893708e-06</v>
+        <v>2.815376265452585e-10</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.895956984299119e-06</v>
+        <v>5.6673898907178e-10</v>
       </c>
       <c r="R7" t="n">
-        <v>4.14739076859405e-07</v>
+        <v>1.923423087468734e-10</v>
       </c>
       <c r="S7" t="n">
-        <v>2.48491915044724e-07</v>
+        <v>3.028748918332269e-10</v>
       </c>
       <c r="T7" t="n">
-        <v>1.809165496524656e-06</v>
+        <v>3.449566188251652e-10</v>
       </c>
       <c r="U7" t="n">
-        <v>2.892702468670905e-07</v>
+        <v>3.72656017155748e-10</v>
       </c>
       <c r="V7" t="n">
-        <v>1.182049231829296e-06</v>
+        <v>1.820912309824507e-10</v>
       </c>
       <c r="W7" t="n">
-        <v>5.361468424780469e-07</v>
+        <v>9.25444831878508e-10</v>
       </c>
       <c r="X7" t="n">
-        <v>1.285684675167431e-06</v>
+        <v>5.103229505643014e-10</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.466042135689349e-06</v>
+        <v>1.053570786169189e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.384536062687403e-06</v>
+        <v>7.622102948801057e-10</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.672173198130622e-06</v>
+        <v>3.136630954969633e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.583796559629263e-07</v>
+        <v>3.936796444392598e-10</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.248180201533614e-08</v>
+        <v>7.012027070096849e-10</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.360809728292224e-07</v>
+        <v>6.700684451743655e-11</v>
       </c>
       <c r="AE7" t="n">
-        <v>5.094742618894088e-07</v>
+        <v>8.868598633249292e-10</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.98814447571749e-07</v>
+        <v>1.812023864289358e-10</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.834431580202363e-08</v>
+        <v>1.044514252868112e-09</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.756819175279816e-07</v>
+        <v>2.084717121153545e-10</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.081848032910784e-07</v>
+        <v>1.34846900312624e-09</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6.707929856020201e-07</v>
+        <v>5.891119536638456e-11</v>
       </c>
       <c r="AK7" t="n">
-        <v>7.277019449247746e-07</v>
+        <v>4.728500369033384e-10</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.630515839678992e-06</v>
+        <v>5.327881469341378e-10</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.936656867153943e-07</v>
+        <v>9.435321413064912e-10</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.115158738684841e-07</v>
+        <v>1.016812523069177e-09</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.655289392805571e-07</v>
+        <v>4.310204415602925e-10</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.857271397260774e-08</v>
+        <v>3.056667141621006e-10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.768696039216593e-07</v>
+        <v>3.174380203141425e-11</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.967140192022271e-08</v>
+        <v>1.908424251961804e-10</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.963690672520897e-07</v>
+        <v>1.898516344134293e-10</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.012453574541723e-07</v>
+        <v>5.244298328932473e-10</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.552760507678613e-06</v>
+        <v>2.514710883971816e-09</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.227356609793787e-07</v>
+        <v>1.159284446217157e-09</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.540782816140563e-06</v>
+        <v>3.701579320836146e-10</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.27782777781249e-06</v>
+        <v>3.093753697669399e-09</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.813113037016592e-07</v>
+        <v>2.029449275298134e-09</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9.050166340784926e-07</v>
+        <v>3.492982847408399e-10</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.161539545246342e-07</v>
+        <v>5.099311528589112e-10</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.753507035573421e-06</v>
+        <v>2.589297942723334e-10</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.050374956132146e-07</v>
+        <v>2.414619892920911e-11</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.574043946879101e-06</v>
+        <v>1.157170026466758e-09</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.476670372037916e-06</v>
+        <v>2.418315547814132e-10</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.227090365318873e-06</v>
+        <v>6.96173896308494e-10</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.327578613403603e-06</v>
+        <v>2.416360667112372e-09</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.450118017804925e-06</v>
+        <v>1.117358011670788e-10</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.374618131601892e-07</v>
+        <v>7.550743363893275e-10</v>
       </c>
       <c r="BJ7" t="n">
-        <v>2.216432221757714e-06</v>
+        <v>1.496494150821093e-09</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.633866516698617e-07</v>
+        <v>3.879813414986444e-10</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.137030949394102e-06</v>
+        <v>1.612236177894744e-10</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.645127326810325e-06</v>
+        <v>4.257359742521061e-10</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.964178181879106e-06</v>
+        <v>3.292826428191731e-11</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.676530274608012e-07</v>
+        <v>2.194697201751694e-10</v>
       </c>
       <c r="BP7" t="n">
-        <v>9.431934131498565e-07</v>
+        <v>1.012906092334731e-09</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.729433958847949e-07</v>
+        <v>6.621144604812557e-11</v>
       </c>
       <c r="BR7" t="n">
-        <v>2.147996553958365e-07</v>
+        <v>1.179082526059361e-11</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.775457292296778e-07</v>
+        <v>4.981767220968436e-10</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.473292467670035e-08</v>
+        <v>1.552035999718981e-10</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.669332843652228e-07</v>
+        <v>3.011735583147157e-10</v>
       </c>
       <c r="BV7" t="n">
-        <v>4.201012416160665e-06</v>
+        <v>7.725233786004537e-10</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.492721708018507e-06</v>
+        <v>4.730705827071802e-10</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.877327804322704e-06</v>
+        <v>4.699831079868488e-10</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.695487412689545e-07</v>
+        <v>5.510810696662816e-10</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.425327458397078e-07</v>
+        <v>1.150459727483621e-09</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.460638259231928e-06</v>
+        <v>1.025805773657851e-09</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.237191492644342e-07</v>
+        <v>2.439956847677394e-10</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.343963276667637e-06</v>
+        <v>5.590332884108928e-12</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.065801598088001e-07</v>
+        <v>6.695754367624929e-11</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.948969611476059e-06</v>
+        <v>1.250230474703073e-09</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.344979068562679e-06</v>
+        <v>4.876990825075644e-11</v>
       </c>
       <c r="CG7" t="n">
-        <v>6.15830572314735e-07</v>
+        <v>6.412242403719404e-10</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.781367870989925e-07</v>
+        <v>2.791935571622162e-10</v>
       </c>
       <c r="CI7" t="n">
-        <v>7.643805020052241e-07</v>
+        <v>5.288671722780691e-10</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.248575441399225e-07</v>
+        <v>3.303726181513866e-10</v>
       </c>
       <c r="CK7" t="n">
-        <v>9.394020139552595e-08</v>
+        <v>6.539735419863746e-11</v>
       </c>
       <c r="CL7" t="n">
-        <v>9.758877013155143e-07</v>
+        <v>2.088325623539333e-10</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.647248382141697e-06</v>
+        <v>1.922659254027792e-10</v>
       </c>
       <c r="CN7" t="n">
-        <v>6.587030156879337e-07</v>
+        <v>1.464528165406875e-09</v>
       </c>
       <c r="CO7" t="n">
-        <v>4.658832608583907e-07</v>
+        <v>1.567094343180031e-09</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.625412323846831e-06</v>
+        <v>1.268978699897616e-09</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.532278474769555e-06</v>
+        <v>2.367710472128692e-10</v>
       </c>
       <c r="CR7" t="n">
-        <v>6.180695208968245e-07</v>
+        <v>1.544366717842749e-11</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.195641854996211e-06</v>
+        <v>8.156007813564514e-11</v>
       </c>
       <c r="CT7" t="n">
-        <v>1.598638505129202e-06</v>
+        <v>9.545891854756405e-10</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.223057353172408e-07</v>
+        <v>4.69177807715937e-10</v>
       </c>
       <c r="CV7" t="n">
-        <v>6.618940062708134e-08</v>
+        <v>1.552697692641658e-10</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.668552386036026e-06</v>
+        <v>1.197839050171012e-09</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.321963850386965e-06</v>
+        <v>2.394597298227552e-10</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.32908303385193e-06</v>
+        <v>8.207848289920605e-10</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.524227511457866e-07</v>
+        <v>4.062566394402722e-10</v>
       </c>
       <c r="DA7" t="n">
-        <v>8.489110996379168e-07</v>
+        <v>6.244690320400537e-10</v>
       </c>
       <c r="DB7" t="n">
-        <v>4.07125241963513e-07</v>
+        <v>3.878153354008873e-10</v>
       </c>
       <c r="DC7" t="n">
-        <v>3.64306856681651e-07</v>
+        <v>5.867180352669976e-11</v>
       </c>
       <c r="DD7" t="n">
-        <v>6.132560770311102e-07</v>
+        <v>1.49340345645399e-10</v>
       </c>
       <c r="DE7" t="n">
-        <v>6.681055424451188e-07</v>
+        <v>4.100477180024598e-10</v>
       </c>
       <c r="DF7" t="n">
-        <v>6.955502271921432e-07</v>
+        <v>3.156401529036401e-10</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.014395249716472e-06</v>
+        <v>4.425368127503049e-10</v>
       </c>
       <c r="DH7" t="n">
-        <v>6.03029639023589e-06</v>
+        <v>6.021582121817914e-10</v>
       </c>
       <c r="DI7" t="n">
-        <v>1.332835154244094e-06</v>
+        <v>1.24831422976257e-10</v>
       </c>
       <c r="DJ7" t="n">
-        <v>8.217000981858291e-07</v>
+        <v>1.324043097383765e-09</v>
       </c>
       <c r="DK7" t="n">
-        <v>8.838637768349145e-07</v>
+        <v>5.534837033138729e-10</v>
       </c>
       <c r="DL7" t="n">
-        <v>1.646802047616802e-06</v>
+        <v>1.350918377163168e-09</v>
       </c>
       <c r="DM7" t="n">
-        <v>7.580109695481951e-08</v>
+        <v>6.894873005869329e-10</v>
       </c>
       <c r="DN7" t="n">
-        <v>3.329180913169694e-07</v>
+        <v>6.159517340620368e-13</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.090201521947165e-06</v>
+        <v>3.863184216967852e-10</v>
       </c>
       <c r="DP7" t="n">
-        <v>1.585656377756095e-06</v>
+        <v>3.304299611706085e-10</v>
       </c>
       <c r="DQ7" t="n">
-        <v>5.192714525037445e-07</v>
+        <v>5.801478186739928e-10</v>
       </c>
       <c r="DR7" t="n">
-        <v>2.075677656421249e-07</v>
+        <v>5.673169226061425e-11</v>
       </c>
       <c r="DS7" t="n">
-        <v>6.35736341791926e-07</v>
+        <v>8.375546090011454e-11</v>
       </c>
       <c r="DT7" t="n">
-        <v>3.610402359299769e-07</v>
+        <v>8.073139934339224e-10</v>
       </c>
       <c r="DU7" t="n">
-        <v>3.334433529289527e-08</v>
+        <v>9.279323420763319e-10</v>
       </c>
       <c r="DV7" t="n">
-        <v>2.012502136494732e-06</v>
+        <v>1.250692466259196e-10</v>
       </c>
       <c r="DW7" t="n">
-        <v>4.113218778911687e-07</v>
+        <v>2.877243165944066e-10</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.559754196023277e-06</v>
+        <v>9.978946557964719e-10</v>
       </c>
       <c r="DY7" t="n">
-        <v>1.444620238544303e-06</v>
+        <v>7.323219253230207e-10</v>
       </c>
       <c r="DZ7" t="n">
-        <v>1.495034638310244e-07</v>
+        <v>8.180947030922425e-10</v>
       </c>
       <c r="EA7" t="n">
-        <v>6.618822112613998e-07</v>
+        <v>9.314418125683233e-10</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.634371642467158e-06</v>
+        <v>7.557074965802713e-10</v>
       </c>
       <c r="EC7" t="n">
-        <v>8.038487635531055e-07</v>
+        <v>3.689080707580672e-10</v>
       </c>
       <c r="ED7" t="n">
-        <v>4.342063277817942e-07</v>
+        <v>1.523858483842844e-09</v>
       </c>
       <c r="EE7" t="n">
-        <v>2.504225449229125e-07</v>
+        <v>7.183555417178411e-10</v>
       </c>
       <c r="EF7" t="n">
-        <v>1.220497694021105e-07</v>
+        <v>5.258334878632809e-10</v>
       </c>
       <c r="EG7" t="n">
-        <v>1.114193651119422e-06</v>
+        <v>3.33796157381272e-10</v>
       </c>
       <c r="EH7" t="n">
-        <v>4.940066560266132e-07</v>
+        <v>2.586189318254384e-10</v>
       </c>
       <c r="EI7" t="n">
-        <v>2.947373900497041e-07</v>
+        <v>2.646206587186839e-10</v>
       </c>
       <c r="EJ7" t="n">
-        <v>4.030004276955879e-07</v>
+        <v>2.917053820716831e-10</v>
       </c>
       <c r="EK7" t="n">
-        <v>6.661402380814252e-07</v>
+        <v>3.936843906426901e-10</v>
       </c>
       <c r="EL7" t="n">
-        <v>2.859388246179151e-07</v>
+        <v>6.741499580797949e-10</v>
       </c>
       <c r="EM7" t="n">
-        <v>5.859274665453995e-07</v>
+        <v>1.234817109674324e-10</v>
       </c>
       <c r="EN7" t="n">
-        <v>3.173353491092712e-07</v>
+        <v>2.486517935995636e-11</v>
       </c>
       <c r="EO7" t="n">
-        <v>1.823367199449422e-07</v>
+        <v>2.684512334649725e-10</v>
       </c>
       <c r="EP7" t="n">
-        <v>1.88386763966264e-07</v>
+        <v>7.214909780728362e-10</v>
       </c>
       <c r="EQ7" t="n">
-        <v>1.983496076718438e-06</v>
+        <v>6.923865647490146e-11</v>
       </c>
       <c r="ER7" t="n">
-        <v>2.71527881068323e-07</v>
+        <v>1.39137451560245e-10</v>
       </c>
       <c r="ES7" t="n">
-        <v>4.436485312453442e-07</v>
+        <v>2.644044982957894e-10</v>
       </c>
       <c r="ET7" t="n">
-        <v>8.472368904222094e-07</v>
+        <v>2.478850458231818e-10</v>
       </c>
       <c r="EU7" t="n">
-        <v>8.520590313310095e-07</v>
+        <v>1.721844888891155e-12</v>
       </c>
       <c r="EV7" t="n">
-        <v>2.45420642386307e-06</v>
+        <v>5.954567394717003e-10</v>
       </c>
       <c r="EW7" t="n">
-        <v>3.243879405090411e-07</v>
+        <v>7.915624822274481e-10</v>
       </c>
       <c r="EX7" t="n">
-        <v>8.400786555284867e-08</v>
+        <v>4.259228386649383e-11</v>
       </c>
       <c r="EY7" t="n">
-        <v>1.601824010322161e-06</v>
+        <v>1.228436907751984e-09</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1.125157041315106e-06</v>
+        <v>1.644249875143444e-10</v>
       </c>
       <c r="FA7" t="n">
-        <v>9.252152608496544e-07</v>
+        <v>8.874302404038303e-10</v>
       </c>
       <c r="FB7" t="n">
-        <v>3.380419144605185e-08</v>
+        <v>1.327948168095006e-10</v>
       </c>
       <c r="FC7" t="n">
-        <v>8.114191700769879e-07</v>
+        <v>3.440132068099899e-10</v>
       </c>
       <c r="FD7" t="n">
-        <v>6.942127583897673e-07</v>
+        <v>2.215772010316641e-10</v>
       </c>
       <c r="FE7" t="n">
-        <v>9.275759538240891e-08</v>
+        <v>2.330983184251068e-10</v>
       </c>
       <c r="FF7" t="n">
-        <v>9.471017392570502e-07</v>
+        <v>1.151775619323558e-10</v>
       </c>
       <c r="FG7" t="n">
-        <v>1.164081368187908e-06</v>
+        <v>1.438448943291704e-10</v>
       </c>
       <c r="FH7" t="n">
-        <v>1.806978673357662e-07</v>
+        <v>4.582121904128655e-10</v>
       </c>
       <c r="FI7" t="n">
-        <v>1.871223503258079e-06</v>
+        <v>5.07874686750398e-10</v>
       </c>
       <c r="FJ7" t="n">
-        <v>1.144611701420217e-06</v>
+        <v>6.555753162551525e-10</v>
       </c>
       <c r="FK7" t="n">
-        <v>2.030495238614094e-07</v>
+        <v>1.417229805733555e-10</v>
       </c>
       <c r="FL7" t="n">
-        <v>6.596196158170642e-07</v>
+        <v>1.6844439038044e-11</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.553097916939805e-08</v>
+        <v>4.966987376953114e-10</v>
       </c>
       <c r="FN7" t="n">
-        <v>1.833473561418941e-06</v>
+        <v>4.625559657522871e-10</v>
       </c>
       <c r="FO7" t="n">
-        <v>5.32445653789182e-07</v>
+        <v>1.509774749663961e-09</v>
       </c>
       <c r="FP7" t="n">
-        <v>1.044273858497036e-07</v>
+        <v>1.313441022610107e-09</v>
       </c>
       <c r="FQ7" t="n">
-        <v>9.578283197697601e-07</v>
+        <v>1.922476622340241e-09</v>
       </c>
       <c r="FR7" t="n">
-        <v>1.151193131931905e-07</v>
+        <v>1.178754427400008e-09</v>
       </c>
       <c r="FS7" t="n">
-        <v>3.268236170583805e-08</v>
+        <v>3.706304152473194e-10</v>
       </c>
       <c r="FT7" t="n">
-        <v>3.170582203892991e-06</v>
+        <v>1.300813234905718e-09</v>
       </c>
       <c r="FU7" t="n">
-        <v>6.315040081972256e-07</v>
+        <v>5.593477347964892e-10</v>
       </c>
       <c r="FV7" t="n">
-        <v>1.504379383732157e-06</v>
+        <v>4.171998579938219e-10</v>
       </c>
       <c r="FW7" t="n">
-        <v>1.175371949102555e-06</v>
+        <v>4.372093798110654e-10</v>
       </c>
       <c r="FX7" t="n">
-        <v>4.99230338846246e-07</v>
+        <v>3.878028176362847e-10</v>
       </c>
       <c r="FY7" t="n">
-        <v>2.392982878518524e-06</v>
+        <v>4.228329908428918e-10</v>
       </c>
       <c r="FZ7" t="n">
-        <v>9.328149417342502e-07</v>
+        <v>2.508417640267879e-10</v>
       </c>
       <c r="GA7" t="n">
-        <v>1.885831437675733e-07</v>
+        <v>1.141118421976728e-09</v>
       </c>
       <c r="GB7" t="n">
-        <v>3.812477586961904e-07</v>
+        <v>2.825126799166355e-10</v>
       </c>
       <c r="GC7" t="n">
-        <v>1.312355266236409e-06</v>
+        <v>8.395527606452902e-10</v>
       </c>
       <c r="GD7" t="n">
-        <v>1.629201278774417e-06</v>
+        <v>9.591198946168333e-10</v>
       </c>
       <c r="GE7" t="n">
-        <v>3.220332018827321e-06</v>
+        <v>8.230707226886125e-10</v>
       </c>
       <c r="GF7" t="n">
-        <v>2.738964042237058e-07</v>
+        <v>3.143159343910185e-10</v>
       </c>
       <c r="GG7" t="n">
-        <v>1.097911763281445e-06</v>
+        <v>4.869077918634446e-10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.005433950107544661</v>
+        <v>0.000384269340429455</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02746078185737133</v>
+        <v>0.003838240634649992</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004602905362844467</v>
+        <v>0.002214155625551939</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008615244179964066</v>
+        <v>0.002101565478369594</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008930252864956856</v>
+        <v>0.002271173056215048</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02445491217076778</v>
+        <v>0.005148619413375854</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0006393142975866795</v>
+        <v>0.0003364127478562295</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01089558750391006</v>
+        <v>0.001453207689337432</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00321120535954833</v>
+        <v>0.0007884521619416773</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008420387282967567</v>
+        <v>0.001103917136788368</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0282837375998497</v>
+        <v>0.003407158656045794</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003055132459849119</v>
+        <v>0.002607274567708373</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007787878625094891</v>
+        <v>0.002905341796576977</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001587530132383108</v>
+        <v>0.0006044321926310658</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02424885332584381</v>
+        <v>0.005298169329762459</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003641699906438589</v>
+        <v>0.0006741072866134346</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005352461710572243</v>
+        <v>0.0006331935292109847</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002912956289947033</v>
+        <v>0.0006297557847574353</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001219976576976478</v>
+        <v>0.0007580239325761795</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002084622625261545</v>
+        <v>0.0004892515717074275</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003081513103097677</v>
+        <v>0.0007500643841922283</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001801502308808267</v>
+        <v>0.0005258015589788556</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0006251753075048327</v>
+        <v>0.0002340620703762397</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0007418981986120343</v>
+        <v>0.0007718398119322956</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001289824489504099</v>
+        <v>0.001058703288435936</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002738614566624165</v>
+        <v>0.0004734044778160751</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002277143066748977</v>
+        <v>0.0007354025146923959</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001234531169757247</v>
+        <v>0.0004472669679671526</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.002422815188765526</v>
+        <v>0.0004951455630362034</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.004389309324324131</v>
+        <v>0.0009641358046792448</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.002859393833205104</v>
+        <v>0.0013256297679618</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001134267309680581</v>
+        <v>0.0001530082809040323</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.002195168053731322</v>
+        <v>0.001435806159861386</v>
       </c>
       <c r="AH8" t="n">
-        <v>9.222142398357391e-05</v>
+        <v>0.001044821459800005</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.004709746222943068</v>
+        <v>0.002337649930268526</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001373305916786194</v>
+        <v>0.0001905592507682741</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.004699526354670525</v>
+        <v>0.0008868654840625823</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.00406821072101593</v>
+        <v>0.000769084959756583</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.804883453994989e-05</v>
+        <v>0.0003212039882782847</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001302819116972387</v>
+        <v>0.001079724752344191</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0002626638161018491</v>
+        <v>0.0003764164575841278</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.003172358497977257</v>
+        <v>0.0009776062797755003</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001581388642080128</v>
+        <v>4.111555244890042e-05</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.001935402629896998</v>
+        <v>0.001471708877943456</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.004371871240437031</v>
+        <v>6.130115798441693e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001438580802641809</v>
+        <v>0.0004282438312657177</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.01712122373282909</v>
+        <v>0.003572022076696157</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.00439623836427927</v>
+        <v>0.002001137472689152</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0006404116284102201</v>
+        <v>0.0007977983914315701</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.002023905981332064</v>
+        <v>0.000937816861551255</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0119746895506978</v>
+        <v>0.00343166571110487</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002531966660171747</v>
+        <v>2.352890078327619e-05</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.003855749731883407</v>
+        <v>0.0006837035180069506</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.00429226690903306</v>
+        <v>0.001137821702286601</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.002031905110925436</v>
+        <v>0.0003643327509053051</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.008445153012871742</v>
+        <v>0.0006109195528551936</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.008855900727212429</v>
+        <v>0.000609462964348495</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.002192552667111158</v>
+        <v>0.0003425891627557576</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.002159898169338703</v>
+        <v>0.001968213124200702</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.006726678926497698</v>
+        <v>0.000145227910252288</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0009681695373728871</v>
+        <v>0.0002952250943053514</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002634804230183363</v>
+        <v>0.0007992604514583945</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0008416327182203531</v>
+        <v>0.001180818071588874</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.001723877619951963</v>
+        <v>0.0001361643371637911</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.00373336486518383</v>
+        <v>0.0008438534568995237</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.003364337608218193</v>
+        <v>0.0003890788648277521</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.002702378900721669</v>
+        <v>0.0006589015247300267</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001767892739735544</v>
+        <v>0.0002231048711109906</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0006911510718055069</v>
+        <v>0.001198899233713746</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.003715859726071358</v>
+        <v>6.323325214907527e-05</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0001381882466375828</v>
+        <v>6.856043910374865e-05</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.005388086196035147</v>
+        <v>0.0006941911997273564</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0006664748652838171</v>
+        <v>0.0005833620089106262</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.008374730125069618</v>
+        <v>0.002608022652566433</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.00240633636713028</v>
+        <v>0.0006166412495076656</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.001115610357373953</v>
+        <v>0.00117488345131278</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0008491710177622736</v>
+        <v>0.0002303497167304158</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.007232677657157183</v>
+        <v>0.002215664135292172</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0006553304265253246</v>
+        <v>0.001170734758488834</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.003006689017638564</v>
+        <v>0.0002161024895031005</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.002153936307877302</v>
+        <v>0.0003046862257178873</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0002781496150419116</v>
+        <v>9.232947923010215e-05</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.00444432906806469</v>
+        <v>0.001373169594444335</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.002613181713968515</v>
+        <v>0.0004542050301097333</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.001799948862753808</v>
+        <v>0.0004341632302384824</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0006180994096212089</v>
+        <v>0.00029420864302665</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.002840102650225163</v>
+        <v>0.0009573345887474716</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.001706440467387438</v>
+        <v>0.0003310214087832719</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001189096597954631</v>
+        <v>0.0004467792459763587</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.002620472107082605</v>
+        <v>0.0001038522386807017</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.006837931927293539</v>
+        <v>9.619671618565917e-05</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.003386701457202435</v>
+        <v>0.001022589160129428</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0005453083431348205</v>
+        <v>0.0009807914029806852</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.008114423602819443</v>
+        <v>0.000201311195269227</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.004791830666363239</v>
+        <v>7.471417484339327e-05</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.004703868646174669</v>
+        <v>0.0008607277413830161</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.006219579372555017</v>
+        <v>0.001221336657181382</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.004926295951008797</v>
+        <v>0.0004347741778474301</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.001118550426326692</v>
+        <v>8.123792940750718e-05</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0003724477719515562</v>
+        <v>0.00040831119986251</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.004149661399424076</v>
+        <v>0.001267400104552507</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.001792589202523232</v>
+        <v>0.0006862750742584467</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.003014679532498121</v>
+        <v>0.0005224373890087008</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0005664420314133167</v>
+        <v>0.0001696672989055514</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.002852203790098429</v>
+        <v>0.001096323947422206</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.001672095153480768</v>
+        <v>0.0003567840903997421</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.002146031707525253</v>
+        <v>0.0003474433906376362</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.001917234156280756</v>
+        <v>0.0001542957907076925</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.004329860210418701</v>
+        <v>0.0001574581838212907</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.004032217431813478</v>
+        <v>0.002912663854658604</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0003639034403022379</v>
+        <v>0.0004100191290490329</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.003680393565446138</v>
+        <v>0.0003350615734234452</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01148951984941959</v>
+        <v>0.0005041406257078052</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0007339077419601381</v>
+        <v>0.002536940621212125</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.003237210679799318</v>
+        <v>0.0004491786239668727</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.004406710155308247</v>
+        <v>0.00199744151905179</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.008714242838323116</v>
+        <v>0.001021667383611202</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.00128989783115685</v>
+        <v>0.0004989573499187827</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.001513262744992971</v>
+        <v>0.001228346256539226</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.001717895152978599</v>
+        <v>0.0003578148025553674</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.003298032796010375</v>
+        <v>0.001122443005442619</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0009033090900629759</v>
+        <v>3.953538544010371e-05</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.002158087678253651</v>
+        <v>0.001147550530731678</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.001479332451708615</v>
+        <v>0.0009265495464205742</v>
       </c>
       <c r="DU8" t="n">
-        <v>8.166296174749732e-05</v>
+        <v>0.0009092509280890226</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.000629627495072782</v>
+        <v>7.908172847237438e-05</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0004218298709020019</v>
+        <v>0.0001263676967937499</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.003519649151712656</v>
+        <v>0.0005215995479375124</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.002673492766916752</v>
+        <v>0.002180448267608881</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.003135181730613112</v>
+        <v>0.0003450756194069982</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.001990837277844548</v>
+        <v>0.001523758401162922</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.002497443929314613</v>
+        <v>6.96526185492985e-05</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0004783757030963898</v>
+        <v>8.19306296762079e-05</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.002135143615305424</v>
+        <v>0.001715184072963893</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.001575876725837588</v>
+        <v>0.00242109433747828</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.001876855036243796</v>
+        <v>6.731317262165248e-05</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.006062780041247606</v>
+        <v>0.0008967539761215448</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.002244463423267007</v>
+        <v>0.0001238636905327439</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.00263700308278203</v>
+        <v>0.001409482094459236</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0009435976389795542</v>
+        <v>0.0006145557854324579</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.003741429653018713</v>
+        <v>0.0001334870758000761</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.002160677453503013</v>
+        <v>4.269303099135868e-05</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.001749693183228374</v>
+        <v>0.0004103774263057858</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0008657271391712129</v>
+        <v>0.0005242519546300173</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0003525311476550996</v>
+        <v>0.0003357998211868107</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.001423167064785957</v>
+        <v>0.001111363992094994</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.001740464707836509</v>
+        <v>0.000869770476128906</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.002684857230633497</v>
+        <v>0.0009459680877625942</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.003260217839851975</v>
+        <v>0.001531096873804927</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0008090353803709149</v>
+        <v>0.0009306479478254914</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.004626437090337276</v>
+        <v>1.461502688471228e-05</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.01067245658487082</v>
+        <v>0.000432191212894395</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.000359373923856765</v>
+        <v>0.0001567498838994652</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.001115621067583561</v>
+        <v>0.0003380448906682432</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.003698222106322646</v>
+        <v>0.001431533368304372</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.001286105019971728</v>
+        <v>0.0005092811188660562</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.001573586603626609</v>
+        <v>0.0006421502912417054</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0001694058591965586</v>
+        <v>0.0003206382971256971</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.002365674125030637</v>
+        <v>0.001043154508806765</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.002675469499081373</v>
+        <v>6.015921826474369e-05</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.001819886267185211</v>
+        <v>0.0002054176002275199</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.003021940588951111</v>
+        <v>0.0003642820520326495</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0006654873141087592</v>
+        <v>0.0001014188746921718</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.001932848594151437</v>
+        <v>0.001171595649793744</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.003937745932489634</v>
+        <v>0.001148122362792492</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.006408256478607655</v>
+        <v>0.000502675655297935</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.001263856887817383</v>
+        <v>7.485083187930286e-05</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.002348213922232389</v>
+        <v>0.0009513263357803226</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0007668480975553393</v>
+        <v>8.233858534367755e-05</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.00243291724473238</v>
+        <v>0.0004849843389820307</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.004688703455030918</v>
+        <v>0.002001666463911533</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.002971628215163946</v>
+        <v>0.001196342287585139</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.003754005068913102</v>
+        <v>0.002635540440678596</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.001401702640578151</v>
+        <v>0.0005488167516887188</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.00226376811042428</v>
+        <v>0.0001862363133113831</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0005210329545661807</v>
+        <v>0.001762124360539019</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.004792041145265102</v>
+        <v>0.0002839262306224555</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.002956804353743792</v>
+        <v>0.0005749576957896352</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0006866854964755476</v>
+        <v>0.003121321089565754</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.0009093333501368761</v>
+        <v>9.188213152810931e-05</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.00608349684625864</v>
+        <v>0.0006721920799463987</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.00311502767726779</v>
+        <v>8.684359636390582e-05</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0001503799576312304</v>
+        <v>0.001785665634088218</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0007608198211528361</v>
+        <v>8.906861330615357e-05</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.001962572801858187</v>
+        <v>0.002037167549133301</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.002603160450235009</v>
+        <v>0.00135026581119746</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.007396154571324587</v>
+        <v>0.000182034564204514</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.004482715856283903</v>
+        <v>0.0008652128162793815</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.001547694904729724</v>
+        <v>0.0001539304212201387</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.001674755476415157</v>
+        <v>1.352832867951292e-08</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02930710650980473</v>
+        <v>1.8402083190594e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002403112361207604</v>
+        <v>3.597521391895953e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01124268397688866</v>
+        <v>1.37787425913416e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008482621051371098</v>
+        <v>9.969942205145799e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02563685551285744</v>
+        <v>8.998866540821382e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00222168629989028</v>
+        <v>2.163624834849998e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006942333653569221</v>
+        <v>1.50071848281641e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.000529731041751802</v>
+        <v>8.083346436649208e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005100348964333534</v>
+        <v>1.251659220713464e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02806218527257442</v>
+        <v>1.654931480743471e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004697145195677876</v>
+        <v>1.315391706668834e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009599726647138596</v>
+        <v>3.420704430823207e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002807219047099352</v>
+        <v>7.246470090649382e-10</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0236255619674921</v>
+        <v>2.440902413525237e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002362747211009264</v>
+        <v>2.851109570656263e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.004360429011285305</v>
+        <v>2.806453025527844e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>9.938153380062431e-05</v>
+        <v>2.335180937507175e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0007081457297317684</v>
+        <v>1.543282479588015e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002283333335071802</v>
+        <v>1.402991944843279e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0003642004448920488</v>
+        <v>7.455193795635751e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>0.00404061283916235</v>
+        <v>2.221237638266871e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003197654383257031</v>
+        <v>2.823356659575893e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0008398519130423665</v>
+        <v>5.655145685068419e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001107678515836596</v>
+        <v>5.226738597485792e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002771295607089996</v>
+        <v>1.071173549860305e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.002424841281026602</v>
+        <v>2.190943071411766e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002462102565914392</v>
+        <v>2.2575539659897e-08</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.001288715749979019</v>
+        <v>3.459727393462231e-09</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.002008209703490138</v>
+        <v>1.246676184507578e-08</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.002377121243625879</v>
+        <v>1.036250463215538e-08</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.003034223802387714</v>
+        <v>1.950983152809727e-09</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001099446322768927</v>
+        <v>7.882476338316735e-10</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001117773354053497</v>
+        <v>2.702854828839918e-09</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.003362008836120367</v>
+        <v>1.409219851922217e-08</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0004509671125560999</v>
+        <v>3.332610187811724e-09</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.004544001072645187</v>
+        <v>1.084496759062858e-08</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.003059911075979471</v>
+        <v>5.121654211848181e-09</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.002597432117909193</v>
+        <v>1.352194090031844e-08</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0007563089020550251</v>
+        <v>3.214878363522189e-10</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001143402652814984</v>
+        <v>8.894099678968814e-09</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001801366568543017</v>
+        <v>4.997307456733324e-09</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0004135313793085515</v>
+        <v>6.191296364477239e-09</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.002191004808992147</v>
+        <v>2.223964301606429e-08</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.001979382010176778</v>
+        <v>5.798695745795612e-09</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.001005592755973339</v>
+        <v>2.192891201957536e-09</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.019881222397089</v>
+        <v>2.592786607635844e-08</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.002883949549868703</v>
+        <v>1.411604877432637e-08</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0006033590179868042</v>
+        <v>2.039939550613212e-09</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.002752114087343216</v>
+        <v>5.530338853532157e-09</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01166157424449921</v>
+        <v>5.019688220642138e-09</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0001311158412136137</v>
+        <v>1.040841013377758e-08</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.000822740257717669</v>
+        <v>2.4852562230393e-09</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.00208602799102664</v>
+        <v>1.995496656803653e-09</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001784291234798729</v>
+        <v>4.300797940004486e-08</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.006759621202945709</v>
+        <v>2.191795900330362e-08</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.007573043461889029</v>
+        <v>1.948558292497182e-08</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.002517492976039648</v>
+        <v>1.605453547881552e-08</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.008239924907684326</v>
+        <v>2.218497918704543e-08</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.009609146043658257</v>
+        <v>1.174617203503203e-08</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.000155446701683104</v>
+        <v>4.897753314025977e-09</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0005290087428875268</v>
+        <v>6.182711231872418e-09</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.001896100351586938</v>
+        <v>3.380738178293541e-08</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.002781106624752283</v>
+        <v>4.763861305434602e-09</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.007125111762434244</v>
+        <v>4.907824369126956e-09</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.001922390423715115</v>
+        <v>8.228784764696684e-09</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.002133568050339818</v>
+        <v>1.606067812076617e-08</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001022879267111421</v>
+        <v>3.784731195111135e-09</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.003094461048021913</v>
+        <v>1.18810872251629e-08</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.002501483540982008</v>
+        <v>1.015088724187763e-08</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.001313095213845372</v>
+        <v>1.624654522025537e-09</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0005131111829541624</v>
+        <v>1.53898653820761e-08</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0001390199031447992</v>
+        <v>2.491460904252563e-08</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.01129064615815878</v>
+        <v>1.93594207331671e-08</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.001036634435877204</v>
+        <v>7.983360639229886e-10</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.002822140697389841</v>
+        <v>1.583382491787688e-08</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.002046098932623863</v>
+        <v>1.703566177013727e-09</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.004261000081896782</v>
+        <v>3.048449936926545e-09</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.001957609783858061</v>
+        <v>8.671016127337339e-10</v>
       </c>
       <c r="CB9" t="n">
-        <v>8.158286073012277e-05</v>
+        <v>9.204459416878308e-10</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.001779457787051797</v>
+        <v>7.420457137641279e-09</v>
       </c>
       <c r="CD9" t="n">
-        <v>8.540775161236525e-05</v>
+        <v>1.901944823856638e-09</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.004600361455231905</v>
+        <v>6.077376824009662e-09</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.001987254712730646</v>
+        <v>2.175820634775505e-10</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002074181335046887</v>
+        <v>3.67003583079395e-09</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.167921436717734e-05</v>
+        <v>5.097268385156895e-09</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.00471904594451189</v>
+        <v>2.829292800043959e-09</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.001502390950918198</v>
+        <v>2.664651832517961e-11</v>
       </c>
       <c r="CK9" t="n">
-        <v>9.74640206550248e-05</v>
+        <v>1.43628176019206e-09</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.00150224706158042</v>
+        <v>7.260203105374785e-09</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.007221272215247154</v>
+        <v>4.981538737069968e-09</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.002277564024552703</v>
+        <v>8.378091997940373e-09</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0006160092307254672</v>
+        <v>2.69742983505239e-09</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.003314726753160357</v>
+        <v>1.825406670263874e-08</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0004906547255814075</v>
+        <v>2.917728814111342e-08</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0006822991417720914</v>
+        <v>1.090096635181226e-08</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.004936832468956709</v>
+        <v>3.043544793968067e-08</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.005336269270628691</v>
+        <v>9.082835816798251e-09</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.001359708490781486</v>
+        <v>1.468551680261498e-08</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0003030028310604393</v>
+        <v>1.11659415047427e-09</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.003612657077610493</v>
+        <v>4.864133984483487e-09</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.00181083579082042</v>
+        <v>1.984096664742196e-09</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.003216949757188559</v>
+        <v>5.796752855502518e-09</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0004698676930274814</v>
+        <v>4.888229376831532e-09</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.004822926130145788</v>
+        <v>2.917202923669038e-09</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.001292387372814119</v>
+        <v>3.902047573944856e-09</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.00107417581602931</v>
+        <v>4.087280736086996e-09</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0004440540506038815</v>
+        <v>5.944209569008763e-09</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.001867697923444211</v>
+        <v>9.332174144560668e-09</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.003574629547074437</v>
+        <v>3.29352545236361e-08</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0009432124788872898</v>
+        <v>1.743469013604226e-08</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.006517502944916487</v>
+        <v>2.739224180814404e-09</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.006936336867511272</v>
+        <v>1.762512447101017e-08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.001379871391691267</v>
+        <v>9.900856134947844e-09</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.002036249963566661</v>
+        <v>3.941846848931618e-09</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.001770706381648779</v>
+        <v>9.462540084825832e-09</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.006711459718644619</v>
+        <v>1.722491660416381e-08</v>
       </c>
       <c r="DN9" t="n">
-        <v>5.748320836573839e-05</v>
+        <v>1.274995042876981e-08</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0003130002878606319</v>
+        <v>6.878753566752493e-09</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.00355256418697536</v>
+        <v>4.971831835121066e-09</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0003379650879651308</v>
+        <v>6.823478226891666e-09</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.001351623330265284</v>
+        <v>1.15672555978108e-08</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.002223776886239648</v>
+        <v>1.24465149298203e-08</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0007810469251126051</v>
+        <v>8.716058985669406e-09</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.002263362752273679</v>
+        <v>1.195827081801326e-08</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.001122178859077394</v>
+        <v>1.612163558206703e-08</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0005823099636472762</v>
+        <v>5.174575434807593e-09</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.002458195434883237</v>
+        <v>1.495612966806448e-09</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.002118765143677592</v>
+        <v>1.229463642005157e-08</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.001732862088829279</v>
+        <v>1.157163254106308e-08</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.002244080416858196</v>
+        <v>1.712115071939024e-08</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.003772584954276681</v>
+        <v>1.053653830851431e-10</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0001445986272301525</v>
+        <v>1.460945053821661e-08</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0007434700382873416</v>
+        <v>1.033763918911745e-08</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.001522373408079147</v>
+        <v>6.629617743669769e-09</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001320661744102836</v>
+        <v>3.82905845919268e-10</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.005384435877203941</v>
+        <v>4.893539351513709e-09</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.001184149878099561</v>
+        <v>1.879553179762183e-09</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.001046003773808479</v>
+        <v>4.918285778643394e-10</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0002018372761085629</v>
+        <v>9.07993680243635e-10</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.004634789656847715</v>
+        <v>4.359749006255242e-09</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.001240585814230144</v>
+        <v>7.665755141772479e-09</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.001738450024276972</v>
+        <v>3.440790319331199e-09</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0002571949153207242</v>
+        <v>7.008690072751733e-09</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.000514462823048234</v>
+        <v>8.015823560469926e-09</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001445813104510307</v>
+        <v>4.802798603265046e-09</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0008190087974071503</v>
+        <v>8.586451549774665e-10</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.001907902886159718</v>
+        <v>2.08733497153446e-09</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0001615329238120466</v>
+        <v>7.160469994715868e-09</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.003416553838178515</v>
+        <v>1.224871648553005e-09</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.002157014096155763</v>
+        <v>1.038198060854256e-08</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.006681222934275866</v>
+        <v>1.032290697366989e-08</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0002273046993650496</v>
+        <v>9.390881405835216e-10</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0005895310896448791</v>
+        <v>6.480407321873827e-10</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.003044834593310952</v>
+        <v>5.662314173093819e-09</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0005682423943653703</v>
+        <v>3.122279768064118e-09</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.002032161457464099</v>
+        <v>9.369465203690197e-09</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0008576133986935019</v>
+        <v>6.433141130912645e-09</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.004614083562046289</v>
+        <v>5.779104972347682e-10</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.002034872304648161</v>
+        <v>3.367440770674079e-09</v>
       </c>
       <c r="FE9" t="n">
-        <v>6.651724106632173e-05</v>
+        <v>6.130416174698894e-09</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.001719602732919157</v>
+        <v>4.89182028218238e-09</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0009919056901708245</v>
+        <v>1.323315901302635e-09</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0002779219066724181</v>
+        <v>7.617347641541983e-09</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.002717559691518545</v>
+        <v>2.534188414671235e-09</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.004840338602662086</v>
+        <v>1.361902679519744e-08</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.001577135175466537</v>
+        <v>6.285338471911928e-09</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0006543640047311783</v>
+        <v>1.972099994418386e-08</v>
       </c>
       <c r="FM9" t="n">
-        <v>4.710569191956893e-05</v>
+        <v>2.015307476455064e-09</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.001683413283899426</v>
+        <v>2.498666162864538e-09</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.001149794785305858</v>
+        <v>1.831610774161163e-08</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.002676913980394602</v>
+        <v>3.389301994616289e-08</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.006742728408426046</v>
+        <v>9.435621173281561e-10</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0006697605713270605</v>
+        <v>9.266342360092494e-09</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.003690546145662665</v>
+        <v>4.468138570246083e-08</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0013821916654706</v>
+        <v>4.301453770949593e-08</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.002431857399642467</v>
+        <v>7.295072101953792e-09</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.001703195041045547</v>
+        <v>1.408659411339386e-09</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.002754192100837827</v>
+        <v>2.966640622048544e-08</v>
       </c>
       <c r="FX9" t="n">
-        <v>9.682058589532971e-05</v>
+        <v>9.882056062338052e-09</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.005780341569334269</v>
+        <v>1.098882584926741e-08</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.002145130652934313</v>
+        <v>1.712656683139357e-09</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0009277912322431803</v>
+        <v>1.248977454793021e-08</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.000241448637098074</v>
+        <v>1.13427551795553e-08</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.001632718602195382</v>
+        <v>9.706758063998677e-09</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.001166880712844431</v>
+        <v>4.478325488221913e-10</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.008121511898934841</v>
+        <v>1.611644151466862e-08</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.001082249218598008</v>
+        <v>4.390471985971089e-09</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.001412335433997214</v>
+        <v>6.167986565941419e-09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.445114685338922e-05</v>
+        <v>8.595918643550249e-08</v>
       </c>
       <c r="B10" t="n">
-        <v>0.003144495654851198</v>
+        <v>6.317707175185205e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>8.192968380171806e-05</v>
+        <v>3.542603963069269e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001473419135436416</v>
+        <v>7.938535418361425e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0007196527440100908</v>
+        <v>1.022631408886809e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0001785906060831621</v>
+        <v>8.755072485655546e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0004752656677737832</v>
+        <v>3.821378868451575e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0006965752108953893</v>
+        <v>4.42605823991471e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>3.760624167625792e-06</v>
+        <v>1.217461317537527e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001218653051182628</v>
+        <v>7.187046549006482e-07</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002657324774190784</v>
+        <v>5.651647370541468e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001451559219276533</v>
+        <v>4.578731022775173e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>0.001144561567343771</v>
+        <v>1.102049827750307e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0009118288289755583</v>
+        <v>4.744716989080189e-06</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0007832359988242388</v>
+        <v>7.644448487553746e-06</v>
       </c>
       <c r="P10" t="n">
-        <v>0.000365281302947551</v>
+        <v>5.04311356053222e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.515614611795172e-05</v>
+        <v>4.262952643330209e-06</v>
       </c>
       <c r="R10" t="n">
-        <v>0.000147904793266207</v>
+        <v>1.093346781999571e-06</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0001667504839133471</v>
+        <v>2.65505491370277e-07</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0005238183075562119</v>
+        <v>9.142403314399417e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>5.313549627317116e-05</v>
+        <v>1.737212755870132e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0002178904833272099</v>
+        <v>6.063274895495852e-07</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002267853124067187</v>
+        <v>1.756234382810362e-06</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0004640717525035143</v>
+        <v>1.168384414995671e-06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0001717669947538525</v>
+        <v>1.142479817417552e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.000616593926679343</v>
+        <v>9.978830348700285e-07</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0005366635741665959</v>
+        <v>1.132482196908313e-07</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0001188281166832894</v>
+        <v>4.484134592530609e-07</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0003433427773416042</v>
+        <v>9.102651574721676e-07</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0001143214612966403</v>
+        <v>1.67991049693228e-06</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0002081276034004986</v>
+        <v>1.058291559274949e-06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0001845602673711255</v>
+        <v>6.237084448912356e-08</v>
       </c>
       <c r="AG10" t="n">
-        <v>8.633504330646247e-05</v>
+        <v>3.853509497275809e-06</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0002984986058436334</v>
+        <v>8.18605030872277e-07</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.45376756740734e-05</v>
+        <v>3.414864067963208e-06</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0001468215341446921</v>
+        <v>6.37267760339455e-07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.000310294795781374</v>
+        <v>1.70667476595554e-07</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0003893894026987255</v>
+        <v>2.281481101817917e-06</v>
       </c>
       <c r="AM10" t="n">
-        <v>5.462859189719893e-05</v>
+        <v>1.872022721727262e-06</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0001329383521806449</v>
+        <v>1.490501745138317e-06</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0004060311475768685</v>
+        <v>5.099628879179363e-07</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.374229759676382e-05</v>
+        <v>9.294703318118991e-07</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0002221275644842535</v>
+        <v>1.415043470842647e-06</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0001212297502206638</v>
+        <v>8.547551715309964e-07</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.161229536402971e-05</v>
+        <v>7.848949508115766e-07</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0002776480687316507</v>
+        <v>2.225522166554583e-06</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.002089485060423613</v>
+        <v>4.221141807647655e-06</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0003363422874826938</v>
+        <v>3.272459935033112e-06</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0004004091897513717</v>
+        <v>1.960190502359183e-06</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0001342833420494571</v>
+        <v>6.822272553108633e-06</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0001306048943661153</v>
+        <v>5.530339876713697e-06</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7.296483090613037e-05</v>
+        <v>1.462971908949839e-06</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.000213894309126772</v>
+        <v>1.609844048289233e-06</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0002087459142785519</v>
+        <v>1.089881607185816e-06</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0005357813788577914</v>
+        <v>6.314326128631365e-07</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0005193256074562669</v>
+        <v>3.572460229861463e-07</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0007258927798829973</v>
+        <v>1.574995849296101e-06</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.044528057216667e-05</v>
+        <v>1.26798840938136e-06</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0006935378769412637</v>
+        <v>4.370446276880102e-06</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0002529829507693648</v>
+        <v>6.063791602173296e-08</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.000171672654687427</v>
+        <v>4.259188131072733e-07</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0002522740396670997</v>
+        <v>9.450171774005867e-07</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0001592312619322911</v>
+        <v>3.772390186895791e-07</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0002097411197610199</v>
+        <v>3.275924882473191e-07</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0001812458067433909</v>
+        <v>2.702992787817493e-06</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0004052637086715549</v>
+        <v>1.208994035550859e-06</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0002871297474484891</v>
+        <v>2.296014372404898e-06</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0004263765877112746</v>
+        <v>1.184090479000588e-06</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.0001775934651959687</v>
+        <v>1.849395857789204e-06</v>
       </c>
       <c r="BR10" t="n">
-        <v>1.483645974076353e-05</v>
+        <v>3.801085028953821e-07</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.000269509240752086</v>
+        <v>4.305552181449457e-07</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0003312469343654811</v>
+        <v>5.46230978670792e-07</v>
       </c>
       <c r="BU10" t="n">
-        <v>2.823562317644246e-05</v>
+        <v>1.440940309294092e-07</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.00120116351172328</v>
+        <v>3.091906819463475e-06</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.76576271164231e-05</v>
+        <v>2.340463652217295e-06</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0003415480023249984</v>
+        <v>3.308294253656641e-06</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0001005341619020328</v>
+        <v>1.692349314907915e-06</v>
       </c>
       <c r="BZ10" t="n">
-        <v>8.084205910563469e-05</v>
+        <v>3.663802999653853e-06</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0001899466151371598</v>
+        <v>1.216137206938583e-06</v>
       </c>
       <c r="CB10" t="n">
-        <v>8.441781392320991e-05</v>
+        <v>5.592535217147088e-07</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0003508736554067582</v>
+        <v>2.017968370182643e-07</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.013459768728353e-05</v>
+        <v>1.874050497008284e-07</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0005725077353417873</v>
+        <v>1.523687046756095e-06</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0002382155362283811</v>
+        <v>9.723453331389464e-07</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0001035401728586294</v>
+        <v>2.458836206642445e-06</v>
       </c>
       <c r="CH10" t="n">
-        <v>9.15407799766399e-05</v>
+        <v>1.137372294124361e-07</v>
       </c>
       <c r="CI10" t="n">
-        <v>7.639802788617089e-06</v>
+        <v>2.147812892872025e-06</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0001125279814004898</v>
+        <v>4.864230618295551e-08</v>
       </c>
       <c r="CK10" t="n">
-        <v>8.012659236555919e-05</v>
+        <v>1.097386416404333e-06</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0001446982787456363</v>
+        <v>7.464421400982246e-07</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.001007386832498014</v>
+        <v>2.918555708220083e-07</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0002253915299661458</v>
+        <v>4.521085656961077e-07</v>
       </c>
       <c r="CO10" t="n">
-        <v>5.275475268717855e-05</v>
+        <v>3.218979372832109e-06</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0006434199749492109</v>
+        <v>1.488330894972023e-06</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0005786604015156627</v>
+        <v>9.530035072202736e-08</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0003294218331575394</v>
+        <v>6.903687221893051e-07</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0007371885585598648</v>
+        <v>8.173743140105216e-07</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0006091574323363602</v>
+        <v>1.096745563700097e-06</v>
       </c>
       <c r="CU10" t="n">
-        <v>2.810894511640072e-05</v>
+        <v>1.988547069231572e-07</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.819290991988964e-05</v>
+        <v>2.102394205394376e-07</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0004895766614936292</v>
+        <v>1.337970047643466e-06</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0002998649142682552</v>
+        <v>1.110998937292607e-06</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0002803743991535157</v>
+        <v>2.573780875536613e-06</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0001566459104651585</v>
+        <v>1.060140334629978e-06</v>
       </c>
       <c r="DA10" t="n">
-        <v>7.600900062243454e-06</v>
+        <v>2.280230091855628e-06</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0001791912072803825</v>
+        <v>2.862938117687008e-07</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0001586527505423874</v>
+        <v>1.203967372020998e-06</v>
       </c>
       <c r="DD10" t="n">
-        <v>6.74827751936391e-05</v>
+        <v>9.307041182182729e-07</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.000353088224073872</v>
+        <v>1.597048026269476e-06</v>
       </c>
       <c r="DF10" t="n">
-        <v>4.271355646778829e-05</v>
+        <v>2.787547373372945e-06</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0002369832363910973</v>
+        <v>3.159663037877181e-07</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0005181955639272928</v>
+        <v>2.653797764651245e-06</v>
       </c>
       <c r="DI10" t="n">
-        <v>5.405394767876714e-05</v>
+        <v>2.060567567241378e-06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>9.357920498587191e-05</v>
+        <v>6.951940576982452e-06</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.010335735278204e-05</v>
+        <v>8.544852647673906e-08</v>
       </c>
       <c r="DL10" t="n">
-        <v>5.413274993770756e-05</v>
+        <v>3.727579723999952e-06</v>
       </c>
       <c r="DM10" t="n">
-        <v>2.233019040431827e-05</v>
+        <v>1.56172256993159e-06</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0001178766106022522</v>
+        <v>4.820500407731743e-07</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.94532549357973e-06</v>
+        <v>1.047365003614686e-06</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0004280295688658953</v>
+        <v>1.470154529670253e-06</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0001985856797546148</v>
+        <v>9.026445013660123e-08</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0002593792451079935</v>
+        <v>2.170203003970528e-07</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0001595310750417411</v>
+        <v>8.439169505436439e-07</v>
       </c>
       <c r="DT10" t="n">
-        <v>7.114209438441321e-05</v>
+        <v>2.146969961813738e-07</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.000233019920415245</v>
+        <v>2.828967353707412e-06</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0003565252118278295</v>
+        <v>2.053707021332229e-06</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.000196570428670384</v>
+        <v>9.347588729724521e-07</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0003004387835972011</v>
+        <v>8.122836447910231e-07</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0003571383713278919</v>
+        <v>3.261362962803105e-06</v>
       </c>
       <c r="DZ10" t="n">
-        <v>8.079510007519275e-05</v>
+        <v>2.1938790268905e-06</v>
       </c>
       <c r="EA10" t="n">
-        <v>7.765961345285177e-05</v>
+        <v>3.205515497484157e-08</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0003392805519979447</v>
+        <v>2.057023039014894e-06</v>
       </c>
       <c r="EC10" t="n">
-        <v>4.17501105403062e-05</v>
+        <v>4.640220367946313e-07</v>
       </c>
       <c r="ED10" t="n">
-        <v>1.050195623975014e-05</v>
+        <v>2.787234507195535e-06</v>
       </c>
       <c r="EE10" t="n">
-        <v>1.306171543546952e-05</v>
+        <v>2.032499651249964e-06</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0002029763418249786</v>
+        <v>1.351808805338806e-06</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0004794778651557863</v>
+        <v>1.187539055536035e-06</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.0002910280018113554</v>
+        <v>1.174899352918146e-06</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0001869090483523905</v>
+        <v>2.21317304749391e-06</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.000193115629372187</v>
+        <v>2.869984712106088e-07</v>
       </c>
       <c r="EK10" t="n">
-        <v>5.584188329521567e-05</v>
+        <v>1.75717707406875e-06</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0001199603138957173</v>
+        <v>3.249767530633108e-07</v>
       </c>
       <c r="EM10" t="n">
-        <v>5.763747685705312e-05</v>
+        <v>3.183517662819213e-07</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0001595088833710179</v>
+        <v>5.637314757223066e-07</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0001035321183735505</v>
+        <v>1.153335347225948e-07</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.000289213057840243</v>
+        <v>1.774280008248752e-06</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0002712458954192698</v>
+        <v>1.33295111481857e-06</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0001914704625960439</v>
+        <v>1.943583129104809e-06</v>
       </c>
       <c r="ES10" t="n">
-        <v>1.646124292165041e-05</v>
+        <v>6.363907232298516e-07</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0002538894186727703</v>
+        <v>1.262825293224523e-07</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0004889710689894855</v>
+        <v>5.749703291257902e-07</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0005905851139687002</v>
+        <v>1.739953404467087e-06</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0003074239648412913</v>
+        <v>2.401388201178634e-06</v>
       </c>
       <c r="EX10" t="n">
-        <v>8.634998084744439e-05</v>
+        <v>3.921115308003209e-07</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.000496889348141849</v>
+        <v>1.931802898980095e-06</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0002127853222191334</v>
+        <v>7.667770205443958e-07</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0002354373427806422</v>
+        <v>2.694506747502601e-06</v>
       </c>
       <c r="FB10" t="n">
-        <v>9.625110396882519e-05</v>
+        <v>1.932753264100029e-07</v>
       </c>
       <c r="FC10" t="n">
-        <v>2.854190279322211e-05</v>
+        <v>2.067828290819307e-06</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0001877264148788527</v>
+        <v>3.250190729886526e-07</v>
       </c>
       <c r="FE10" t="n">
-        <v>5.654786218656227e-05</v>
+        <v>1.249779529644002e-06</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0001271067303605378</v>
+        <v>1.620565939219887e-07</v>
       </c>
       <c r="FG10" t="n">
-        <v>1.053745654644445e-05</v>
+        <v>6.609153047065774e-07</v>
       </c>
       <c r="FH10" t="n">
-        <v>2.087779466819484e-05</v>
+        <v>1.173516238850425e-06</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0005537736578844488</v>
+        <v>2.613844117149711e-06</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0002939051191788167</v>
+        <v>9.602742920833407e-07</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.000107294887129683</v>
+        <v>1.693770400379435e-06</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0002886446891352534</v>
+        <v>1.586605662851071e-06</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.0001041161813191138</v>
+        <v>4.792561867361655e-07</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0002118730335496366</v>
+        <v>2.496680508556892e-06</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.000165839257533662</v>
+        <v>2.075836164294742e-06</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0004154790076427162</v>
+        <v>3.22939354191476e-06</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0002905495930463076</v>
+        <v>3.887041657435475e-06</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.0005174201214686036</v>
+        <v>2.88216324406676e-06</v>
       </c>
       <c r="FS10" t="n">
-        <v>9.222190419677645e-05</v>
+        <v>2.41183602156525e-06</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.000138633098686114</v>
+        <v>1.523930563962494e-06</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0002010844182223082</v>
+        <v>2.084125583223795e-08</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0003263262042310089</v>
+        <v>2.598423634481151e-06</v>
       </c>
       <c r="FW10" t="n">
-        <v>9.16053177206777e-05</v>
+        <v>5.30307670487673e-06</v>
       </c>
       <c r="FX10" t="n">
-        <v>7.45586003176868e-05</v>
+        <v>5.455516429719864e-07</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0004142020188737661</v>
+        <v>6.519721296172065e-07</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0003577853785827756</v>
+        <v>8.248646281572292e-07</v>
       </c>
       <c r="GA10" t="n">
-        <v>1.118089676310774e-05</v>
+        <v>3.133100108243525e-06</v>
       </c>
       <c r="GB10" t="n">
-        <v>1.81433842953993e-05</v>
+        <v>1.652907485549804e-06</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0001841072662500665</v>
+        <v>4.032924152852502e-06</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0004758529830724001</v>
+        <v>4.081589395354968e-06</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.001280207419767976</v>
+        <v>6.463376394094666e-07</v>
       </c>
       <c r="GF10" t="n">
-        <v>8.239092858275399e-05</v>
+        <v>8.791225241111533e-07</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0003060604503843933</v>
+        <v>4.543458231864861e-08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.007753857411444187</v>
+        <v>4.820560207008384e-06</v>
       </c>
       <c r="B11" t="n">
-        <v>0.06456597149372101</v>
+        <v>0.0001408988609910011</v>
       </c>
       <c r="C11" t="n">
-        <v>0.007068997714668512</v>
+        <v>4.538031134870835e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02591192722320557</v>
+        <v>4.411731424625032e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0119650000706315</v>
+        <v>6.760993710486218e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03835391253232956</v>
+        <v>0.0001287589402636513</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004953915718942881</v>
+        <v>2.890677933464758e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01912180706858635</v>
+        <v>5.660087845171802e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.007178876549005508</v>
+        <v>4.119281584280543e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01101733930408955</v>
+        <v>3.159440893796273e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.06034954637289047</v>
+        <v>0.0001256211980944499</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002318047918379307</v>
+        <v>8.210778469219804e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01963204331696033</v>
+        <v>0.0001233067887369543</v>
       </c>
       <c r="N11" t="n">
-        <v>0.00588435772806406</v>
+        <v>1.099334622267634e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>0.03337590768933296</v>
+        <v>0.0001627274323254824</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001102714682929218</v>
+        <v>2.819745895976666e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.004341600462794304</v>
+        <v>2.363874955335632e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.007398989517241716</v>
+        <v>5.232654075371101e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001659966073930264</v>
+        <v>1.765938759490382e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>0.006383803673088551</v>
+        <v>3.654855754575692e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>0.002712959190830588</v>
+        <v>5.645178134727757e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>0.008684295229613781</v>
+        <v>9.665814104664605e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.005675442516803741</v>
+        <v>6.863060207251692e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003616258502006531</v>
+        <v>5.42997986485716e-06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.002361355349421501</v>
+        <v>3.324453791719861e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.008461222983896732</v>
+        <v>2.645247150212526e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.004554076585918665</v>
+        <v>1.097143831430003e-05</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001270783133804798</v>
+        <v>9.773743840923999e-06</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.002042595064267516</v>
+        <v>4.592124241753481e-06</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0005342777003534138</v>
+        <v>1.034057640936226e-05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.002035137731581926</v>
+        <v>4.810315294889733e-05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.001426767557859421</v>
+        <v>1.869263360276818e-05</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.001537665608339012</v>
+        <v>7.55945875425823e-05</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.001482749357819557</v>
+        <v>6.547068551299162e-06</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.003018959891051054</v>
+        <v>9.905698971124366e-05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.001386261312291026</v>
+        <v>2.060181577689946e-05</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.01023957878351212</v>
+        <v>1.782355320756324e-05</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.006586391013115644</v>
+        <v>1.781484752427787e-05</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0005273108836263418</v>
+        <v>1.234881437994773e-05</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.002890016650781035</v>
+        <v>8.947930837166496e-06</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.001734272693283856</v>
+        <v>1.718153725960292e-05</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.009210530668497086</v>
+        <v>2.514359039196279e-05</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.003441906534135342</v>
+        <v>5.007239451515488e-06</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.004804295487701893</v>
+        <v>4.147937215748243e-05</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.008239259943366051</v>
+        <v>1.911831714096479e-05</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.001638565096072853</v>
+        <v>2.942425999208353e-05</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.0354093611240387</v>
+        <v>9.419442358193919e-05</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.005266210064291954</v>
+        <v>4.742948658531532e-05</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.005164443980902433</v>
+        <v>2.495328226359561e-05</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.006273670587688684</v>
+        <v>7.492617442039773e-05</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.01850085891783237</v>
+        <v>0.0001361934118904173</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.009132888168096542</v>
+        <v>8.057718332565855e-06</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.008669763803482056</v>
+        <v>4.004406946478412e-05</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.009727814234793186</v>
+        <v>1.110164885176346e-05</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.004456254653632641</v>
+        <v>2.753328953986056e-05</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.01353685278445482</v>
+        <v>1.682201218500268e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.01521283946931362</v>
+        <v>3.530141111696139e-05</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.909509051591158e-05</v>
+        <v>4.206981975585222e-05</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.004293766804039478</v>
+        <v>6.824578304076567e-05</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.00764347892254591</v>
+        <v>2.037657759501599e-05</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.00103641499299556</v>
+        <v>3.249399014748633e-05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.007600895594805479</v>
+        <v>6.217155896592885e-05</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.004953298717737198</v>
+        <v>2.3116976080928e-05</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.003648941870778799</v>
+        <v>2.529863195377402e-06</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.009061484597623348</v>
+        <v>3.754279168788344e-05</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.005125902127474546</v>
+        <v>2.888285598601215e-05</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0007418112363666296</v>
+        <v>2.893825512728654e-05</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.003895638510584831</v>
+        <v>1.137665458372794e-05</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.001745052519254386</v>
+        <v>1.305038131249603e-05</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.00643534492701292</v>
+        <v>1.042304666043492e-05</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.004223193041980267</v>
+        <v>2.154441426682752e-05</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.006076836958527565</v>
+        <v>2.272351048304699e-05</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0006236627232283354</v>
+        <v>1.827834785217419e-05</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.02139545418322086</v>
+        <v>4.983467442798428e-05</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.007405050564557314</v>
+        <v>4.681047357735224e-06</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.001831521280109882</v>
+        <v>1.452355172659736e-05</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.003860750701278448</v>
+        <v>1.464371052861679e-05</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.008758878335356712</v>
+        <v>4.780425661010668e-05</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.002158742863684893</v>
+        <v>5.070967745268717e-05</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.003087135730311275</v>
+        <v>1.701347719063051e-05</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.00420304061844945</v>
+        <v>2.161178963433485e-05</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.001413146266713738</v>
+        <v>5.030924512539059e-07</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.01082334760576487</v>
+        <v>4.774331682710908e-05</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.004626153036952019</v>
+        <v>1.794170202629175e-05</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.004069133196026087</v>
+        <v>1.778809382813051e-05</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.002953908639028668</v>
+        <v>3.901857780874707e-06</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.004073872696608305</v>
+        <v>2.573188976384699e-05</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.003835247363895178</v>
+        <v>2.322097770957043e-06</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.003503481391817331</v>
+        <v>5.662661237693101e-07</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.00492109265178442</v>
+        <v>5.155182407179382e-06</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.01395374070852995</v>
+        <v>7.29452494852012e-06</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.002933094277977943</v>
+        <v>1.780951060936786e-05</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0008635742124170065</v>
+        <v>5.348988634068519e-05</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0178051833063364</v>
+        <v>5.074865475762635e-05</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.007104138378053904</v>
+        <v>1.528007123852149e-05</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.01674219407141209</v>
+        <v>8.441019417659845e-06</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.01248999871313572</v>
+        <v>4.349370283307508e-05</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.009332317858934402</v>
+        <v>4.062975131091662e-05</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.00285971537232399</v>
+        <v>2.474676875863224e-05</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.001394433784298599</v>
+        <v>1.051001891028136e-05</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0104504032060504</v>
+        <v>3.978031963924877e-05</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.004415910691022873</v>
+        <v>2.397680873400532e-05</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.006889781914651394</v>
+        <v>2.544967719586566e-05</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.002180944895371795</v>
+        <v>4.36019035987556e-06</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.003710493911057711</v>
+        <v>3.637559711933136e-05</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.004052304197102785</v>
+        <v>9.928098734235391e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.006514918524771929</v>
+        <v>7.369994818873238e-07</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.00414577592164278</v>
+        <v>9.486474482400808e-06</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.006174941547214985</v>
+        <v>1.90126957022585e-06</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.01096299476921558</v>
+        <v>8.868679287843406e-05</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.004130481742322445</v>
+        <v>7.183593697845936e-05</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.0129368482157588</v>
+        <v>1.833040369092487e-05</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.02230158448219299</v>
+        <v>1.108427204599138e-05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01217122562229633</v>
+        <v>8.655320561956614e-05</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.005670794285833836</v>
+        <v>8.869717930792831e-06</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.008919057436287403</v>
+        <v>5.592458910541609e-05</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.01560742594301701</v>
+        <v>3.23667045449838e-05</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.002948121633380651</v>
+        <v>1.192741365230177e-05</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.00653162132948637</v>
+        <v>4.332764001446776e-05</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.003035357221961021</v>
+        <v>6.935068086022511e-06</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.003401614492759109</v>
+        <v>2.806700103974435e-05</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.002526151947677135</v>
+        <v>2.403358303126879e-05</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.004364714492112398</v>
+        <v>1.044940654537641e-05</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.004089398309588432</v>
+        <v>1.758862708811648e-05</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.007529404945671558</v>
+        <v>5.529983536689542e-05</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0006654374301433563</v>
+        <v>2.812749517033808e-05</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0007393492851406336</v>
+        <v>9.849140951700974e-06</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.006170616950839758</v>
+        <v>1.05199906101916e-05</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.005741504486650229</v>
+        <v>4.827024531550705e-05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.006608095020055771</v>
+        <v>1.201895247504581e-05</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.004316294565796852</v>
+        <v>5.665104981744662e-05</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.004991922061890364</v>
+        <v>2.059482903860044e-05</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.003217054530978203</v>
+        <v>4.931196963298135e-05</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.003479782957583666</v>
+        <v>6.545309588545933e-05</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.01058617047965527</v>
+        <v>9.214061719831079e-05</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.007549950387328863</v>
+        <v>4.03182548325276e-06</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.01321285218000412</v>
+        <v>2.366210082982434e-06</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.005225914064794779</v>
+        <v>8.609658834757283e-07</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.002884783316403627</v>
+        <v>6.549108366016299e-05</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.002901303581893444</v>
+        <v>2.051578485406935e-05</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0007162997499108315</v>
+        <v>4.739339146908605e-06</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.004821863491088152</v>
+        <v>9.054990186996292e-06</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.002051113173365593</v>
+        <v>2.159817267965991e-05</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.001758971251547337</v>
+        <v>3.476068013696931e-05</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.00147559423930943</v>
+        <v>1.853475259849802e-05</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.005237163975834846</v>
+        <v>4.448321487870999e-05</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.005590524058789015</v>
+        <v>1.86611468961928e-05</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.008230580948293209</v>
+        <v>1.084879295376595e-05</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.008563738316297531</v>
+        <v>3.927841680706479e-05</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.002996424678713083</v>
+        <v>3.963945346185938e-05</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.01144470367580652</v>
+        <v>1.651917955314275e-05</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.01433752477169037</v>
+        <v>4.8369070100307e-06</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.001566444989293814</v>
+        <v>2.951386704808101e-06</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.002437534043565392</v>
+        <v>4.084727152076084e-06</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.009789523668587208</v>
+        <v>4.984936822438613e-05</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.003718142164871097</v>
+        <v>1.23242289191694e-05</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.002743805292993784</v>
+        <v>2.883763590944e-05</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.00186608184594661</v>
+        <v>5.048786988481879e-06</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.003308906685560942</v>
+        <v>3.04004606732633e-05</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.006333733908832073</v>
+        <v>3.633280812209705e-06</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.00560680078342557</v>
+        <v>4.19237585447263e-06</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.005941528826951981</v>
+        <v>1.57204285642365e-05</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.002641093218699098</v>
+        <v>2.59257503785193e-05</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.002676256699487567</v>
+        <v>1.228442397405161e-05</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.007337004877626896</v>
+        <v>3.132684287265874e-05</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.008812256157398224</v>
+        <v>2.04412208404392e-05</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0005703432252630591</v>
+        <v>2.692306225071661e-06</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.004557269625365734</v>
+        <v>6.382611900335178e-05</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.003064330900087953</v>
+        <v>1.497486482548993e-05</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.005006712861359119</v>
+        <v>2.306230453541502e-05</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.003754568286240101</v>
+        <v>0.0001137720391852781</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.007686116732656956</v>
+        <v>2.526216121623293e-05</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.002206563949584961</v>
+        <v>2.491524901415687e-05</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.01060929149389267</v>
+        <v>2.011477408814244e-05</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.002112051704898477</v>
+        <v>2.354900061618537e-07</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0006446994957514107</v>
+        <v>4.007639290648513e-05</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.008028661832213402</v>
+        <v>5.002434045309201e-05</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.003808790352195501</v>
+        <v>1.360368332825601e-05</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.002554100938141346</v>
+        <v>0.0001280221476918086</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.002251819474622607</v>
+        <v>1.477272235206328e-05</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.01084558665752411</v>
+        <v>2.787414632621221e-05</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.005457424558699131</v>
+        <v>8.270961188827641e-06</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.004088611342012882</v>
+        <v>6.972768460400403e-05</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.003121792571619153</v>
+        <v>6.888392817927524e-06</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.004492179490625858</v>
+        <v>7.918955816421658e-05</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.004604684188961983</v>
+        <v>3.7077388697071e-05</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.01210587285459042</v>
+        <v>2.666622094693594e-05</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0002151026856154203</v>
+        <v>2.472124651831109e-05</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.005710121244192123</v>
+        <v>1.608482853043824e-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0009210354182869196</v>
+        <v>8.964523345866837e-08</v>
       </c>
       <c r="B12" t="n">
-        <v>0.008144271560013294</v>
+        <v>3.389544076526363e-07</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0004570763267111033</v>
+        <v>7.208801378055796e-08</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001805705134756863</v>
+        <v>1.190809015838568e-07</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002749538980424404</v>
+        <v>7.705423854531546e-08</v>
       </c>
       <c r="F12" t="n">
-        <v>0.005411015823483467</v>
+        <v>2.768333047242777e-07</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000748204649426043</v>
+        <v>2.976940827181807e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0008939937688410282</v>
+        <v>2.282744304693551e-08</v>
       </c>
       <c r="I12" t="n">
-        <v>0.000262877787463367</v>
+        <v>4.337793058084571e-08</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001025618286803365</v>
+        <v>4.171962775245674e-09</v>
       </c>
       <c r="K12" t="n">
-        <v>0.008066900074481964</v>
+        <v>3.189027211192297e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000179141090484336</v>
+        <v>1.231890109920641e-07</v>
       </c>
       <c r="M12" t="n">
-        <v>1.372149563394487e-05</v>
+        <v>2.183770533292773e-07</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0009598917094990611</v>
+        <v>1.347443969734741e-07</v>
       </c>
       <c r="O12" t="n">
-        <v>0.003756266552954912</v>
+        <v>3.559007950570958e-07</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0005736536113545299</v>
+        <v>4.524160246432984e-08</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.000433136650826782</v>
+        <v>1.188520570849505e-08</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001154608675278723</v>
+        <v>1.768518664846397e-08</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0002040743711404502</v>
+        <v>2.369548557368262e-09</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0008132486836984754</v>
+        <v>2.135744203712875e-08</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0006713622715324163</v>
+        <v>6.717922218513195e-08</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0002033461787505075</v>
+        <v>4.759101557283429e-09</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0003338832757435739</v>
+        <v>5.395404656383107e-08</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0002463283308316022</v>
+        <v>7.119750478068454e-08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0008061698172241449</v>
+        <v>1.339370072628299e-07</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.001159945852123201</v>
+        <v>8.90611460135915e-08</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.001104323426261544</v>
+        <v>5.455425977629602e-08</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0003901902236975729</v>
+        <v>1.084768257442192e-07</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0008085765293799341</v>
+        <v>8.437449849907352e-09</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0004481207579374313</v>
+        <v>6.62671340023735e-09</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.000790164340287447</v>
+        <v>1.558453561756323e-07</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.001347741927020252</v>
+        <v>9.711284576496837e-08</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0006581292254850268</v>
+        <v>1.531962254830432e-07</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0003347487945575267</v>
+        <v>2.73765010661009e-10</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.001643403549678624</v>
+        <v>1.640246267697876e-07</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0001485258544562384</v>
+        <v>1.677731376048541e-08</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.002249659039080143</v>
+        <v>1.941567262520039e-08</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0007096671615727246</v>
+        <v>7.850559313737904e-08</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0003572350833564997</v>
+        <v>2.707976065607909e-08</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0003214317257516086</v>
+        <v>6.166634136661742e-08</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0007308619096875191</v>
+        <v>1.904317414869183e-08</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.000534597085788846</v>
+        <v>4.824830668326285e-08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0001833552232710645</v>
+        <v>8.327049982881363e-08</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.0009740923997014761</v>
+        <v>1.284496420339565e-08</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.704341725097038e-05</v>
+        <v>4.13315888181387e-08</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0003981432237196714</v>
+        <v>2.84188192978263e-08</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.005083091091364622</v>
+        <v>3.053839634503674e-07</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.001013159519061446</v>
+        <v>9.058508965154033e-08</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.001951833837665617</v>
+        <v>3.387010494293463e-08</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0005958880065008998</v>
+        <v>1.946910828110049e-07</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.00367978191934526</v>
+        <v>2.44629859480483e-07</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.001180892111733556</v>
+        <v>4.850178214610423e-08</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.001053601736202836</v>
+        <v>5.989330276179317e-08</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0002627726644277573</v>
+        <v>1.528357707059058e-08</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.0005465745343826711</v>
+        <v>1.280664818636978e-08</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.002520151436328888</v>
+        <v>5.097403033005321e-08</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.001265445374883711</v>
+        <v>5.351977350187553e-08</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.000837818079162389</v>
+        <v>1.014185571079906e-07</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.002443644450977445</v>
+        <v>7.56167395365992e-08</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0009018752607516944</v>
+        <v>1.53698209715003e-08</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0006459861760959029</v>
+        <v>2.21466240901691e-08</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0001607284648343921</v>
+        <v>7.495398079981896e-08</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.000745236175134778</v>
+        <v>9.777219389661695e-08</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0009842657018452883</v>
+        <v>1.270612859372022e-08</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.002165340352803469</v>
+        <v>2.654099340304583e-08</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0001064998941728845</v>
+        <v>4.229589478654816e-08</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0003427854389883578</v>
+        <v>3.611250321000625e-08</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.001377993263304234</v>
+        <v>8.920771676912409e-08</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0004168306768406183</v>
+        <v>4.524675745187778e-08</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0006510951789095998</v>
+        <v>1.87719102484607e-08</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.0004693792725447565</v>
+        <v>1.059682119830541e-09</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.0004378045559860766</v>
+        <v>8.85857573962312e-08</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0003323324781376868</v>
+        <v>1.169611074658405e-09</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.002482744865119457</v>
+        <v>1.884814651020861e-07</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0001421968918293715</v>
+        <v>2.478161320595973e-08</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0001446295063942671</v>
+        <v>3.166562123624317e-08</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0004072478041052818</v>
+        <v>2.20927027783091e-08</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.001264384132809937</v>
+        <v>1.533618387838942e-07</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0003775603254325688</v>
+        <v>7.332268125992414e-08</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0005753366858698428</v>
+        <v>2.943633958807368e-08</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.0001485486864112318</v>
+        <v>1.076428723933986e-08</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0003540839825291187</v>
+        <v>1.306593322425442e-08</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.001167292008176446</v>
+        <v>1.08326943859538e-07</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.0001967920397873968</v>
+        <v>1.514751879483356e-08</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0001279547868762165</v>
+        <v>3.50266127213672e-08</v>
       </c>
       <c r="CH12" t="n">
-        <v>3.012424713233486e-05</v>
+        <v>2.461843706669242e-08</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0008558568079024553</v>
+        <v>7.40379562103044e-08</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0002702312194742262</v>
+        <v>2.0707464187808e-08</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.0003981684858445078</v>
+        <v>7.384660105635987e-10</v>
       </c>
       <c r="CL12" t="n">
-        <v>7.701246431679465e-06</v>
+        <v>4.584062196499872e-08</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.00255183270201087</v>
+        <v>5.247941459174399e-08</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0006715792696923018</v>
+        <v>1.378352294523211e-07</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0002910135372076184</v>
+        <v>1.067146797595342e-07</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.001183249056339264</v>
+        <v>4.68585348301076e-08</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0006566887022927403</v>
+        <v>3.143756543977361e-08</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.001080619636923075</v>
+        <v>5.269703251542524e-08</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0009802135173231363</v>
+        <v>5.93469877685493e-08</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0006449413485825062</v>
+        <v>9.503108522324055e-09</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0004991037421859801</v>
+        <v>9.788903021501483e-09</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.0003363955183885992</v>
+        <v>9.997989103283089e-09</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.00104645814280957</v>
+        <v>9.829876290723405e-08</v>
       </c>
       <c r="CX12" t="n">
-        <v>6.914287223480642e-05</v>
+        <v>2.483071881442811e-08</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0002469049941282719</v>
+        <v>4.563590749739888e-08</v>
       </c>
       <c r="CZ12" t="n">
-        <v>6.049539661034942e-05</v>
+        <v>4.735477432404878e-08</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0008570859208703041</v>
+        <v>8.818504682039929e-08</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0002546593605075032</v>
+        <v>3.713935825544468e-08</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0004507899866439402</v>
+        <v>1.050520026524282e-08</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.0001930571452248842</v>
+        <v>3.998847475372713e-08</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.001632809988223016</v>
+        <v>4.988122981330889e-08</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0004715061804745346</v>
+        <v>8.071679502563711e-08</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.0002600600419100374</v>
+        <v>3.505944690118667e-08</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.001501569524407387</v>
+        <v>4.447588608513797e-08</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0002021308027906343</v>
+        <v>6.51153726494158e-08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.001373633043840528</v>
+        <v>9.234815934178187e-08</v>
       </c>
       <c r="DK12" t="n">
-        <v>9.743234841153026e-08</v>
+        <v>1.530180426811967e-08</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.001259628916159272</v>
+        <v>9.38854753940177e-08</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.001335187582299113</v>
+        <v>7.62929186493011e-09</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0001359440211672336</v>
+        <v>6.37711794482243e-09</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0003839803393930197</v>
+        <v>2.560861034339723e-08</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.000814535073004663</v>
+        <v>7.779198618607097e-09</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.002663666848093271</v>
+        <v>3.139085436032474e-08</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.001313087297603488</v>
+        <v>2.262486731297031e-08</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0001725225592963398</v>
+        <v>1.273379712785072e-08</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.000198229230591096</v>
+        <v>9.011660750957162e-08</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0002566143521107733</v>
+        <v>5.635929056779787e-08</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0005171812372282147</v>
+        <v>4.18662509105161e-08</v>
       </c>
       <c r="DW12" t="n">
-        <v>5.310487176757306e-05</v>
+        <v>2.127698550680179e-08</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0008582576410844922</v>
+        <v>9.877270201741339e-08</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0001161369727924466</v>
+        <v>7.591465589484869e-08</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0002302869543200359</v>
+        <v>8.305131871111371e-08</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.001233509392477572</v>
+        <v>3.621390476382658e-08</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.001151537406258285</v>
+        <v>5.722370843841418e-08</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.0002488994505256414</v>
+        <v>3.647692992103657e-08</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0002889263560064137</v>
+        <v>9.406360845787276e-08</v>
       </c>
       <c r="EE12" t="n">
-        <v>2.842633693944663e-05</v>
+        <v>5.953875970021727e-08</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.001264697406440973</v>
+        <v>1.89657392013487e-08</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.001658338005654514</v>
+        <v>2.752996408617037e-08</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.0001882962824311107</v>
+        <v>1.560002260703186e-08</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0005739914486184716</v>
+        <v>7.761560283370272e-10</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0001690010394668207</v>
+        <v>4.707951362092899e-08</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0005958735710009933</v>
+        <v>1.152855588770763e-08</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0003061549505218863</v>
+        <v>3.123194858289935e-08</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0004501124785747379</v>
+        <v>2.318476610696507e-08</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.000346723390975967</v>
+        <v>1.920897219065409e-08</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.000355868338374421</v>
+        <v>2.959968981031125e-08</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0002928676549345255</v>
+        <v>5.79215608809136e-08</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.001050450140610337</v>
+        <v>1.243478742196658e-08</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0003884902398567647</v>
+        <v>6.192179657915631e-09</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0003277328796684742</v>
+        <v>1.355454859464089e-08</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0003662628878373653</v>
+        <v>6.105027949843134e-08</v>
       </c>
       <c r="EU12" t="n">
-        <v>7.843135972507298e-05</v>
+        <v>4.279060661360745e-08</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.002778070047497749</v>
+        <v>6.019311626914714e-08</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.001256402698345482</v>
+        <v>4.271782927389722e-10</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0005436738720163703</v>
+        <v>1.804563787288771e-08</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0009900646982714534</v>
+        <v>1.091176642376013e-07</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.0002444629790261388</v>
+        <v>1.227298973560664e-08</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0002059210673905909</v>
+        <v>4.505645279095916e-08</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0004942386294715106</v>
+        <v>9.972763059806766e-09</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0008627443457953632</v>
+        <v>6.832487997598946e-08</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0001135513448389247</v>
+        <v>1.86545001668037e-08</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0001590434549143538</v>
+        <v>7.76737341112721e-09</v>
       </c>
       <c r="FF12" t="n">
-        <v>8.92682874109596e-05</v>
+        <v>1.941824834261752e-08</v>
       </c>
       <c r="FG12" t="n">
-        <v>8.33957819850184e-05</v>
+        <v>1.240603708652088e-08</v>
       </c>
       <c r="FH12" t="n">
-        <v>9.885837062029168e-05</v>
+        <v>3.681625315721249e-08</v>
       </c>
       <c r="FI12" t="n">
-        <v>4.790886305272579e-05</v>
+        <v>4.421047350433582e-08</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.002238084562122822</v>
+        <v>1.968555451981047e-08</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0005126415635459125</v>
+        <v>1.894352408271516e-08</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0008931225165724754</v>
+        <v>1.134350924303362e-07</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0006780716357752681</v>
+        <v>1.300404939286182e-08</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.0008817151538096368</v>
+        <v>7.395114209884923e-08</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.001317694899626076</v>
+        <v>1.333173145212641e-07</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.001853187219239771</v>
+        <v>3.611677001913449e-08</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0007039314950816333</v>
+        <v>5.08958208911281e-08</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.001124956761486828</v>
+        <v>7.793482836859766e-08</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0005584921455010772</v>
+        <v>3.548140270481781e-08</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.001303266966715455</v>
+        <v>2.249481667604414e-08</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.001111521618440747</v>
+        <v>1.418826833798903e-08</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.0001459035993320867</v>
+        <v>4.882438275899403e-08</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0009338118834421039</v>
+        <v>1.932281890049126e-08</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.0005038903909735382</v>
+        <v>3.785625324326247e-08</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.001432651886716485</v>
+        <v>2.502523521741296e-08</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.001031813328154385</v>
+        <v>4.824924459967406e-08</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0003561936318874359</v>
+        <v>8.455968725229468e-08</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.000401912082452327</v>
+        <v>1.983940123295724e-09</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.0005214640405029058</v>
+        <v>1.34343821400762e-07</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0004423074133228511</v>
+        <v>1.12465485813118e-07</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.000208672572625801</v>
+        <v>9.527592226277193e-08</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.0001535575138404965</v>
+        <v>4.646082629733428e-08</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0002089977060677484</v>
+        <v>7.329588047610969e-09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3.486855462142557e-07</v>
+        <v>7.622990239042338e-09</v>
       </c>
       <c r="B13" t="n">
-        <v>3.37102210323792e-06</v>
+        <v>4.34086686595947e-08</v>
       </c>
       <c r="C13" t="n">
-        <v>4.383126679385896e-07</v>
+        <v>2.873870030839498e-09</v>
       </c>
       <c r="D13" t="n">
-        <v>1.800467316570575e-06</v>
+        <v>2.675679944275089e-08</v>
       </c>
       <c r="E13" t="n">
-        <v>1.096239770959073e-06</v>
+        <v>1.088025314288643e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>7.305999361051363e-07</v>
+        <v>2.777496277417413e-08</v>
       </c>
       <c r="G13" t="n">
-        <v>1.425886750894279e-07</v>
+        <v>8.464935419283393e-09</v>
       </c>
       <c r="H13" t="n">
-        <v>8.040737498049566e-08</v>
+        <v>1.212655931226436e-08</v>
       </c>
       <c r="I13" t="n">
-        <v>1.168558156905419e-07</v>
+        <v>4.165592315530375e-10</v>
       </c>
       <c r="J13" t="n">
-        <v>7.129963250918081e-07</v>
+        <v>2.566828416483702e-10</v>
       </c>
       <c r="K13" t="n">
-        <v>2.699019432839123e-06</v>
+        <v>4.196547109813764e-08</v>
       </c>
       <c r="L13" t="n">
-        <v>1.536121203571383e-07</v>
+        <v>6.762255644332527e-09</v>
       </c>
       <c r="M13" t="n">
-        <v>1.395177719132334e-06</v>
+        <v>4.315975132840322e-08</v>
       </c>
       <c r="N13" t="n">
-        <v>1.07572088836605e-06</v>
+        <v>2.658659425947008e-08</v>
       </c>
       <c r="O13" t="n">
-        <v>1.098164943869051e-06</v>
+        <v>2.674938848201691e-08</v>
       </c>
       <c r="P13" t="n">
-        <v>2.860170980056864e-07</v>
+        <v>4.273351450478913e-09</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.966700769022282e-07</v>
+        <v>6.279659903185575e-09</v>
       </c>
       <c r="R13" t="n">
-        <v>1.508006306494281e-07</v>
+        <v>5.301561412096589e-10</v>
       </c>
       <c r="S13" t="n">
-        <v>2.21860148030828e-08</v>
+        <v>1.859037701557043e-09</v>
       </c>
       <c r="T13" t="n">
-        <v>5.085520342618111e-07</v>
+        <v>5.42124567459723e-09</v>
       </c>
       <c r="U13" t="n">
-        <v>9.131099432124756e-08</v>
+        <v>1.102162983102062e-08</v>
       </c>
       <c r="V13" t="n">
-        <v>2.471902007528115e-07</v>
+        <v>2.205927440712685e-09</v>
       </c>
       <c r="W13" t="n">
-        <v>3.844947968900669e-07</v>
+        <v>6.802561181018518e-09</v>
       </c>
       <c r="X13" t="n">
-        <v>3.120880194273923e-07</v>
+        <v>7.256775624853162e-09</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.479652773170528e-07</v>
+        <v>1.190695098074457e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.526058662828291e-07</v>
+        <v>7.202507923409485e-09</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.954508542847179e-07</v>
+        <v>3.745893817352908e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.725950085074146e-07</v>
+        <v>3.730699749127098e-09</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.068702684709933e-07</v>
+        <v>7.620571729205494e-09</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.889001310928506e-08</v>
+        <v>1.503097646349261e-09</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.177216771315216e-07</v>
+        <v>1.047255704378358e-08</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.269910399059881e-07</v>
+        <v>5.774101641264906e-09</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.913726149245122e-08</v>
+        <v>1.573089924988835e-08</v>
       </c>
       <c r="AH13" t="n">
-        <v>8.1249062588995e-08</v>
+        <v>2.608744553711517e-09</v>
       </c>
       <c r="AI13" t="n">
-        <v>9.282912571961788e-08</v>
+        <v>1.496614920881711e-08</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5.075143860722164e-08</v>
+        <v>1.895213541658336e-09</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.628021545409865e-07</v>
+        <v>3.506537948894106e-09</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.394475302480714e-07</v>
+        <v>8.7997182873778e-09</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.15759902996615e-07</v>
+        <v>1.256827975026908e-08</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.024411204753051e-07</v>
+        <v>9.903440734149171e-09</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.562897580242861e-07</v>
+        <v>3.90390031412835e-09</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.115988451123485e-07</v>
+        <v>4.526158559059468e-09</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.966137688214076e-07</v>
+        <v>3.022024186449812e-09</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.323638088024381e-09</v>
+        <v>7.323437412054545e-10</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.446553253321326e-07</v>
+        <v>4.013829268956215e-09</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.039165908878203e-08</v>
+        <v>1.220981538097021e-09</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.097658125421731e-06</v>
+        <v>2.956311107027432e-08</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.382808250127709e-07</v>
+        <v>1.911674907262295e-08</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.123452015392104e-07</v>
+        <v>8.349654301298415e-11</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.978816754899526e-07</v>
+        <v>3.747460652903101e-08</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.552070472143896e-08</v>
+        <v>2.283236533173749e-08</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.146400236962108e-07</v>
+        <v>1.947961791870512e-09</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.039211833311128e-07</v>
+        <v>4.422819444016568e-09</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.985597973292897e-07</v>
+        <v>1.526578863320083e-09</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.678528403521341e-07</v>
+        <v>2.722862824100503e-09</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.650500725096208e-07</v>
+        <v>1.472316668582607e-08</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.041157795763866e-07</v>
+        <v>1.382697512042341e-09</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.785530336448574e-07</v>
+        <v>1.028201346287005e-08</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.288938258578128e-07</v>
+        <v>2.54728718118713e-08</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.640301654035284e-07</v>
+        <v>2.159173284610461e-09</v>
       </c>
       <c r="BI13" t="n">
-        <v>7.66524976825167e-08</v>
+        <v>2.153273781502207e-09</v>
       </c>
       <c r="BJ13" t="n">
-        <v>4.841481882067455e-07</v>
+        <v>1.283816253305758e-08</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.790380359054325e-08</v>
+        <v>2.968508550083016e-09</v>
       </c>
       <c r="BL13" t="n">
-        <v>3.410564488603995e-07</v>
+        <v>2.698921086619066e-10</v>
       </c>
       <c r="BM13" t="n">
-        <v>5.737390438298462e-07</v>
+        <v>6.452510969978675e-09</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.043017156618589e-07</v>
+        <v>5.512919010186579e-10</v>
       </c>
       <c r="BO13" t="n">
-        <v>2.601579396355191e-09</v>
+        <v>8.147354790821737e-09</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.665173042259994e-07</v>
+        <v>1.352398015797007e-08</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.267776153530576e-07</v>
+        <v>8.935349127270342e-10</v>
       </c>
       <c r="BR13" t="n">
-        <v>8.586445687797095e-08</v>
+        <v>3.81457088138859e-09</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.256426855889003e-07</v>
+        <v>4.593839530997457e-09</v>
       </c>
       <c r="BT13" t="n">
-        <v>1.424093909463409e-07</v>
+        <v>1.917372705051434e-09</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.523650183798964e-08</v>
+        <v>3.317933705559994e-10</v>
       </c>
       <c r="BV13" t="n">
-        <v>1.077312845154665e-06</v>
+        <v>1.301810037546147e-08</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.273441843200999e-07</v>
+        <v>1.059578735862488e-08</v>
       </c>
       <c r="BX13" t="n">
-        <v>2.092671422815329e-07</v>
+        <v>5.060167396209181e-09</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.02492840881041e-08</v>
+        <v>4.79292516786245e-09</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.834625464880446e-07</v>
+        <v>1.156143358826967e-08</v>
       </c>
       <c r="CA13" t="n">
-        <v>2.973126242977742e-07</v>
+        <v>1.106052138766245e-08</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.790385688124843e-08</v>
+        <v>1.31298716343764e-09</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.428860170766711e-07</v>
+        <v>6.149671882837993e-10</v>
       </c>
       <c r="CD13" t="n">
-        <v>1.363624235750649e-08</v>
+        <v>8.113159588596375e-10</v>
       </c>
       <c r="CE13" t="n">
-        <v>5.860130727342039e-07</v>
+        <v>1.344278821591161e-08</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.94285371182923e-07</v>
+        <v>7.226549914030045e-11</v>
       </c>
       <c r="CG13" t="n">
-        <v>1.35297867132067e-07</v>
+        <v>7.801331136647605e-09</v>
       </c>
       <c r="CH13" t="n">
-        <v>7.956799663588754e-08</v>
+        <v>4.458129421180956e-09</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.256850422099888e-07</v>
+        <v>6.667787211256382e-09</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.995044840441551e-08</v>
+        <v>2.626159734120392e-09</v>
       </c>
       <c r="CK13" t="n">
-        <v>2.573024104890465e-08</v>
+        <v>1.608400967967327e-09</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.527613958136499e-07</v>
+        <v>3.614683441455213e-09</v>
       </c>
       <c r="CM13" t="n">
-        <v>3.544433866409236e-07</v>
+        <v>1.352896372708301e-08</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.749220501778836e-07</v>
+        <v>1.935527471630394e-08</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.20833135497378e-07</v>
+        <v>1.906273539020731e-08</v>
       </c>
       <c r="CP13" t="n">
-        <v>5.718293891732174e-07</v>
+        <v>7.463892615078294e-09</v>
       </c>
       <c r="CQ13" t="n">
-        <v>5.444723001346574e-07</v>
+        <v>7.734515250490404e-09</v>
       </c>
       <c r="CR13" t="n">
-        <v>2.159149801173044e-07</v>
+        <v>3.954936822481159e-09</v>
       </c>
       <c r="CS13" t="n">
-        <v>4.390540766507911e-07</v>
+        <v>9.528325684016181e-09</v>
       </c>
       <c r="CT13" t="n">
-        <v>1.282749479969425e-07</v>
+        <v>6.240337135920981e-09</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.846686643602879e-07</v>
+        <v>1.668156279777122e-09</v>
       </c>
       <c r="CV13" t="n">
-        <v>5.130078584159037e-09</v>
+        <v>1.462198473412002e-09</v>
       </c>
       <c r="CW13" t="n">
-        <v>5.343172801985929e-07</v>
+        <v>1.237826285915844e-08</v>
       </c>
       <c r="CX13" t="n">
-        <v>3.297443527117139e-07</v>
+        <v>9.062187666941668e-10</v>
       </c>
       <c r="CY13" t="n">
-        <v>3.031107382867049e-07</v>
+        <v>8.980683752213281e-09</v>
       </c>
       <c r="CZ13" t="n">
-        <v>1.080700826605607e-07</v>
+        <v>6.4492389206805e-09</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.755866717052413e-07</v>
+        <v>7.304571614241695e-09</v>
       </c>
       <c r="DB13" t="n">
-        <v>6.015053344299304e-08</v>
+        <v>3.415426386155218e-09</v>
       </c>
       <c r="DC13" t="n">
-        <v>8.536501638900518e-08</v>
+        <v>2.276328014971796e-09</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.703522798379709e-07</v>
+        <v>3.319804209311883e-09</v>
       </c>
       <c r="DE13" t="n">
-        <v>2.410640433936351e-07</v>
+        <v>7.960757386626938e-09</v>
       </c>
       <c r="DF13" t="n">
-        <v>4.225463499096804e-07</v>
+        <v>1.115303627230446e-09</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.939833052550966e-07</v>
+        <v>5.708736150467075e-09</v>
       </c>
       <c r="DH13" t="n">
-        <v>1.136462856266007e-06</v>
+        <v>9.901438779991167e-09</v>
       </c>
       <c r="DI13" t="n">
-        <v>2.80054308632316e-07</v>
+        <v>3.728257258472922e-09</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.138136494522769e-07</v>
+        <v>1.623354073387873e-08</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.009986985740397e-07</v>
+        <v>5.630588773009038e-10</v>
       </c>
       <c r="DL13" t="n">
-        <v>1.046619928501968e-07</v>
+        <v>1.4159809325065e-08</v>
       </c>
       <c r="DM13" t="n">
-        <v>2.036426707263672e-07</v>
+        <v>7.350846598086491e-09</v>
       </c>
       <c r="DN13" t="n">
-        <v>5.577982165050344e-08</v>
+        <v>1.263070759094376e-09</v>
       </c>
       <c r="DO13" t="n">
-        <v>4.050960455970198e-07</v>
+        <v>9.056631000703419e-09</v>
       </c>
       <c r="DP13" t="n">
-        <v>1.33250651401795e-07</v>
+        <v>8.51249626343531e-10</v>
       </c>
       <c r="DQ13" t="n">
-        <v>1.527248230104306e-07</v>
+        <v>9.56478896085855e-10</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.585242407983969e-08</v>
+        <v>2.506568952398425e-09</v>
       </c>
       <c r="DS13" t="n">
-        <v>2.751450622895391e-09</v>
+        <v>3.925690883477273e-09</v>
       </c>
       <c r="DT13" t="n">
-        <v>1.724729514762657e-07</v>
+        <v>7.963639525598865e-09</v>
       </c>
       <c r="DU13" t="n">
-        <v>5.356073984330578e-08</v>
+        <v>8.651723781838427e-09</v>
       </c>
       <c r="DV13" t="n">
-        <v>3.168753721638495e-07</v>
+        <v>1.612639577430741e-09</v>
       </c>
       <c r="DW13" t="n">
-        <v>2.411449600003834e-07</v>
+        <v>8.308310706084399e-10</v>
       </c>
       <c r="DX13" t="n">
-        <v>2.02566681650751e-07</v>
+        <v>5.066346009385825e-09</v>
       </c>
       <c r="DY13" t="n">
-        <v>4.319010429298942e-07</v>
+        <v>1.091362467064982e-08</v>
       </c>
       <c r="DZ13" t="n">
-        <v>1.980674824153539e-08</v>
+        <v>9.069819562057546e-09</v>
       </c>
       <c r="EA13" t="n">
-        <v>4.372738970914725e-08</v>
+        <v>5.954189141732513e-09</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.753650025193565e-07</v>
+        <v>9.011820623072708e-09</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.220195713358407e-07</v>
+        <v>2.180401414975108e-09</v>
       </c>
       <c r="ED13" t="n">
-        <v>3.498376699440087e-09</v>
+        <v>1.311132891146372e-08</v>
       </c>
       <c r="EE13" t="n">
-        <v>7.316133121548773e-08</v>
+        <v>3.401628534405177e-09</v>
       </c>
       <c r="EF13" t="n">
-        <v>1.55804855239694e-07</v>
+        <v>2.551445277276798e-09</v>
       </c>
       <c r="EG13" t="n">
-        <v>4.725147562112397e-07</v>
+        <v>3.265534509466761e-09</v>
       </c>
       <c r="EH13" t="n">
-        <v>2.881625391637499e-07</v>
+        <v>5.286200366327876e-09</v>
       </c>
       <c r="EI13" t="n">
-        <v>9.793629374144075e-08</v>
+        <v>5.60369617375045e-09</v>
       </c>
       <c r="EJ13" t="n">
-        <v>2.095224687082009e-07</v>
+        <v>6.233616289819111e-09</v>
       </c>
       <c r="EK13" t="n">
-        <v>2.010115167649928e-07</v>
+        <v>6.187306667015946e-09</v>
       </c>
       <c r="EL13" t="n">
-        <v>1.011128958339214e-07</v>
+        <v>3.990300090350729e-09</v>
       </c>
       <c r="EM13" t="n">
-        <v>2.506380702982369e-08</v>
+        <v>1.080882050530363e-09</v>
       </c>
       <c r="EN13" t="n">
-        <v>9.857676985802755e-08</v>
+        <v>1.285288542263174e-09</v>
       </c>
       <c r="EO13" t="n">
-        <v>8.832962805627176e-08</v>
+        <v>1.045740605221113e-09</v>
       </c>
       <c r="EP13" t="n">
-        <v>2.42328411559356e-07</v>
+        <v>5.947674797113223e-09</v>
       </c>
       <c r="EQ13" t="n">
-        <v>4.556753765427857e-07</v>
+        <v>3.71241881680362e-09</v>
       </c>
       <c r="ER13" t="n">
-        <v>1.41860553526385e-07</v>
+        <v>4.562488165049672e-09</v>
       </c>
       <c r="ES13" t="n">
-        <v>2.116461104151313e-07</v>
+        <v>3.406795734406387e-09</v>
       </c>
       <c r="ET13" t="n">
-        <v>3.188073094406718e-08</v>
+        <v>1.128565463304199e-09</v>
       </c>
       <c r="EU13" t="n">
-        <v>9.818015200835362e-08</v>
+        <v>1.998908594202931e-09</v>
       </c>
       <c r="EV13" t="n">
-        <v>4.733468870199431e-07</v>
+        <v>7.693493841998134e-09</v>
       </c>
       <c r="EW13" t="n">
-        <v>2.250197539410692e-08</v>
+        <v>7.159658643729472e-09</v>
       </c>
       <c r="EX13" t="n">
-        <v>6.028346888342639e-08</v>
+        <v>8.224373404530638e-10</v>
       </c>
       <c r="EY13" t="n">
-        <v>5.324162088982121e-07</v>
+        <v>1.412172334624984e-08</v>
       </c>
       <c r="EZ13" t="n">
-        <v>2.669382297426637e-07</v>
+        <v>8.283674857167966e-10</v>
       </c>
       <c r="FA13" t="n">
-        <v>1.823477759899106e-07</v>
+        <v>9.598315031666971e-09</v>
       </c>
       <c r="FB13" t="n">
-        <v>9.769066622311584e-08</v>
+        <v>2.358808259828038e-09</v>
       </c>
       <c r="FC13" t="n">
-        <v>2.471676054938143e-07</v>
+        <v>5.670834912763212e-09</v>
       </c>
       <c r="FD13" t="n">
-        <v>8.326153988491569e-08</v>
+        <v>1.230767043836067e-09</v>
       </c>
       <c r="FE13" t="n">
-        <v>3.003509618793032e-08</v>
+        <v>3.465477682595974e-09</v>
       </c>
       <c r="FF13" t="n">
-        <v>2.684807896002894e-07</v>
+        <v>8.044525601214048e-10</v>
       </c>
       <c r="FG13" t="n">
-        <v>2.948289363757794e-07</v>
+        <v>1.944781002904961e-09</v>
       </c>
       <c r="FH13" t="n">
-        <v>2.964027245866419e-08</v>
+        <v>6.508666050564216e-09</v>
       </c>
       <c r="FI13" t="n">
-        <v>4.243798628067452e-07</v>
+        <v>6.620942016866138e-09</v>
       </c>
       <c r="FJ13" t="n">
-        <v>3.620421864525269e-07</v>
+        <v>6.443571898273603e-09</v>
       </c>
       <c r="FK13" t="n">
-        <v>1.579079444979925e-08</v>
+        <v>1.298633089952261e-09</v>
       </c>
       <c r="FL13" t="n">
-        <v>3.563259838301747e-07</v>
+        <v>1.8896348930042e-09</v>
       </c>
       <c r="FM13" t="n">
-        <v>2.701854384667968e-08</v>
+        <v>1.046408792948483e-10</v>
       </c>
       <c r="FN13" t="n">
-        <v>4.110903830678581e-07</v>
+        <v>4.738029968365254e-10</v>
       </c>
       <c r="FO13" t="n">
-        <v>1.647045877462006e-07</v>
+        <v>1.001083393958879e-08</v>
       </c>
       <c r="FP13" t="n">
-        <v>1.101380320278622e-07</v>
+        <v>6.398905849636094e-09</v>
       </c>
       <c r="FQ13" t="n">
-        <v>1.515033147825307e-07</v>
+        <v>1.479476363641652e-08</v>
       </c>
       <c r="FR13" t="n">
-        <v>1.864830068143419e-07</v>
+        <v>1.403923288734177e-08</v>
       </c>
       <c r="FS13" t="n">
-        <v>1.949380532551004e-07</v>
+        <v>5.043536255300296e-09</v>
       </c>
       <c r="FT13" t="n">
-        <v>4.180322150659777e-07</v>
+        <v>1.902086843585948e-08</v>
       </c>
       <c r="FU13" t="n">
-        <v>2.339749016755377e-07</v>
+        <v>3.541518855953996e-09</v>
       </c>
       <c r="FV13" t="n">
-        <v>2.668860688004315e-08</v>
+        <v>1.127761439789765e-08</v>
       </c>
       <c r="FW13" t="n">
-        <v>2.886663139634038e-07</v>
+        <v>4.779230344809093e-09</v>
       </c>
       <c r="FX13" t="n">
-        <v>2.961237157705909e-07</v>
+        <v>4.585875235108006e-09</v>
       </c>
       <c r="FY13" t="n">
-        <v>6.741734068782534e-07</v>
+        <v>9.998478711636949e-10</v>
       </c>
       <c r="FZ13" t="n">
-        <v>1.04438242942706e-07</v>
+        <v>2.940727661382425e-10</v>
       </c>
       <c r="GA13" t="n">
-        <v>1.516102088316984e-07</v>
+        <v>1.13226654718801e-08</v>
       </c>
       <c r="GB13" t="n">
-        <v>7.387743750086884e-08</v>
+        <v>6.963317478181352e-09</v>
       </c>
       <c r="GC13" t="n">
-        <v>2.936281475740543e-07</v>
+        <v>1.223960488516695e-08</v>
       </c>
       <c r="GD13" t="n">
-        <v>2.773087715013389e-07</v>
+        <v>1.756561474053342e-08</v>
       </c>
       <c r="GE13" t="n">
-        <v>7.562042014797044e-07</v>
+        <v>1.217743061943111e-08</v>
       </c>
       <c r="GF13" t="n">
-        <v>1.701233571793637e-07</v>
+        <v>4.73887151741792e-10</v>
       </c>
       <c r="GG13" t="n">
-        <v>2.910508953846147e-07</v>
+        <v>3.37366523606164e-10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0002374263131059706</v>
+        <v>3.536713484209031e-05</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002523765899240971</v>
+        <v>8.004491974133998e-05</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0003460117732174695</v>
+        <v>0.0001535841001896188</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002188677899539471</v>
+        <v>8.259585592895746e-05</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0006042835884727538</v>
+        <v>0.0003356907109264284</v>
       </c>
       <c r="F14" t="n">
-        <v>0.004816655535250902</v>
+        <v>0.0006798270624130964</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001463473308831453</v>
+        <v>0.0001741002197377384</v>
       </c>
       <c r="H14" t="n">
-        <v>0.003200932405889034</v>
+        <v>0.0003661515365820378</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0006251570302993059</v>
+        <v>5.967128527117893e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0003996531304437667</v>
+        <v>5.735081867896952e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.002777280518785119</v>
+        <v>0.0001949799043359235</v>
       </c>
       <c r="L14" t="n">
-        <v>0.000243763264734298</v>
+        <v>0.0002673450508154929</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0007626391598023474</v>
+        <v>0.0001009530751616694</v>
       </c>
       <c r="N14" t="n">
-        <v>0.001703612972050905</v>
+        <v>0.0004315541591495275</v>
       </c>
       <c r="O14" t="n">
-        <v>0.004250139929354191</v>
+        <v>0.0008789892890490592</v>
       </c>
       <c r="P14" t="n">
-        <v>0.002046583220362663</v>
+        <v>0.0002961776335723698</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.000573975732550025</v>
+        <v>0.0004860341432504356</v>
       </c>
       <c r="R14" t="n">
-        <v>0.001351870014332235</v>
+        <v>0.0002380883379373699</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0001588760642334819</v>
+        <v>4.317770799389109e-05</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0005583931342698634</v>
+        <v>4.084821193828247e-05</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0005288562970235944</v>
+        <v>8.972250361694023e-05</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0005930119077675045</v>
+        <v>1.594479908817448e-05</v>
       </c>
       <c r="W14" t="n">
-        <v>0.001058021909557283</v>
+        <v>1.464704200770939e-05</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0006622343207709491</v>
+        <v>0.0001026735990308225</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.553639054298401e-05</v>
+        <v>7.31328982510604e-05</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.000158166978508234</v>
+        <v>4.661109778680839e-05</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0002394411567365751</v>
+        <v>1.825333310989663e-05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0008470246102660894</v>
+        <v>2.438157025608234e-06</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.000124843863886781</v>
+        <v>7.775596168357879e-05</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0001788462104741484</v>
+        <v>3.61161983164493e-05</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0001769242517184466</v>
+        <v>7.253344665514305e-05</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0003467600618023425</v>
+        <v>7.274458039319143e-05</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0006321848486550152</v>
+        <v>4.309321229811758e-05</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0003640481154434383</v>
+        <v>7.87031021900475e-05</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0004849391989409924</v>
+        <v>8.500400872435421e-05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0009250554139725864</v>
+        <v>2.692204361665063e-05</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0006574410945177078</v>
+        <v>0.0001002637000055984</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0004799373564310372</v>
+        <v>2.103913720929995e-05</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0004169661551713943</v>
+        <v>2.685111394384876e-05</v>
       </c>
       <c r="AN14" t="n">
-        <v>5.041412077844143e-05</v>
+        <v>8.017949585337192e-05</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0006322961417026818</v>
+        <v>7.191600275291421e-07</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.001254020258784294</v>
+        <v>9.94370348053053e-05</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.419774970505387e-05</v>
+        <v>8.023760528885759e-06</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0009345617727376521</v>
+        <v>7.516691766795702e-06</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.382798993494362e-05</v>
+        <v>1.271848850592505e-05</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.00133896095212549</v>
+        <v>0.0001648286415729672</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.001851633074693382</v>
+        <v>0.0004914276651106775</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.0005236744182184339</v>
+        <v>4.714621900347993e-05</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0005071128834970295</v>
+        <v>0.0001660771522438154</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0009627314284443855</v>
+        <v>5.472098200698383e-05</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0008339757332578301</v>
+        <v>0.0005048660677857697</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0004255651438143104</v>
+        <v>0.0001200150509248488</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.002254186663776636</v>
+        <v>0.0002228279045084491</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0005258105229586363</v>
+        <v>4.073017771588638e-05</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0001176719088107347</v>
+        <v>0.0001785686472430825</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.314834460383281e-05</v>
+        <v>0.0002262309426441789</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0004109768487978727</v>
+        <v>8.140466525219381e-05</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.000911257229745388</v>
+        <v>0.0002412859757896513</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0007379283779300749</v>
+        <v>0.0001291252119699493</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.002582289278507233</v>
+        <v>4.225437442073599e-05</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.00106522417627275</v>
+        <v>4.333393007982522e-06</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0002275377191836014</v>
+        <v>0.000141848431667313</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.0003275170456618071</v>
+        <v>2.306133137608413e-05</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0002722183999139816</v>
+        <v>6.366131856339052e-06</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0004270153003744781</v>
+        <v>0.0002336095203645527</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0005080648115836084</v>
+        <v>0.0002192998363170773</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.001000064774416387</v>
+        <v>0.0001279693678952754</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0002312996075488627</v>
+        <v>0.0001767799403751269</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0006817643297836185</v>
+        <v>0.0001098329012165777</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0001373191480524838</v>
+        <v>6.481049058493227e-05</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0002265449438709766</v>
+        <v>0.000137152019306086</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0006518752197735012</v>
+        <v>7.274840754689649e-05</v>
       </c>
       <c r="BU14" t="n">
-        <v>8.5296924225986e-06</v>
+        <v>2.764840246527456e-06</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0008066978771239519</v>
+        <v>0.0001869990810519084</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0004031300195492804</v>
+        <v>5.393014725996181e-05</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0002244158677058294</v>
+        <v>0.0001464225351810455</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0005352637963369489</v>
+        <v>4.493425876717083e-06</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0003775343939196318</v>
+        <v>0.0002879155217669904</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0001672197395237163</v>
+        <v>8.057444210862741e-05</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.0007883792277425528</v>
+        <v>0.0001059191708918661</v>
       </c>
       <c r="CC14" t="n">
-        <v>8.522278949385509e-05</v>
+        <v>2.641686842252966e-05</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0001839088363340124</v>
+        <v>1.285624330193968e-05</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0002978660340886563</v>
+        <v>9.325181963504292e-06</v>
       </c>
       <c r="CF14" t="n">
-        <v>5.064087599748746e-05</v>
+        <v>4.31358021160122e-05</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0006833364022895694</v>
+        <v>4.639657709049061e-05</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.000147166836541146</v>
+        <v>0.0001198937170556746</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.000535413739271462</v>
+        <v>0.0001830298569984734</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.000564145331736654</v>
+        <v>6.446614133892581e-05</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0003423955058678985</v>
+        <v>1.244331997440895e-05</v>
       </c>
       <c r="CL14" t="n">
-        <v>4.264155722921714e-05</v>
+        <v>1.615829387446865e-05</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0004811579128727317</v>
+        <v>1.352930121356621e-05</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0005449388409033418</v>
+        <v>9.655015310272574e-05</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0003529594978317618</v>
+        <v>3.041016680072062e-05</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0005751105491071939</v>
+        <v>4.725948019768111e-05</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0004386866639833897</v>
+        <v>5.079476977698505e-05</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0005922384443692863</v>
+        <v>1.940885704243556e-05</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0005958392866887152</v>
+        <v>0.0002060307888314128</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0001157633378170431</v>
+        <v>5.633623004541732e-06</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0006480521988123655</v>
+        <v>7.650619227206334e-05</v>
       </c>
       <c r="CV14" t="n">
-        <v>5.128400516696274e-06</v>
+        <v>2.081884122162592e-05</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0003171322168782353</v>
+        <v>5.660887836711481e-06</v>
       </c>
       <c r="CX14" t="n">
-        <v>8.643584442324936e-05</v>
+        <v>5.998661799822003e-05</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0005202259635552764</v>
+        <v>5.367157427826896e-05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>8.171143417712301e-05</v>
+        <v>0.0001547609135741368</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0007643777644261718</v>
+        <v>0.0001929941645357758</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0005306777893565595</v>
+        <v>4.137145879212767e-05</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0004559509106911719</v>
+        <v>3.345413279021159e-05</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.0002781941439025104</v>
+        <v>1.823922139010392e-05</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0002536923857405782</v>
+        <v>0.0001674101804383099</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.001410113763995469</v>
+        <v>0.0001728689094306901</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0003748437447939068</v>
+        <v>7.181371620390564e-05</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.00250391848385334</v>
+        <v>7.110319711500779e-05</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.002306014765053988</v>
+        <v>5.843195322086103e-05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.002508270787075162</v>
+        <v>2.225046227977145e-05</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.0008905349532142282</v>
+        <v>8.026675641303882e-05</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.000589547271374613</v>
+        <v>5.151485675014555e-05</v>
       </c>
       <c r="DM14" t="n">
-        <v>2.202227915404364e-05</v>
+        <v>0.0001843033824115992</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0001258950505871326</v>
+        <v>2.482124546077102e-05</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0003459297586232424</v>
+        <v>0.000123260062537156</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0002413007750874385</v>
+        <v>4.827315933653153e-05</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0004977022181265056</v>
+        <v>4.734788672067225e-05</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.001316178473643959</v>
+        <v>9.828170004766434e-05</v>
       </c>
       <c r="DS14" t="n">
-        <v>4.982216341886669e-05</v>
+        <v>0.000134802030515857</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.002067752182483673</v>
+        <v>7.160114910220727e-05</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0001394618884660304</v>
+        <v>6.149217369966209e-06</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0005294250440783799</v>
+        <v>0.0001566044229548424</v>
       </c>
       <c r="DW14" t="n">
-        <v>3.171380376443267e-05</v>
+        <v>3.872344677802175e-05</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0007866026135161519</v>
+        <v>0.000130785585497506</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0008642965694889426</v>
+        <v>0.0001030025450745597</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0001841109478846192</v>
+        <v>5.555835377890617e-05</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.001123781083151698</v>
+        <v>1.943913730428903e-06</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.0004651288036257029</v>
+        <v>4.717341653304175e-06</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0002627804933581501</v>
+        <v>3.142202695016749e-05</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0004793237894773483</v>
+        <v>7.468306284863502e-05</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0003271734167356044</v>
+        <v>6.607295654248446e-05</v>
       </c>
       <c r="EF14" t="n">
-        <v>5.537563993129879e-06</v>
+        <v>7.822154657333158e-06</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0004119369550608099</v>
+        <v>1.919505848491099e-05</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.0002147125196643174</v>
+        <v>6.063091495889239e-05</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0003417374973651022</v>
+        <v>0.0001724446337902918</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0002356767363380641</v>
+        <v>0.0001123829424614087</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.001204285537824035</v>
+        <v>8.763093501329422e-05</v>
       </c>
       <c r="EL14" t="n">
-        <v>9.466413757763803e-05</v>
+        <v>7.133444887585938e-05</v>
       </c>
       <c r="EM14" t="n">
-        <v>7.515001925639808e-06</v>
+        <v>5.058827809989452e-05</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.000338839105097577</v>
+        <v>1.166488982562441e-05</v>
       </c>
       <c r="EO14" t="n">
-        <v>7.652854401385412e-05</v>
+        <v>5.489774775924161e-05</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0003263507387600839</v>
+        <v>4.888414332526736e-05</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0001466195972170681</v>
+        <v>1.482365587435197e-05</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.00075849040877074</v>
+        <v>8.788793638814241e-05</v>
       </c>
       <c r="ES14" t="n">
-        <v>9.513692202745005e-05</v>
+        <v>0.0002403232647338882</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0006495980196632445</v>
+        <v>0.0001614855427760631</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0007080381619744003</v>
+        <v>0.0001270393113372847</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.000728482031263411</v>
+        <v>6.724899139953777e-05</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.0007874618750065565</v>
+        <v>2.257886808365583e-05</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.0001516962074674666</v>
+        <v>3.531545371515676e-05</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0002138304407708347</v>
+        <v>7.375127097475342e-06</v>
       </c>
       <c r="EZ14" t="n">
-        <v>8.600180444773287e-05</v>
+        <v>3.295619535492733e-05</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0005733727593906224</v>
+        <v>4.29756473749876e-05</v>
       </c>
       <c r="FB14" t="n">
-        <v>4.029960837215185e-05</v>
+        <v>0.0001080694710253738</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0006617263425141573</v>
+        <v>0.000200675698579289</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0005867599393241107</v>
+        <v>8.700444595888257e-05</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0004496744659263641</v>
+        <v>1.3685039448319e-05</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0002919729449786246</v>
+        <v>7.902704965090379e-06</v>
       </c>
       <c r="FG14" t="n">
-        <v>2.328273694729432e-05</v>
+        <v>4.87598663312383e-05</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.001262950128875673</v>
+        <v>3.312230182928033e-05</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0007431039121001959</v>
+        <v>1.592427361174487e-05</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0008654854027554393</v>
+        <v>5.177025741431862e-05</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.000488457502797246</v>
+        <v>9.471010707784444e-05</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0002679043100215495</v>
+        <v>8.030453318497166e-05</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.0002883840352296829</v>
+        <v>3.330559411551803e-05</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0006282557733356953</v>
+        <v>8.684706699568778e-05</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0003989133110735565</v>
+        <v>0.000107356856460683</v>
       </c>
       <c r="FP14" t="n">
-        <v>1.369020537822507e-05</v>
+        <v>3.857161937048659e-05</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.001081103808246553</v>
+        <v>0.0002212078252341598</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.001842471654526889</v>
+        <v>9.641135693527758e-05</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.0002384409017395228</v>
+        <v>9.407616744283587e-05</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.001955617219209671</v>
+        <v>0.0003652125305961818</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0004704095190390944</v>
+        <v>6.807248428231105e-05</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0003462505992501974</v>
+        <v>1.988055009860545e-05</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.001882411888800561</v>
+        <v>3.485186607576907e-05</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0001665577001404017</v>
+        <v>0.0001458157785236835</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0001139307714765891</v>
+        <v>3.628025660873391e-05</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0002783000818453729</v>
+        <v>5.728390169679187e-05</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0004884188529103994</v>
+        <v>0.0001807317603379488</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0003703508118633181</v>
+        <v>2.024697096203454e-05</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.002002417808398604</v>
+        <v>9.35668867896311e-05</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0007123156683519483</v>
+        <v>2.699888682400342e-05</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.00113112828694284</v>
+        <v>0.0001951691374415532</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0005986580508761108</v>
+        <v>0.0001032701402436942</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0007440397748723626</v>
+        <v>2.813734226947417e-06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.0004118129727430642</v>
+        <v>0.1085646823048592</v>
       </c>
       <c r="B15" t="n">
-        <v>0.007756754290312529</v>
+        <v>1.021109223365784</v>
       </c>
       <c r="C15" t="n">
-        <v>0.000422396813519299</v>
+        <v>0.0380321741104126</v>
       </c>
       <c r="D15" t="n">
-        <v>0.003180555999279022</v>
+        <v>0.2766221761703491</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0007339577423408628</v>
+        <v>0.5042160749435425</v>
       </c>
       <c r="F15" t="n">
-        <v>0.005864545237272978</v>
+        <v>0.8180153369903564</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0005485326983034611</v>
+        <v>0.4130997359752655</v>
       </c>
       <c r="H15" t="n">
-        <v>0.002456562127918005</v>
+        <v>1.146449446678162</v>
       </c>
       <c r="I15" t="n">
-        <v>4.051224823342636e-05</v>
+        <v>0.2431680858135223</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001661615213379264</v>
+        <v>0.05473300814628601</v>
       </c>
       <c r="K15" t="n">
-        <v>0.006437366362661123</v>
+        <v>1.200941681861877</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0003637332993093878</v>
+        <v>0.2245233952999115</v>
       </c>
       <c r="M15" t="n">
-        <v>0.003352949395775795</v>
+        <v>0.5455113649368286</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0003611576976254582</v>
+        <v>1.439121603965759</v>
       </c>
       <c r="O15" t="n">
-        <v>0.005545507650822401</v>
+        <v>0.9781197905540466</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0008413924952037632</v>
+        <v>0.2848686575889587</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0008144238963723183</v>
+        <v>0.9392232298851013</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0007833329145796597</v>
+        <v>0.3916301131248474</v>
       </c>
       <c r="S15" t="n">
-        <v>5.475504076457582e-05</v>
+        <v>0.165513664484024</v>
       </c>
       <c r="T15" t="n">
-        <v>0.000650558271445334</v>
+        <v>0.2361571788787842</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0003979194443672895</v>
+        <v>0.1088635548949242</v>
       </c>
       <c r="V15" t="n">
-        <v>0.000890272727701813</v>
+        <v>0.4232285618782043</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0009570568799972534</v>
+        <v>0.2461090981960297</v>
       </c>
       <c r="X15" t="n">
-        <v>0.001007641316391528</v>
+        <v>0.1713123321533203</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.00070143339689821</v>
+        <v>0.1142114326357841</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.001104658702388406</v>
+        <v>0.1605732589960098</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.001025261241011322</v>
+        <v>0.001814901828765869</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.624702993780375e-05</v>
+        <v>0.2231440842151642</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.001038017449900508</v>
+        <v>0.3404627442359924</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0003369622281752527</v>
+        <v>0.04554818570613861</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0005372431478463113</v>
+        <v>0.398312121629715</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0003466648049652576</v>
+        <v>0.3626108169555664</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0002582592715043575</v>
+        <v>0.2252554893493652</v>
       </c>
       <c r="AH15" t="n">
-        <v>8.894203347153962e-05</v>
+        <v>0.0117456242442131</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0001163516353699379</v>
+        <v>0.3273480236530304</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0003536911681294441</v>
+        <v>0.2078892439603806</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0007593021146021783</v>
+        <v>0.2858917713165283</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.0008937341626733541</v>
+        <v>0.3595708310604095</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0001060988870449364</v>
+        <v>0.1043777242302895</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.0007511891890317202</v>
+        <v>0.06629832088947296</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0007590733584947884</v>
+        <v>0.1641089767217636</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.001238575205206871</v>
+        <v>0.2006572484970093</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.0003379251284059137</v>
+        <v>0.1019016429781914</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.0003488370857667178</v>
+        <v>0.2288595587015152</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.0009130854159593582</v>
+        <v>0.06344233453273773</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.0009974436834454536</v>
+        <v>0.1046040207147598</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.004815455060452223</v>
+        <v>1.94943368434906</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.0006242240197025239</v>
+        <v>0.04747293144464493</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.0002660881436895579</v>
+        <v>0.2424208074808121</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.000286811264231801</v>
+        <v>0.2319469898939133</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.00390477804467082</v>
+        <v>0.692006528377533</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.001380173140205443</v>
+        <v>0.09056589007377625</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.001135177095420659</v>
+        <v>0.3267459273338318</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.0022151586599648</v>
+        <v>0.1108988374471664</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0009359559044241905</v>
+        <v>0.1551438421010971</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.001637836219742894</v>
+        <v>0.6901437640190125</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.001805179635994136</v>
+        <v>0.05417690798640251</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.001113621750846505</v>
+        <v>0.1597884744405746</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.001551203895360231</v>
+        <v>0.3191340863704681</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.001571945496834815</v>
+        <v>0.1343685388565063</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.00109085557051003</v>
+        <v>0.1235750094056129</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.0009566480293869972</v>
+        <v>0.5315117239952087</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.000576210324652493</v>
+        <v>0.07758221030235291</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.0002434018824715167</v>
+        <v>0.06193191558122635</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.001655094791203737</v>
+        <v>0.2159051299095154</v>
       </c>
       <c r="BN15" t="n">
-        <v>9.593482536729425e-05</v>
+        <v>0.3765617311000824</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0007076783804222941</v>
+        <v>0.09096748381853104</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0002834241895470768</v>
+        <v>0.2167304456233978</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.0005569712375290692</v>
+        <v>0.2079620957374573</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.0003283550904598087</v>
+        <v>0.3243005573749542</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.0002256097504869103</v>
+        <v>0.06044743210077286</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.0009117294102907181</v>
+        <v>0.02010261826217175</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.0004342779866419733</v>
+        <v>0.1891173124313354</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.002745712641626596</v>
+        <v>0.771762490272522</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.0009119783062487841</v>
+        <v>0.03736426681280136</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.000428529514465481</v>
+        <v>0.4022414982318878</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.0001071296428563073</v>
+        <v>0.364467591047287</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.001949265832081437</v>
+        <v>0.3395852446556091</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.259689452126622e-05</v>
+        <v>0.3224305510520935</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0005339424824342132</v>
+        <v>0.2762607038021088</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.001068686367943883</v>
+        <v>0.002202675677835941</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.578006675932556e-05</v>
+        <v>0.04341666027903557</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.001112511847168207</v>
+        <v>0.3388303220272064</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.0007332982495427132</v>
+        <v>0.09429271519184113</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.0004150521417614073</v>
+        <v>0.09824934601783752</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.0001154752681031823</v>
+        <v>0.2175338268280029</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.0008121521095745265</v>
+        <v>0.2301478534936905</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.000508734374307096</v>
+        <v>0.07661724835634232</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.000495127635076642</v>
+        <v>0.03777434676885605</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.0006315935170277953</v>
+        <v>0.01373821124434471</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.0008373979362659156</v>
+        <v>0.27439945936203</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.0005343370139598846</v>
+        <v>0.3903340697288513</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.0001617862144485116</v>
+        <v>0.1826540231704712</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.001126809744164348</v>
+        <v>0.6690869927406311</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.0001454395242035389</v>
+        <v>0.4146171510219574</v>
       </c>
       <c r="CR15" t="n">
-        <v>3.553688293322921e-05</v>
+        <v>0.1685066670179367</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.0009846515022218227</v>
+        <v>0.01544108428061008</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0009280579397454858</v>
+        <v>0.1883959323167801</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.0001371886173728853</v>
+        <v>0.01361189410090446</v>
       </c>
       <c r="CV15" t="n">
-        <v>4.911555879516527e-05</v>
+        <v>0.1226556897163391</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.0009619264164939523</v>
+        <v>0.2987266182899475</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.000802986731287092</v>
+        <v>0.1058980822563171</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.0007353606633841991</v>
+        <v>0.152635931968689</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.0002419349475530908</v>
+        <v>0.2153743952512741</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.0008427781285718083</v>
+        <v>0.301397293806076</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.0004146330174989998</v>
+        <v>0.007592816837131977</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.000859975116327405</v>
+        <v>0.01255198195576668</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.0005196037818677723</v>
+        <v>0.00973116047680378</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.0003694098559208214</v>
+        <v>0.05121967196464539</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.0006494661793112755</v>
+        <v>0.1843187510967255</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.099466655636206e-06</v>
+        <v>0.1124333888292313</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.003101311391219497</v>
+        <v>0.1714845448732376</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0001211488852277398</v>
+        <v>0.5169990062713623</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.002420138800516725</v>
+        <v>0.3893471360206604</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.0006956837605684996</v>
+        <v>0.1140749007463455</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.001732248696498573</v>
+        <v>0.04539894312620163</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.001112361089326441</v>
+        <v>0.07905136048793793</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.0001216532473335974</v>
+        <v>0.1715354770421982</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.0005922499112784863</v>
+        <v>0.1657265722751617</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.0003121623594779521</v>
+        <v>0.098326176404953</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2.654627314768732e-05</v>
+        <v>0.08442283421754837</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.0001113657854148187</v>
+        <v>0.2406525462865829</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.0007385864737443626</v>
+        <v>0.1745487302541733</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.000110156019218266</v>
+        <v>0.1819551587104797</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.0002453447959851474</v>
+        <v>0.05007999390363693</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.0006171002169139683</v>
+        <v>0.342274397611618</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.0001774419797584414</v>
+        <v>0.2002217173576355</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.0001146161885117181</v>
+        <v>0.4021744430065155</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.00085062300786376</v>
+        <v>0.1245522871613503</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.0004332169482950121</v>
+        <v>0.005681239068508148</v>
       </c>
       <c r="EA15" t="n">
-        <v>5.801381485071033e-05</v>
+        <v>0.221304327249527</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.001008750055916607</v>
+        <v>0.04809956252574921</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.0001921435759868473</v>
+        <v>0.01918351277709007</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.0003670227015390992</v>
+        <v>0.2437146157026291</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.00110764498822391</v>
+        <v>0.3440817594528198</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.000315052893711254</v>
+        <v>0.01384299993515015</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0006094678537920117</v>
+        <v>0.243061900138855</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.0005905646248720586</v>
+        <v>0.1441054940223694</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.0002355063916184008</v>
+        <v>0.07424475252628326</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0004622415290214121</v>
+        <v>0.2763164639472961</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.0002024084533331916</v>
+        <v>0.1660359352827072</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.0007599826203659177</v>
+        <v>0.04066352546215057</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.0005760305793955922</v>
+        <v>0.1444746851921082</v>
       </c>
       <c r="EN15" t="n">
-        <v>9.835670061875135e-05</v>
+        <v>0.009055683389306068</v>
       </c>
       <c r="EO15" t="n">
-        <v>4.533008905127645e-05</v>
+        <v>0.1469220221042633</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0005720889312215149</v>
+        <v>0.2221356332302094</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.0009157411986961961</v>
+        <v>0.1697671413421631</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.0002602490421850234</v>
+        <v>0.03646636754274368</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.0005304197547957301</v>
+        <v>0.1545308232307434</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.0001891443971544504</v>
+        <v>0.2529759705066681</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.0008948687463998795</v>
+        <v>0.05733045190572739</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.001614282606169581</v>
+        <v>0.0476473942399025</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.0003199102648068219</v>
+        <v>0.2727341055870056</v>
       </c>
       <c r="EX15" t="n">
-        <v>4.806947254110128e-05</v>
+        <v>0.09276892244815826</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.000984931131824851</v>
+        <v>0.3796289563179016</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.0005924647557549179</v>
+        <v>0.06732019037008286</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.0003447326307650656</v>
+        <v>0.1801110208034515</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.0002935984230134636</v>
+        <v>0.1713873445987701</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.0006848868215456605</v>
+        <v>0.282723605632782</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.0008298109169118106</v>
+        <v>0.09903442114591599</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.0005210612434893847</v>
+        <v>0.03745768964290619</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.0008355280733667314</v>
+        <v>0.03659624978899956</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.0005222597392275929</v>
+        <v>0.05942150950431824</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.0006210406427271664</v>
+        <v>0.1393234729766846</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.000554107129573822</v>
+        <v>0.25556880235672</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.001472773728892207</v>
+        <v>0.2675189971923828</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0001247907057404518</v>
+        <v>0.02069359086453915</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.0006381084676831961</v>
+        <v>0.1761154979467392</v>
       </c>
       <c r="FM15" t="n">
-        <v>8.785462705418468e-05</v>
+        <v>0.3110276758670807</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.0005224636988714337</v>
+        <v>0.1338250935077667</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.0005231930408626795</v>
+        <v>0.3310009837150574</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0006523008341901004</v>
+        <v>0.2161502540111542</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.0003317184746265411</v>
+        <v>0.01737438142299652</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.0006565037765540183</v>
+        <v>0.2100310921669006</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.0008483353885821998</v>
+        <v>0.2516216039657593</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.0004996851203031838</v>
+        <v>0.6156765818595886</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0005580995930358768</v>
+        <v>0.157831221818924</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.0007286160252988338</v>
+        <v>0.1772186458110809</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.0008091498166322708</v>
+        <v>0.451951652765274</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.0008693806594237685</v>
+        <v>0.2549871504306793</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.001355200656689703</v>
+        <v>0.1494167447090149</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.0002858682128135115</v>
+        <v>0.02983042597770691</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.0008948341128416359</v>
+        <v>0.223090648651123</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.0002462587144691497</v>
+        <v>0.1123302578926086</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.0004305460897739977</v>
+        <v>0.1993634104728699</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.0006741653778590262</v>
+        <v>0.04868578910827637</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.002687775762751698</v>
+        <v>0.1820282340049744</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.0008148502092808485</v>
+        <v>0.1069272011518478</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.0003641460789367557</v>
+        <v>0.07218153774738312</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6.467221203010354e-10</v>
+        <v>6.224520898712171e-09</v>
       </c>
       <c r="B16" t="n">
-        <v>5.241297396096911e-10</v>
+        <v>3.433967776800273e-08</v>
       </c>
       <c r="C16" t="n">
-        <v>4.926535290827871e-10</v>
+        <v>7.369573395976659e-09</v>
       </c>
       <c r="D16" t="n">
-        <v>5.327869256888107e-10</v>
+        <v>1.504720259504211e-08</v>
       </c>
       <c r="E16" t="n">
-        <v>8.039029442130641e-10</v>
+        <v>7.695457604484091e-09</v>
       </c>
       <c r="F16" t="n">
-        <v>1.455565667995984e-10</v>
+        <v>2.95441520137274e-08</v>
       </c>
       <c r="G16" t="n">
-        <v>2.990631353672057e-11</v>
+        <v>1.010105421528351e-08</v>
       </c>
       <c r="H16" t="n">
-        <v>6.499308730090192e-11</v>
+        <v>1.316363018588618e-08</v>
       </c>
       <c r="I16" t="n">
-        <v>3.275905657851297e-10</v>
+        <v>1.17065546145767e-09</v>
       </c>
       <c r="J16" t="n">
-        <v>3.170376183803114e-10</v>
+        <v>1.871360844063474e-09</v>
       </c>
       <c r="K16" t="n">
-        <v>7.983579353165737e-10</v>
+        <v>3.444979768119083e-08</v>
       </c>
       <c r="L16" t="n">
-        <v>1.979754554737312e-10</v>
+        <v>9.566345937628284e-09</v>
       </c>
       <c r="M16" t="n">
-        <v>1.615542144506321e-10</v>
+        <v>1.771265445427161e-08</v>
       </c>
       <c r="N16" t="n">
-        <v>1.689544476546345e-10</v>
+        <v>2.063836745946901e-08</v>
       </c>
       <c r="O16" t="n">
-        <v>2.612131067003531e-10</v>
+        <v>2.98269924314809e-08</v>
       </c>
       <c r="P16" t="n">
-        <v>3.892411670758378e-10</v>
+        <v>9.116267740694184e-09</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.098526907801102e-10</v>
+        <v>7.012131320038861e-09</v>
       </c>
       <c r="R16" t="n">
-        <v>1.853831810283424e-10</v>
+        <v>8.4876811135004e-10</v>
       </c>
       <c r="S16" t="n">
-        <v>1.853161929465941e-10</v>
+        <v>5.351719511992314e-09</v>
       </c>
       <c r="T16" t="n">
-        <v>2.176717972535158e-10</v>
+        <v>1.000417748642235e-09</v>
       </c>
       <c r="U16" t="n">
-        <v>1.678146233086153e-10</v>
+        <v>5.858960872018315e-09</v>
       </c>
       <c r="V16" t="n">
-        <v>2.189023129428591e-10</v>
+        <v>6.886367920344583e-09</v>
       </c>
       <c r="W16" t="n">
-        <v>6.321529411046356e-10</v>
+        <v>2.328655490657638e-09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.206410804588387e-10</v>
+        <v>1.763672430321606e-09</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.640618917444272e-10</v>
+        <v>3.770023404570111e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.295877571916293e-10</v>
+        <v>1.74075776016025e-09</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.954703204853914e-10</v>
+        <v>3.962989658656824e-10</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.486393508276507e-10</v>
+        <v>4.273885245709153e-09</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.299167384256506e-10</v>
+        <v>9.276921453249543e-09</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.61708005161654e-10</v>
+        <v>6.354112791484567e-09</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.127182236437818e-10</v>
+        <v>4.273011722233377e-09</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.946704186739368e-10</v>
+        <v>2.786452846237353e-09</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.394416692170665e-10</v>
+        <v>1.016143702514682e-08</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.257462051151848e-10</v>
+        <v>5.6351046051617e-10</v>
       </c>
       <c r="AI16" t="n">
-        <v>9.482450935571762e-11</v>
+        <v>1.347017519748306e-08</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.458377862917359e-10</v>
+        <v>2.418164279927026e-10</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.77679462756808e-10</v>
+        <v>9.786861099314592e-09</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.165541135828008e-10</v>
+        <v>4.683730736587677e-09</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.022602502149695e-10</v>
+        <v>1.057637355472707e-08</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.648163688861004e-10</v>
+        <v>9.669072653650801e-09</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.026978849183457e-11</v>
+        <v>1.33264643764619e-09</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.754517642282849e-10</v>
+        <v>3.012702975979664e-09</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.060831449408496e-11</v>
+        <v>1.916981906546766e-09</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.248440405556607e-10</v>
+        <v>4.85755036194746e-09</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.026858707595338e-12</v>
+        <v>3.699316852845413e-09</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.278122495675717e-10</v>
+        <v>6.916015760083383e-09</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.217035999230177e-10</v>
+        <v>2.375149499300733e-08</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.675674599077581e-10</v>
+        <v>1.169915897492046e-08</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.923527224283021e-10</v>
+        <v>1.813591499200129e-10</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.099709626283811e-10</v>
+        <v>2.295480605596367e-08</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.50157622447189e-10</v>
+        <v>1.709815578010421e-08</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.344806181499905e-10</v>
+        <v>2.356769890354826e-09</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.658016584611289e-10</v>
+        <v>1.186233111738488e-09</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.4720330777116e-11</v>
+        <v>6.199117885685723e-10</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.573055713466331e-10</v>
+        <v>3.776397416999089e-09</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.043706398031532e-10</v>
+        <v>5.027653404710009e-09</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.236693968400317e-10</v>
+        <v>1.455934039995554e-09</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.780793984496043e-10</v>
+        <v>4.784549645364677e-09</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.135480598435379e-11</v>
+        <v>9.551355262260586e-09</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.584429059648841e-10</v>
+        <v>2.086213979346496e-10</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.095311757959294e-10</v>
+        <v>2.026564249746343e-09</v>
       </c>
       <c r="BJ16" t="n">
-        <v>4.313618073847891e-10</v>
+        <v>8.833731968138636e-09</v>
       </c>
       <c r="BK16" t="n">
-        <v>2.015919653430842e-10</v>
+        <v>1.279654826547016e-09</v>
       </c>
       <c r="BL16" t="n">
-        <v>4.758207716726304e-11</v>
+        <v>4.893857319387962e-09</v>
       </c>
       <c r="BM16" t="n">
-        <v>5.200080643863458e-11</v>
+        <v>7.965049064750929e-09</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.919119361319503e-11</v>
+        <v>3.054740238539466e-09</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.468636878776408e-10</v>
+        <v>2.534833454248542e-09</v>
       </c>
       <c r="BP16" t="n">
-        <v>1.512081848620284e-10</v>
+        <v>9.507890474935721e-09</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.780600832392622e-12</v>
+        <v>4.027750577506595e-09</v>
       </c>
       <c r="BR16" t="n">
-        <v>6.773121646874714e-11</v>
+        <v>5.954350346115689e-09</v>
       </c>
       <c r="BS16" t="n">
-        <v>5.861713892052478e-12</v>
+        <v>2.036860902165927e-09</v>
       </c>
       <c r="BT16" t="n">
-        <v>7.941763913166255e-11</v>
+        <v>1.977313646150947e-09</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.493218769801132e-10</v>
+        <v>1.277265626598023e-09</v>
       </c>
       <c r="BV16" t="n">
-        <v>6.791887885437831e-11</v>
+        <v>1.145136874214359e-08</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.454809216485444e-10</v>
+        <v>5.108212519644439e-09</v>
       </c>
       <c r="BX16" t="n">
-        <v>2.739812023089261e-11</v>
+        <v>3.048882035727729e-09</v>
       </c>
       <c r="BY16" t="n">
-        <v>4.362517291855994e-10</v>
+        <v>2.613932625905591e-09</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.672786297841512e-11</v>
+        <v>7.774102250834858e-09</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.012436523506466e-10</v>
+        <v>6.333361834975904e-09</v>
       </c>
       <c r="CB16" t="n">
-        <v>1.743686306454606e-10</v>
+        <v>4.872213188455987e-10</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.903011082049488e-11</v>
+        <v>6.483102943377617e-11</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.566362136164791e-11</v>
+        <v>7.02118474471547e-10</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.165500612687609e-10</v>
+        <v>1.013808592631449e-08</v>
       </c>
       <c r="CF16" t="n">
-        <v>5.360718119407082e-11</v>
+        <v>2.099561857704657e-09</v>
       </c>
       <c r="CG16" t="n">
-        <v>4.415876345142955e-11</v>
+        <v>4.997730673750311e-09</v>
       </c>
       <c r="CH16" t="n">
-        <v>6.956206444197477e-12</v>
+        <v>4.093854144571196e-09</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.715000273212365e-11</v>
+        <v>7.095219967112598e-09</v>
       </c>
       <c r="CJ16" t="n">
-        <v>6.968081667224624e-11</v>
+        <v>2.061553427967766e-10</v>
       </c>
       <c r="CK16" t="n">
-        <v>5.525997021083029e-11</v>
+        <v>2.823352884817609e-09</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.447976877289037e-10</v>
+        <v>2.430925905017034e-09</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.230300167298637e-10</v>
+        <v>5.56362156345358e-09</v>
       </c>
       <c r="CN16" t="n">
-        <v>7.555150949301037e-12</v>
+        <v>6.054335255356591e-09</v>
       </c>
       <c r="CO16" t="n">
-        <v>8.315188815277708e-11</v>
+        <v>1.033741359179885e-08</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.403539506839024e-10</v>
+        <v>1.064983212728521e-09</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.585582941667553e-10</v>
+        <v>5.344061859702265e-10</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.017912837353308e-11</v>
+        <v>4.239418593954269e-09</v>
       </c>
       <c r="CS16" t="n">
-        <v>1.628639445527824e-10</v>
+        <v>5.627426524767998e-09</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.173965534841727e-10</v>
+        <v>2.774522611659336e-09</v>
       </c>
       <c r="CU16" t="n">
-        <v>3.042615881465593e-10</v>
+        <v>2.97581026487137e-09</v>
       </c>
       <c r="CV16" t="n">
-        <v>5.757270354900257e-11</v>
+        <v>8.384826721830052e-10</v>
       </c>
       <c r="CW16" t="n">
-        <v>5.930866908698817e-11</v>
+        <v>7.333653684327146e-09</v>
       </c>
       <c r="CX16" t="n">
-        <v>2.26363892907866e-12</v>
+        <v>2.141454347182048e-09</v>
       </c>
       <c r="CY16" t="n">
-        <v>7.441661870055682e-11</v>
+        <v>5.781895850986984e-09</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.235643441206303e-11</v>
+        <v>4.858347946168351e-09</v>
       </c>
       <c r="DA16" t="n">
-        <v>5.480399467572283e-11</v>
+        <v>7.811181035322079e-09</v>
       </c>
       <c r="DB16" t="n">
-        <v>8.086210173674502e-11</v>
+        <v>8.756804725784662e-10</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.196626387729328e-11</v>
+        <v>2.470139648380609e-09</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.706459973327412e-10</v>
+        <v>2.274209043306996e-09</v>
       </c>
       <c r="DE16" t="n">
-        <v>3.27089327845087e-10</v>
+        <v>2.319870073819175e-09</v>
       </c>
       <c r="DF16" t="n">
-        <v>3.276774962479578e-10</v>
+        <v>2.777159169298216e-09</v>
       </c>
       <c r="DG16" t="n">
-        <v>4.006019960201002e-10</v>
+        <v>3.44703865451379e-09</v>
       </c>
       <c r="DH16" t="n">
-        <v>4.212301063510893e-10</v>
+        <v>1.555720885448864e-09</v>
       </c>
       <c r="DI16" t="n">
-        <v>5.144866754847044e-10</v>
+        <v>1.013527395343772e-08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>6.446815303817743e-11</v>
+        <v>1.243188751942625e-08</v>
       </c>
       <c r="DK16" t="n">
-        <v>1.606244998120232e-11</v>
+        <v>5.939668201726533e-10</v>
       </c>
       <c r="DL16" t="n">
-        <v>7.617772523893507e-10</v>
+        <v>7.558519143913145e-09</v>
       </c>
       <c r="DM16" t="n">
-        <v>3.67400332379475e-10</v>
+        <v>5.121461033041896e-09</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.367673196916996e-10</v>
+        <v>2.648089303391998e-09</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.297177448262744e-10</v>
+        <v>7.361554033025186e-09</v>
       </c>
       <c r="DP16" t="n">
-        <v>1.26478327810986e-10</v>
+        <v>7.237191956832589e-10</v>
       </c>
       <c r="DQ16" t="n">
-        <v>3.853811991749723e-10</v>
+        <v>3.064593023793805e-09</v>
       </c>
       <c r="DR16" t="n">
-        <v>3.198113301960959e-11</v>
+        <v>3.172166140874566e-10</v>
       </c>
       <c r="DS16" t="n">
-        <v>1.151545248045949e-10</v>
+        <v>6.461346568897852e-09</v>
       </c>
       <c r="DT16" t="n">
-        <v>6.174680905468577e-11</v>
+        <v>3.837445916587967e-09</v>
       </c>
       <c r="DU16" t="n">
-        <v>6.457724632813466e-11</v>
+        <v>4.388855501247235e-09</v>
       </c>
       <c r="DV16" t="n">
-        <v>6.951254849507649e-11</v>
+        <v>3.684062499509366e-10</v>
       </c>
       <c r="DW16" t="n">
-        <v>1.790132764245556e-10</v>
+        <v>4.802264363945596e-09</v>
       </c>
       <c r="DX16" t="n">
-        <v>1.361079582373748e-10</v>
+        <v>5.97439697713753e-09</v>
       </c>
       <c r="DY16" t="n">
-        <v>4.317010360299633e-10</v>
+        <v>9.093434449880533e-09</v>
       </c>
       <c r="DZ16" t="n">
-        <v>1.314080927405925e-10</v>
+        <v>2.080846828178551e-09</v>
       </c>
       <c r="EA16" t="n">
-        <v>2.23965929135872e-10</v>
+        <v>4.351548454906151e-09</v>
       </c>
       <c r="EB16" t="n">
-        <v>7.085571018805581e-11</v>
+        <v>3.116037206041256e-09</v>
       </c>
       <c r="EC16" t="n">
-        <v>6.045260125819851e-11</v>
+        <v>4.061438685365459e-10</v>
       </c>
       <c r="ED16" t="n">
-        <v>1.144325745272567e-10</v>
+        <v>6.118930695464542e-09</v>
       </c>
       <c r="EE16" t="n">
-        <v>1.894083778708477e-10</v>
+        <v>4.211619053506865e-09</v>
       </c>
       <c r="EF16" t="n">
-        <v>2.728609005409055e-10</v>
+        <v>4.050471957839363e-09</v>
       </c>
       <c r="EG16" t="n">
-        <v>9.425096814119627e-11</v>
+        <v>5.91670179517223e-09</v>
       </c>
       <c r="EH16" t="n">
-        <v>8.570168880117635e-11</v>
+        <v>7.967781989748346e-10</v>
       </c>
       <c r="EI16" t="n">
-        <v>1.220489403985781e-10</v>
+        <v>1.738760913028159e-09</v>
       </c>
       <c r="EJ16" t="n">
-        <v>1.596914545043404e-10</v>
+        <v>8.817917063197456e-09</v>
       </c>
       <c r="EK16" t="n">
-        <v>1.697962048741175e-10</v>
+        <v>7.362300546986944e-09</v>
       </c>
       <c r="EL16" t="n">
-        <v>4.048597568306889e-11</v>
+        <v>1.448050568342296e-09</v>
       </c>
       <c r="EM16" t="n">
-        <v>1.529774570907527e-12</v>
+        <v>4.064499015132839e-10</v>
       </c>
       <c r="EN16" t="n">
-        <v>9.919035037775359e-11</v>
+        <v>4.032383038587994e-10</v>
       </c>
       <c r="EO16" t="n">
-        <v>8.868480949608681e-11</v>
+        <v>3.438862306026635e-09</v>
       </c>
       <c r="EP16" t="n">
-        <v>1.247968950401912e-10</v>
+        <v>3.904352841033187e-09</v>
       </c>
       <c r="EQ16" t="n">
-        <v>1.506309244003745e-10</v>
+        <v>3.082781585561634e-09</v>
       </c>
       <c r="ER16" t="n">
-        <v>1.585011566440642e-10</v>
+        <v>6.785375816775741e-09</v>
       </c>
       <c r="ES16" t="n">
-        <v>2.349345717966855e-10</v>
+        <v>3.317857988349715e-09</v>
       </c>
       <c r="ET16" t="n">
-        <v>1.005798846986927e-10</v>
+        <v>1.126289617126019e-09</v>
       </c>
       <c r="EU16" t="n">
-        <v>2.10036765757593e-10</v>
+        <v>1.816963801637428e-09</v>
       </c>
       <c r="EV16" t="n">
-        <v>3.418628435891691e-10</v>
+        <v>2.885048200340634e-09</v>
       </c>
       <c r="EW16" t="n">
-        <v>3.556340638644073e-11</v>
+        <v>2.797726272874002e-09</v>
       </c>
       <c r="EX16" t="n">
-        <v>7.933792511849447e-11</v>
+        <v>6.854529166488987e-10</v>
       </c>
       <c r="EY16" t="n">
-        <v>4.411376819390966e-11</v>
+        <v>1.044991293497333e-08</v>
       </c>
       <c r="EZ16" t="n">
-        <v>1.397547876036409e-11</v>
+        <v>2.276616450913593e-09</v>
       </c>
       <c r="FA16" t="n">
-        <v>2.670083945610635e-11</v>
+        <v>5.602906583135336e-09</v>
       </c>
       <c r="FB16" t="n">
-        <v>5.303160688363562e-11</v>
+        <v>2.470999849180089e-09</v>
       </c>
       <c r="FC16" t="n">
-        <v>2.950534261358939e-11</v>
+        <v>7.280291924871563e-09</v>
       </c>
       <c r="FD16" t="n">
-        <v>9.143080736961906e-11</v>
+        <v>1.604079924444335e-10</v>
       </c>
       <c r="FE16" t="n">
-        <v>5.809252384691987e-12</v>
+        <v>2.849762426038183e-09</v>
       </c>
       <c r="FF16" t="n">
-        <v>1.915070046987211e-10</v>
+        <v>5.076716824703453e-10</v>
       </c>
       <c r="FG16" t="n">
-        <v>2.798505177592503e-11</v>
+        <v>5.117889445571677e-10</v>
       </c>
       <c r="FH16" t="n">
-        <v>4.801951891675316e-11</v>
+        <v>4.688335941693822e-09</v>
       </c>
       <c r="FI16" t="n">
-        <v>3.772857581907374e-10</v>
+        <v>8.164887432826617e-09</v>
       </c>
       <c r="FJ16" t="n">
-        <v>3.127055836493753e-10</v>
+        <v>1.836799601306893e-09</v>
       </c>
       <c r="FK16" t="n">
-        <v>1.189350840036241e-10</v>
+        <v>1.923785797330879e-09</v>
       </c>
       <c r="FL16" t="n">
-        <v>3.513095370166752e-10</v>
+        <v>6.270942876085428e-09</v>
       </c>
       <c r="FM16" t="n">
-        <v>1.028941098990543e-10</v>
+        <v>2.674428178917054e-10</v>
       </c>
       <c r="FN16" t="n">
-        <v>3.156073180576868e-10</v>
+        <v>6.554286002824483e-09</v>
       </c>
       <c r="FO16" t="n">
-        <v>3.608200405125217e-10</v>
+        <v>8.648035176861413e-09</v>
       </c>
       <c r="FP16" t="n">
-        <v>1.451436609789525e-10</v>
+        <v>8.501074511002571e-09</v>
       </c>
       <c r="FQ16" t="n">
-        <v>2.547125010909923e-11</v>
+        <v>7.635064136479741e-09</v>
       </c>
       <c r="FR16" t="n">
-        <v>4.285269639137113e-10</v>
+        <v>1.357596968176722e-08</v>
       </c>
       <c r="FS16" t="n">
-        <v>3.491691380475004e-10</v>
+        <v>8.581189980816362e-09</v>
       </c>
       <c r="FT16" t="n">
-        <v>3.348402666247807e-10</v>
+        <v>1.121839177109507e-09</v>
       </c>
       <c r="FU16" t="n">
-        <v>1.579856245825795e-10</v>
+        <v>6.927312057314339e-10</v>
       </c>
       <c r="FV16" t="n">
-        <v>1.670632659989124e-10</v>
+        <v>1.449157793764755e-09</v>
       </c>
       <c r="FW16" t="n">
-        <v>7.877965640945561e-11</v>
+        <v>9.496719854951152e-09</v>
       </c>
       <c r="FX16" t="n">
-        <v>9.796199962330832e-11</v>
+        <v>1.671906835198911e-09</v>
       </c>
       <c r="FY16" t="n">
-        <v>2.487227368508371e-10</v>
+        <v>2.098771378911124e-09</v>
       </c>
       <c r="FZ16" t="n">
-        <v>4.207606207895509e-10</v>
+        <v>5.995381968659785e-10</v>
       </c>
       <c r="GA16" t="n">
-        <v>1.873202565283449e-10</v>
+        <v>8.650861360592899e-09</v>
       </c>
       <c r="GB16" t="n">
-        <v>1.948531891393657e-10</v>
+        <v>2.811441524031011e-09</v>
       </c>
       <c r="GC16" t="n">
-        <v>3.681468740968086e-10</v>
+        <v>1.228935264663278e-08</v>
       </c>
       <c r="GD16" t="n">
-        <v>1.272211502811871e-12</v>
+        <v>9.889638441507032e-09</v>
       </c>
       <c r="GE16" t="n">
-        <v>2.613165586695665e-11</v>
+        <v>3.087143873869991e-09</v>
       </c>
       <c r="GF16" t="n">
-        <v>3.306583895579251e-10</v>
+        <v>3.849098373365223e-09</v>
       </c>
       <c r="GG16" t="n">
-        <v>9.497055225571316e-11</v>
+        <v>3.94390686775381e-10</v>
       </c>
     </row>
   </sheetData>
